--- a/posts/2026/assets/toy-compare/toy-data.xlsx
+++ b/posts/2026/assets/toy-compare/toy-data.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产品资料" sheetId="1" r:id="R9244ab99931049f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产品来源" sheetId="2" r:id="R7b4cbec55a7e4707"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="标签定义" sheetId="3" r:id="Re6c68bffda884012"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="综合资源" sheetId="4" r:id="R9a245dfc639f443b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资料统计" sheetId="5" r:id="Rb32d85e9659f40cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产品资料" sheetId="1" r:id="R38c2a5b912834b67"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产品来源" sheetId="2" r:id="Rffd7b0b75a7241e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="标签定义" sheetId="3" r:id="Rf8e01a91ea3842df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="综合资源" sheetId="4" r:id="R3fba14e235734891"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资料统计" sheetId="5" r:id="R54a46eb2fe424b4d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -185,8 +185,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Products" displayName="Products" ref="A4:T271" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:T271"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Products" displayName="Products" ref="A4:T273" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:T273"/>
   <x:tableColumns count="20">
     <x:tableColumn id="1" name="产品"/>
     <x:tableColumn id="2" name="品牌／厂商"/>
@@ -214,8 +214,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Sources" displayName="Sources" ref="A4:H294" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:H294"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Sources" displayName="Sources" ref="A4:H323" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:H323"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="产品"/>
     <x:tableColumn id="2" name="顺序"/>
@@ -513,7 +513,7 @@
     </x:row>
     <x:row r="2" ht="34" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>267 条具体商品记录 · 数值空白表示未知，服装项不适用人形高度 · 本表与网页资料同步维护</x:v>
+        <x:v>269 条具体商品记录 · 数值空白表示未知，服装项不适用人形高度 · 本表与网页资料同步维护</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -1439,7 +1439,7 @@
         <x:v>https://shop.mattel.com/products/barbie-made-to-move-tennis-player-doll-hkt73</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="110" customHeight="1">
+    <x:row r="18" ht="219" customHeight="1">
       <x:c r="A18" s="11" t="str">
         <x:v>OBITSU 22 cm · S 胸</x:v>
       </x:c>
@@ -1450,7 +1450,7 @@
         <x:v>内部骨架、关节可动</x:v>
       </x:c>
       <x:c r="D18" s="13" t="str">
-        <x:v>素体成品</x:v>
+        <x:v>素体成品、头部另配</x:v>
       </x:c>
       <x:c r="E18" s="20" t="str">
         <x:v>比例 1:6</x:v>
@@ -1459,7 +1459,7 @@
         <x:v>220</x:v>
       </x:c>
       <x:c r="G18" s="16" t="str">
-        <x:v>官方身体约 22 cm，不附头</x:v>
+        <x:v>官方 S 胸规格表全长约 22 cm；不附头，约数随测量方法变化。</x:v>
       </x:c>
       <x:c r="H18" s="17" t="str">
         <x:v>布衣穿脱、换手、头部适配器</x:v>
@@ -1483,18 +1483,22 @@
         <x:v>按所列来源的具体型号整理；不代表全部批次。</x:v>
       </x:c>
       <x:c r="O18" s="11" t="str">
-        <x:v>高度 22 cm（官方身体约 22 cm，不附头）</x:v>
+        <x:v>素体全长约 22 cm（官方 S 胸规格表全长约 22 cm；不附头，约数随测量方法变化。）</x:v>
       </x:c>
       <x:c r="P18" s="11" t="str">
-        <x:v>身体构造：胸至腰采用软质外皮与内部骨架，其他连接由多种材料构成。
-交付内容：无头自然肤色 S 胸素体，附持物／握拳手与头部适配器。
-适配范围：不同批次的肤色与关节强度可能有差别；未证明与 24 cm 的所有衣服通用。</x:v>
+        <x:v>常见叫法：OB22、OB 22、オビツ22、オビツ製作所
+身体构造：胸至腰采用软质外皮与内部骨架，其他连接由多种材料构成。
+交付内容：身体默认装张开手、中号头部适配器；另附持物手、握拳手、小／大适配器与固定垫圈。无头，头与衣服另配。
+适配范围：不同批次的肤色与关节强度可能有差别；未证明与 24 cm 的所有衣服通用。
+厂商与叫法：OB22 是 OBITSU BODY 22 的常见简称，厂商为日本株式会社オビツ製作所（Obitsu Plastic Manufacturing）。不是 AZONE 的厂牌。
+头部与维护：按头部首孔选择适配器，不能保证适配所有头。官方不单独销售本款首部、脚踝等维护小零件；关节松紧和肤色有个体／批次差异。
+S 胸参考尺寸：官方尺寸表（cm）：肩宽 3.4、胸围 8.6、腰围 6.7、臀围 9.5；脚底长 2.4 × 宽 0.9。为约数，不能据此保证服装通用。</x:v>
       </x:c>
       <x:c r="Q18" s="11" t="str">
         <x:v>未取得产品对应证据</x:v>
       </x:c>
       <x:c r="R18" s="11" t="str">
-        <x:v>2026-10-05</x:v>
+        <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="S18" s="11" t="str">
         <x:v>obitsu-22-s</x:v>
@@ -1503,7 +1507,7 @@
         <x:v>https://obitsu.co.jp/doll-division/obitsu-body-and-parts/obitsu-body/obitsu-body-22/</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="110" customHeight="1">
+    <x:row r="19" ht="219" customHeight="1">
       <x:c r="A19" s="11" t="str">
         <x:v>OBITSU 24 cm · S 胸</x:v>
       </x:c>
@@ -1514,7 +1518,7 @@
         <x:v>内部骨架、关节可动</x:v>
       </x:c>
       <x:c r="D19" s="13" t="str">
-        <x:v>素体成品</x:v>
+        <x:v>素体成品、头部另配</x:v>
       </x:c>
       <x:c r="E19" s="20" t="str">
         <x:v>约 1:6</x:v>
@@ -1523,7 +1527,7 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="G19" s="16" t="str">
-        <x:v>官方身体约 24 cm，不附头</x:v>
+        <x:v>商品页标称约 24 cm；官方 S 胸规格表另列全长约 21.8 cm，两页口径未统一，不当作实测同值。</x:v>
       </x:c>
       <x:c r="H19" s="17" t="str">
         <x:v>布衣穿脱、换手、头部适配器</x:v>
@@ -1547,18 +1551,23 @@
         <x:v>按所列来源的具体型号整理；不代表全部批次。</x:v>
       </x:c>
       <x:c r="O19" s="11" t="str">
-        <x:v>高度 24 cm（官方身体约 24 cm，不附头）</x:v>
+        <x:v>标称约 24 cm（官方商品页的近似高度；不附头。）
+规格表全长约 21.8 cm（官方默认 S 胸尺寸表；与商品页约 24 cm 并列保留，未确认口径差异原因。）</x:v>
       </x:c>
       <x:c r="P19" s="11" t="str">
-        <x:v>身体构造：自然肤色哑光 S 胸。胸至腰采用软质外皮与内部骨架，ABS／POM／PVC 复合构成。
-交付与适配：无头，附手型与头部适配器。官方有 24／26 共用手套件，但这不是全身和全部衣服通用的证明。
-尺寸口径：约 24 cm 为身体规格，不含另配头。</x:v>
+        <x:v>常见叫法：OB24、OB 24、オビツ24、オビツ製作所
+身体构造：自然肤色哑光 S 胸。胸至腰采用软质外皮与内部骨架，ABS／POM／PVC 复合构成。
+交付与适配：身体默认装张开手、中号头部适配器；另附持物手、握拳手、小／大适配器与固定垫圈。无头，头与衣服另配。
+尺寸口径：商品页标称约 24 cm；官方 S 胸规格表另列全长约 21.8 cm，两页口径未统一，不当作实测同值。
+厂商与叫法：OB24 是 OBITSU BODY 24 的常见简称，厂商为日本株式会社オビツ製作所（Obitsu Plastic Manufacturing）。不是 AZONE 的厂牌。
+头部与维护：按头部首孔选择适配器，不能保证适配所有头。官方不单独销售本款首部、脚踝等维护小零件；关节松紧和肤色有个体／批次差异。
+S 胸参考尺寸：官方尺寸表（cm）：肩宽 3.2、腰围 7.4、臀围 9.8；脚底长 2.5 × 宽 1.1。胸围在同页图文与表格也有差异，选服装请核对原页与具体身体。</x:v>
       </x:c>
       <x:c r="Q19" s="11" t="str">
         <x:v>未取得产品对应证据</x:v>
       </x:c>
       <x:c r="R19" s="11" t="str">
-        <x:v>2026-10-05</x:v>
+        <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="S19" s="11" t="str">
         <x:v>obitsu-24-s-matte</x:v>
@@ -16209,7 +16218,7 @@
         <x:v>https://www.goodsmile.com/en/product/57238</x:v>
       </x:c>
     </x:row>
-    <x:row r="250" ht="110" customHeight="1">
+    <x:row r="250" ht="165" customHeight="1">
       <x:c r="A250" s="11" t="str">
         <x:v>Pure Neemo 2 Feel · S · 白肌</x:v>
       </x:c>
@@ -16230,7 +16239,7 @@
         <x:v>未披露</x:v>
       </x:c>
       <x:c r="H250" s="17" t="str">
-        <x:v>服装另配</x:v>
+        <x:v>服装另配、换手</x:v>
       </x:c>
       <x:c r="I250" s="18" t="str">
         <x:v>材料未披露</x:v>
@@ -16257,7 +16266,8 @@
         <x:v>本款交付：型号 PFL103-WHT，白肌，头部不附属。
 结构版本：Feel 系列重新调整 Emotion 的关节结构及外形。本条为普通白肌版本，不混入另售的 Silky Skin 型号。
 高度与配件限制：官方本款页未给出素体厘米高度；不借用装头整娃的全高。
-销售页面口径：页面库存、再入荷及会员购买限制可能变化；此条是型号资料，不表示现货或代购热度排名。</x:v>
+销售页面口径：资料可免登录阅读，购买限制与现货以商品页为准。官方 2026 年 8 月 27 日公告逐步恢复 Emotion 以外的 Pure Neemo 系列店头销售，各店方式不同；不据此推定本款有现货。
+换手与批次：官方 PFL065 白肌换手注明适用 Emotion／Feel 女孩 S、M。普通换手 A／B 从 2026 年 8 月出货起由 PFL063／064 改为 PFL107／108；另售配件，不等于本体附送。</x:v>
       </x:c>
       <x:c r="Q250" s="11" t="str">
         <x:v>未取得产品对应证据</x:v>
@@ -16272,7 +16282,7 @@
         <x:v>https://www.azone-int.co.jp/azonet/item/4573199849805</x:v>
       </x:c>
     </x:row>
-    <x:row r="251" ht="110" customHeight="1">
+    <x:row r="251" ht="165" customHeight="1">
       <x:c r="A251" s="11" t="str">
         <x:v>Pure Neemo 2 Feel · M · 白肌</x:v>
       </x:c>
@@ -16293,7 +16303,7 @@
         <x:v>未披露</x:v>
       </x:c>
       <x:c r="H251" s="17" t="str">
-        <x:v>服装另配</x:v>
+        <x:v>服装另配、换手</x:v>
       </x:c>
       <x:c r="I251" s="18" t="str">
         <x:v>材料未披露</x:v>
@@ -16320,7 +16330,8 @@
         <x:v>本款交付：型号 PFL104-WHT，白肌，头部不附属。
 结构版本：Feel 系列重新调整 Emotion 的关节结构及外形。本条为普通白肌版本，不混入另售的 Silky Skin 型号。
 高度与配件限制：官方本款页未给出素体厘米高度；不借用装头整娃的全高。
-销售页面口径：页面库存、再入荷及会员购买限制可能变化；此条是型号资料，不表示现货或代购热度排名。</x:v>
+销售页面口径：资料可免登录阅读，购买限制与现货以商品页为准。官方 2026 年 8 月 27 日公告逐步恢复 Emotion 以外的 Pure Neemo 系列店头销售，各店方式不同；不据此推定本款有现货。
+换手与批次：官方 PFL065 白肌换手注明适用 Emotion／Feel 女孩 S、M。普通换手 A／B 从 2026 年 8 月出货起由 PFL063／064 改为 PFL107／108；另售配件，不等于本体附送。</x:v>
       </x:c>
       <x:c r="Q251" s="11" t="str">
         <x:v>未取得产品对应证据</x:v>
@@ -16335,7 +16346,7 @@
         <x:v>https://www.azone-int.co.jp/azonet/item/4573199849812</x:v>
       </x:c>
     </x:row>
-    <x:row r="252" ht="110" customHeight="1">
+    <x:row r="252" ht="180" customHeight="1">
       <x:c r="A252" s="11" t="str">
         <x:v>Pure Neemo 2 Emotion · S · 白肌</x:v>
       </x:c>
@@ -16356,7 +16367,7 @@
         <x:v>未披露</x:v>
       </x:c>
       <x:c r="H252" s="17" t="str">
-        <x:v>服装另配</x:v>
+        <x:v>服装另配、换手</x:v>
       </x:c>
       <x:c r="I252" s="18" t="str">
         <x:v>材料未披露</x:v>
@@ -16381,9 +16392,10 @@
       </x:c>
       <x:c r="P252" s="11" t="str">
         <x:v>本款交付：型号 PFL099-WHT，白肌，头部不附属。
-结构版本：Emotion 系列增加胸下与腰部活动结构；本款白肌 SKU 单列。
+结构版本：Emotion 系列增加胸下、腰关节，支持跪坐和前屈等姿势；S、M 为不同身体规格。
 高度与配件限制：官方本款页未给出素体厘米高度；不借用装头整娃的全高。 本款页注明 2025-03-03 起出货批次不再附高跟脚；旧系列介绍中的配件不能套用到新批次。
-销售页面口径：页面库存、再入荷及会员购买限制可能变化；此条是型号资料，不表示现货或代购热度排名。</x:v>
+销售页面口径：资料可免登录阅读，购买限制与现货以商品页为准。官方 2026 年 8 月 27 日公告逐步恢复 Emotion 以外的 Pure Neemo 系列店头销售，各店方式不同；不据此推定本款有现货。
+换手与批次：官方 PFL065 白肌换手注明适用 Emotion／Feel 女孩 S、M。普通换手 A／B 从 2026 年 8 月出货起由 PFL063／064 改为 PFL107／108；另售配件，不等于本体附送。</x:v>
       </x:c>
       <x:c r="Q252" s="11" t="str">
         <x:v>未取得产品对应证据</x:v>
@@ -16398,7 +16410,7 @@
         <x:v>https://www.azone-int.co.jp/azonet/item/4573199846163</x:v>
       </x:c>
     </x:row>
-    <x:row r="253" ht="110" customHeight="1">
+    <x:row r="253" ht="180" customHeight="1">
       <x:c r="A253" s="11" t="str">
         <x:v>Pure Neemo 2 Emotion · M · 白肌</x:v>
       </x:c>
@@ -16419,7 +16431,7 @@
         <x:v>未披露</x:v>
       </x:c>
       <x:c r="H253" s="17" t="str">
-        <x:v>服装另配</x:v>
+        <x:v>服装另配、换手</x:v>
       </x:c>
       <x:c r="I253" s="18" t="str">
         <x:v>材料未披露</x:v>
@@ -16444,9 +16456,10 @@
       </x:c>
       <x:c r="P253" s="11" t="str">
         <x:v>本款交付：型号 PFL100-WHT，白肌，头部不附属。
-结构版本：Emotion 系列增加胸下与腰部活动结构；本款白肌 SKU 单列。
+结构版本：Emotion 系列增加胸下、腰关节，支持跪坐和前屈等姿势；S、M 为不同身体规格。
 高度与配件限制：官方本款页未给出素体厘米高度；不借用装头整娃的全高。 本款页注明 2025-03-03 起出货批次不再附高跟脚；旧系列介绍中的配件不能套用到新批次。
-销售页面口径：页面库存、再入荷及会员购买限制可能变化；此条是型号资料，不表示现货或代购热度排名。</x:v>
+销售页面口径：资料可免登录阅读，购买限制与现货以商品页为准。官方 2026 年 8 月 27 日公告逐步恢复 Emotion 以外的 Pure Neemo 系列店头销售，各店方式不同；不据此推定本款有现货。
+换手与批次：官方 PFL065 白肌换手注明适用 Emotion／Feel 女孩 S、M。普通换手 A／B 从 2026 年 8 月出货起由 PFL063／064 改为 PFL107／108；另售配件，不等于本体附送。</x:v>
       </x:c>
       <x:c r="Q253" s="11" t="str">
         <x:v>未取得产品对应证据</x:v>
@@ -16461,7 +16474,7 @@
         <x:v>https://www.azone-int.co.jp/azonet/item/4573199846187</x:v>
       </x:c>
     </x:row>
-    <x:row r="254" ht="110" customHeight="1">
+    <x:row r="254" ht="165" customHeight="1">
       <x:c r="A254" s="11" t="str">
         <x:v>Pure Neemo Flection · M · 白肌</x:v>
       </x:c>
@@ -16482,7 +16495,7 @@
         <x:v>未披露</x:v>
       </x:c>
       <x:c r="H254" s="17" t="str">
-        <x:v>服装另配</x:v>
+        <x:v>服装另配、换手</x:v>
       </x:c>
       <x:c r="I254" s="18" t="str">
         <x:v>材料未披露</x:v>
@@ -16507,9 +16520,10 @@
       </x:c>
       <x:c r="P254" s="11" t="str">
         <x:v>本款交付：型号 PFL088-WHT，白肌，头部不附属。
-结构版本：Flection 为关节可动素体。保留本款 M 女孩白肌型号，不从同系列尺寸字母推算高度。
+结构版本：Flection 系列有 22 处可动部位。2022 年改用新模具后，默认张开手逐步改为自然手；本条为 M 女孩白肌。
 高度与配件限制：官方本款页未给出素体厘米高度；不借用装头整娃的全高。
-销售页面口径：页面库存、再入荷及会员购买限制可能变化；此条是型号资料，不表示现货或代购热度排名。</x:v>
+销售页面口径：资料可免登录阅读，购买限制与现货以商品页为准。官方 2026 年 8 月 27 日公告逐步恢复 Emotion 以外的 Pure Neemo 系列店头销售，各店方式不同；不据此推定本款有现货。
+换手与批次：新模具可使用 Flection 换手，但松紧、肤色会有个体差异。2026 年 8 月起小手 A 由 PFL057 改为 PFL105，另有内容改版的 PFL106；换手套件另售。</x:v>
       </x:c>
       <x:c r="Q254" s="11" t="str">
         <x:v>未取得产品对应证据</x:v>
@@ -16524,7 +16538,7 @@
         <x:v>https://www.azone-int.co.jp/azonet/item/4573199841397</x:v>
       </x:c>
     </x:row>
-    <x:row r="255" ht="110" customHeight="1">
+    <x:row r="255" ht="150" customHeight="1">
       <x:c r="A255" s="11" t="str">
         <x:v>Picco Neemo · S 女孩 · 白肌</x:v>
       </x:c>
@@ -16545,7 +16559,7 @@
         <x:v>未披露</x:v>
       </x:c>
       <x:c r="H255" s="17" t="str">
-        <x:v>服装另配</x:v>
+        <x:v>服装另配、换手</x:v>
       </x:c>
       <x:c r="I255" s="18" t="str">
         <x:v>材料未披露</x:v>
@@ -16572,7 +16586,8 @@
         <x:v>本款交付：型号 PCN038-WHT，白肌，头部不附属。
 结构版本：Picco Neemo 为 1:12 可动素体。S、M、D 与胸部规格分别记录，换手接口不默认通用。
 高度与配件限制：官方本款页未给出素体厘米高度；不借用装头整娃的全高。
-销售页面口径：页面库存、再入荷及会员购买限制可能变化；此条是型号资料，不表示现货或代购热度排名。</x:v>
+销售页面口径：页面库存、再入荷及会员购买限制可能变化；此条是型号资料，不表示现货或代购热度排名。
+换手与配件：官方为 S／M 系列列出 PCA012（A）、PCA013（B） 换手，另有 PCA011 关节套件与 PCA010 首关节。配件另售；D 和 P 的换手另外列型，不默认通用。</x:v>
       </x:c>
       <x:c r="Q255" s="11" t="str">
         <x:v>未取得产品对应证据</x:v>
@@ -16587,7 +16602,7 @@
         <x:v>https://www.azone-int.co.jp/azonet/item/4573199841533</x:v>
       </x:c>
     </x:row>
-    <x:row r="256" ht="110" customHeight="1">
+    <x:row r="256" ht="150" customHeight="1">
       <x:c r="A256" s="11" t="str">
         <x:v>Picco Neemo · M 女孩 · 白肌</x:v>
       </x:c>
@@ -16608,7 +16623,7 @@
         <x:v>未披露</x:v>
       </x:c>
       <x:c r="H256" s="17" t="str">
-        <x:v>服装另配</x:v>
+        <x:v>服装另配、换手</x:v>
       </x:c>
       <x:c r="I256" s="18" t="str">
         <x:v>材料未披露</x:v>
@@ -16635,7 +16650,8 @@
         <x:v>本款交付：型号 PCN043-WHT，白肌，头部不附属。
 结构版本：Picco Neemo 为 1:12 可动素体。S、M、D 与胸部规格分别记录，换手接口不默认通用。
 高度与配件限制：官方本款页未给出素体厘米高度；不借用装头整娃的全高。
-销售页面口径：页面库存、再入荷及会员购买限制可能变化；此条是型号资料，不表示现货或代购热度排名。</x:v>
+销售页面口径：页面库存、再入荷及会员购买限制可能变化；此条是型号资料，不表示现货或代购热度排名。
+换手与配件：官方为 S／M 系列列出 PCA012（A）、PCA013（B） 换手，另有 PCA011 关节套件与 PCA010 首关节。配件另售；D 和 P 的换手另外列型，不默认通用。</x:v>
       </x:c>
       <x:c r="Q256" s="11" t="str">
         <x:v>未取得产品对应证据</x:v>
@@ -16650,7 +16666,7 @@
         <x:v>https://www.azone-int.co.jp/azonet/item/4573199841564</x:v>
       </x:c>
     </x:row>
-    <x:row r="257" ht="110" customHeight="1">
+    <x:row r="257" ht="150" customHeight="1">
       <x:c r="A257" s="11" t="str">
         <x:v>Picco Neemo · S 女孩 LL 胸 · 白肌</x:v>
       </x:c>
@@ -16671,7 +16687,7 @@
         <x:v>未披露</x:v>
       </x:c>
       <x:c r="H257" s="17" t="str">
-        <x:v>服装另配</x:v>
+        <x:v>服装另配、换手</x:v>
       </x:c>
       <x:c r="I257" s="18" t="str">
         <x:v>材料未披露</x:v>
@@ -16698,7 +16714,8 @@
         <x:v>本款交付：型号 PCN041-WHT，白肌，头部不附属。胸部规格 LL。
 结构版本：Picco Neemo 为 1:12 可动素体。S、M、D 与胸部规格分别记录，换手接口不默认通用。
 高度与配件限制：官方本款页未给出素体厘米高度；不借用装头整娃的全高。
-销售页面口径：页面库存、再入荷及会员购买限制可能变化；此条是型号资料，不表示现货或代购热度排名。</x:v>
+销售页面口径：页面库存、再入荷及会员购买限制可能变化；此条是型号资料，不表示现货或代购热度排名。
+换手与配件：官方为 S／M 系列列出 PCA012（A）、PCA013（B） 换手，另有 PCA011 关节套件与 PCA010 首关节。配件另售；D 和 P 的换手另外列型，不默认通用。</x:v>
       </x:c>
       <x:c r="Q257" s="11" t="str">
         <x:v>未取得产品对应证据</x:v>
@@ -16713,7 +16730,7 @@
         <x:v>https://www.azone-int.co.jp/azonet/item/4573199841540</x:v>
       </x:c>
     </x:row>
-    <x:row r="258" ht="110" customHeight="1">
+    <x:row r="258" ht="150" customHeight="1">
       <x:c r="A258" s="11" t="str">
         <x:v>Picco Neemo · S 女孩 3L 胸 · 白肌</x:v>
       </x:c>
@@ -16734,7 +16751,7 @@
         <x:v>未披露</x:v>
       </x:c>
       <x:c r="H258" s="17" t="str">
-        <x:v>服装另配</x:v>
+        <x:v>服装另配、换手</x:v>
       </x:c>
       <x:c r="I258" s="18" t="str">
         <x:v>材料未披露</x:v>
@@ -16761,7 +16778,8 @@
         <x:v>本款交付：型号 PCN042-WHT，白肌，头部不附属。胸部规格 3L。
 结构版本：Picco Neemo 为 1:12 可动素体。S、M、D 与胸部规格分别记录，换手接口不默认通用。
 高度与配件限制：官方本款页未给出素体厘米高度；不借用装头整娃的全高。
-销售页面口径：页面库存、再入荷及会员购买限制可能变化；此条是型号资料，不表示现货或代购热度排名。</x:v>
+销售页面口径：页面库存、再入荷及会员购买限制可能变化；此条是型号资料，不表示现货或代购热度排名。
+换手与配件：官方为 S／M 系列列出 PCA012（A）、PCA013（B） 换手，另有 PCA011 关节套件与 PCA010 首关节。配件另售；D 和 P 的换手另外列型，不默认通用。</x:v>
       </x:c>
       <x:c r="Q258" s="11" t="str">
         <x:v>未取得产品对应证据</x:v>
@@ -16776,7 +16794,7 @@
         <x:v>https://www.azone-int.co.jp/azonet/item/4573199841557</x:v>
       </x:c>
     </x:row>
-    <x:row r="259" ht="110" customHeight="1">
+    <x:row r="259" ht="165" customHeight="1">
       <x:c r="A259" s="11" t="str">
         <x:v>Picco Neemo D · 弟弟 · 白肌</x:v>
       </x:c>
@@ -16797,7 +16815,7 @@
         <x:v>未披露</x:v>
       </x:c>
       <x:c r="H259" s="17" t="str">
-        <x:v>服装另配</x:v>
+        <x:v>服装另配、换手</x:v>
       </x:c>
       <x:c r="I259" s="18" t="str">
         <x:v>材料未披露</x:v>
@@ -16821,10 +16839,11 @@
         <x:v>未披露</x:v>
       </x:c>
       <x:c r="P259" s="11" t="str">
-        <x:v>本款交付：型号 PCN048-WHT，白肌，头部不附属。
-结构版本：Picco Neemo 为 1:12 可动素体。S、M、D 与胸部规格分别记录，换手接口不默认通用。
+        <x:v>本款交付：PCN048-WHT 白肌，附身体与首关节（含已装部分）；头部不附属。2025 年 6 月 27 日发售。
+结构版本：Picco Neemo D 采用较大的手脚；弟弟款比 D 男孩身体更小。不能把 D 与 S／M 或 P 的换手接口默认视为通用。
 高度与配件限制：官方本款页未给出素体厘米高度；不借用装头整娃的全高。
-销售页面口径：页面库存、再入荷及会员购买限制可能变化；此条是型号资料，不表示现货或代购热度排名。</x:v>
+销售页面口径：页面库存、再入荷及会员购买限制可能变化；此条是型号资料，不表示现货或代购热度排名。
+换手与配件：D 系列分别有小手脚、中手脚换手套件。2026 年 8 月起 PCA016／015 改为 PCA017／018，按具体手脚版本选择；本款页未指定两个套件都兼容。D 关节套件 PCA014 另售。</x:v>
       </x:c>
       <x:c r="Q259" s="11" t="str">
         <x:v>未取得产品对应证据</x:v>
@@ -17598,6 +17617,132 @@
       </x:c>
       <x:c r="T271" s="11" t="str">
         <x:v>https://piccodo.official.ec/items/72138227</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="272" ht="123" customHeight="1">
+      <x:c r="A272" s="11" t="str">
+        <x:v>Picco Neemo P · 白肌</x:v>
+      </x:c>
+      <x:c r="B272" s="11" t="str">
+        <x:v>AZONE</x:v>
+      </x:c>
+      <x:c r="C272" s="12" t="str">
+        <x:v>关节可动</x:v>
+      </x:c>
+      <x:c r="D272" s="13" t="str">
+        <x:v>素体成品、头部另配</x:v>
+      </x:c>
+      <x:c r="E272" s="20" t="str">
+        <x:v>比例 1:12</x:v>
+      </x:c>
+      <x:c r="F272" s="21"/>
+      <x:c r="G272" s="16" t="str">
+        <x:v>未披露</x:v>
+      </x:c>
+      <x:c r="H272" s="17" t="str">
+        <x:v>服装另配、换手</x:v>
+      </x:c>
+      <x:c r="I272" s="18" t="str">
+        <x:v>材料未披露</x:v>
+      </x:c>
+      <x:c r="J272" s="19" t="str">
+        <x:v>素体</x:v>
+      </x:c>
+      <x:c r="K272" s="11" t="str">
+        <x:v>ピコニーモP PCN036-WHT</x:v>
+      </x:c>
+      <x:c r="L272" s="11" t="str">
+        <x:v>日本</x:v>
+      </x:c>
+      <x:c r="M272" s="11" t="str">
+        <x:v>未披露</x:v>
+      </x:c>
+      <x:c r="N272" s="11" t="str">
+        <x:v>单独出售的白肌素体；按本款与指定配件来源核对。</x:v>
+      </x:c>
+      <x:c r="O272" s="11" t="str">
+        <x:v>未披露</x:v>
+      </x:c>
+      <x:c r="P272" s="11" t="str">
+        <x:v>本款交付：ピコニーモP PCN036-WHT；头部、衣服另配。
+结构版本：P 是官方所列 Picco Neemo 系列最小规格。P、S／M、D 分别列出配套手型。
+换手与批次：P 系列换手 A：2026 年 8 月起 PCA009 改为 PCA019；白肌对应 WHT。换手另售，不与 S／M、D 的手套件混为一款。
+尺寸与材料：本款公开商品页未列素体厘米高度与材料组成，保留未披露；不借用装头整娃高度或其他素体的材料。</x:v>
+      </x:c>
+      <x:c r="Q272" s="11" t="str">
+        <x:v>未取得产品对应证据</x:v>
+      </x:c>
+      <x:c r="R272" s="11" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="S272" s="11" t="str">
+        <x:v>azone-body-pcn036-wht</x:v>
+      </x:c>
+      <x:c r="T272" s="11" t="str">
+        <x:v>https://www.azone-int.co.jp/azonet/item/4573199840475</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="273" ht="123" customHeight="1">
+      <x:c r="A273" s="11" t="str">
+        <x:v>Q’z BODY · M · C 胸 · 白肌</x:v>
+      </x:c>
+      <x:c r="B273" s="11" t="str">
+        <x:v>AZONE</x:v>
+      </x:c>
+      <x:c r="C273" s="12" t="str">
+        <x:v>关节可动</x:v>
+      </x:c>
+      <x:c r="D273" s="13" t="str">
+        <x:v>素体成品、头部另配</x:v>
+      </x:c>
+      <x:c r="E273" s="20" t="str">
+        <x:v>比例 1:6</x:v>
+      </x:c>
+      <x:c r="F273" s="21"/>
+      <x:c r="G273" s="16" t="str">
+        <x:v>未披露</x:v>
+      </x:c>
+      <x:c r="H273" s="17" t="str">
+        <x:v>服装另配、换手</x:v>
+      </x:c>
+      <x:c r="I273" s="18" t="str">
+        <x:v>材料未披露</x:v>
+      </x:c>
+      <x:c r="J273" s="19" t="str">
+        <x:v>素体</x:v>
+      </x:c>
+      <x:c r="K273" s="11" t="str">
+        <x:v>AZONE Q’z BODY M/Cバスト AOB016-WHT</x:v>
+      </x:c>
+      <x:c r="L273" s="11" t="str">
+        <x:v>日本</x:v>
+      </x:c>
+      <x:c r="M273" s="11" t="str">
+        <x:v>未披露</x:v>
+      </x:c>
+      <x:c r="N273" s="11" t="str">
+        <x:v>单独出售的白肌素体；按本款与指定配件来源核对。</x:v>
+      </x:c>
+      <x:c r="O273" s="11" t="str">
+        <x:v>未披露</x:v>
+      </x:c>
+      <x:c r="P273" s="11" t="str">
+        <x:v>本款交付：AZONE Q’z BODY M/Cバスト AOB016-WHT；头部、衣服另配。
+结构与可动：Q’z 为独立身体系列。官方说明其髋部侧向开合比 Pure Neemo 较小；手腕、膝、脚踝可动，膝旋转后弯曲角度变小。
+换手与操作：专用换手套件 AOB021-WHT 另售，2026 年 8 月起改版内容。手腕须先对齐旋转、弯曲方向；摆腿时握住大腿与身体，避免从脚踝拉动髋关节。
+尺寸与材料：本款公开商品页未列素体厘米高度与材料组成，保留未披露；不借用装头整娃高度或其他素体的材料。</x:v>
+      </x:c>
+      <x:c r="Q273" s="11" t="str">
+        <x:v>未取得产品对应证据</x:v>
+      </x:c>
+      <x:c r="R273" s="11" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="S273" s="11" t="str">
+        <x:v>azone-body-aob016-wht</x:v>
+      </x:c>
+      <x:c r="T273" s="11" t="str">
+        <x:v>https://www.azone-int.co.jp/azonet/item/4573199842639</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -17607,7 +17752,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8e918426ff7472b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R640005e0f3194a94"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18200,7 +18345,7 @@
         <x:v>https://obitsu.co.jp/doll-division/obitsu-body-and-parts/obitsu-body/obitsu-body-22/</x:v>
       </x:c>
       <x:c r="G24" s="11" t="str">
-        <x:v>2026-10-05</x:v>
+        <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="H24" s="11" t="str">
         <x:v>obitsu-22-s</x:v>
@@ -18208,85 +18353,85 @@
     </x:row>
     <x:row r="25" ht="72" customHeight="1">
       <x:c r="A25" s="11" t="str">
-        <x:v>OBITSU 24 cm · S 胸</x:v>
+        <x:v>OBITSU 22 cm · S 胸</x:v>
       </x:c>
       <x:c r="B25" s="11" t="str">
-        <x:v>主来源</x:v>
+        <x:v>补充来源</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
-        <x:v>官方产品页</x:v>
+        <x:v>官方尺寸与配件表</x:v>
       </x:c>
       <x:c r="D25" s="11" t="str">
-        <x:v>24BD-F02N-S / ナチュラル・マットスキン</x:v>
+        <x:v>OBITSU BODY 22：S 胸尺寸与附属件</x:v>
       </x:c>
       <x:c r="E25" s="11" t="str">
-        <x:v>型号、交付形态与商品规格</x:v>
+        <x:v>默认 S 胸的尺寸口径、换手、头部适配器与维护零件限制。</x:v>
       </x:c>
       <x:c r="F25" s="11" t="str">
-        <x:v>https://obitsu.co.jp/doll-division/obitsu-body-and-parts/obitsu-body/obitsu-body-24/</x:v>
+        <x:v>https://obitsu.co.jp/doll-division/body-spec/obitsu-body-22/</x:v>
       </x:c>
       <x:c r="G25" s="11" t="str">
-        <x:v>2026-10-05</x:v>
+        <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="H25" s="11" t="str">
-        <x:v>obitsu-24-s-matte</x:v>
+        <x:v>obitsu-22-s</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="72" customHeight="1">
       <x:c r="A26" s="11" t="str">
-        <x:v>OBITSU 50 cm 素体</x:v>
+        <x:v>OBITSU 22 cm · S 胸</x:v>
       </x:c>
       <x:c r="B26" s="11" t="str">
-        <x:v>主来源</x:v>
+        <x:v>补充来源</x:v>
       </x:c>
       <x:c r="C26" s="11" t="str">
-        <x:v>官方产品页</x:v>
+        <x:v>官方适配 FAQ</x:v>
       </x:c>
       <x:c r="D26" s="11" t="str">
-        <x:v>50BD-F01W-G / ホワイティ</x:v>
+        <x:v>OBITSU：跨厂商适配与关节说明</x:v>
       </x:c>
       <x:c r="E26" s="11" t="str">
-        <x:v>型号、交付形态与商品规格</x:v>
+        <x:v>官方未验证全部第三方头／服装适配；具体连接需核对。</x:v>
       </x:c>
       <x:c r="F26" s="11" t="str">
-        <x:v>https://obitsu.co.jp/doll-division/obitsu-body-and-parts/obitsu-body/obitsubody48-50/</x:v>
+        <x:v>https://obitsu.co.jp/doll-division/faq/</x:v>
       </x:c>
       <x:c r="G26" s="11" t="str">
-        <x:v>2026-10-05</x:v>
+        <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="H26" s="11" t="str">
-        <x:v>obitsu-50-white</x:v>
+        <x:v>obitsu-22-s</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="72" customHeight="1">
       <x:c r="A27" s="11" t="str">
-        <x:v>黏土人偶 · 爱丽丝</x:v>
+        <x:v>OBITSU 22 cm · S 胸</x:v>
       </x:c>
       <x:c r="B27" s="11" t="str">
-        <x:v>主来源</x:v>
+        <x:v>补充来源</x:v>
       </x:c>
       <x:c r="C27" s="11" t="str">
-        <x:v>官方产品页</x:v>
+        <x:v>官方厂商主页</x:v>
       </x:c>
       <x:c r="D27" s="11" t="str">
-        <x:v>Nendoroid Doll Alice</x:v>
+        <x:v>株式会社オビツ製作所</x:v>
       </x:c>
       <x:c r="E27" s="11" t="str">
-        <x:v>型号、交付形态与商品规格</x:v>
+        <x:v>厂商全称与所在地；不替代本款产地标示。</x:v>
       </x:c>
       <x:c r="F27" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/5336/Nendoroid%2BDoll%2BAlice</x:v>
+        <x:v>https://obitsu.co.jp/</x:v>
       </x:c>
       <x:c r="G27" s="11" t="str">
-        <x:v>2026-10-05</x:v>
+        <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="H27" s="11" t="str">
-        <x:v>nendoll-alice</x:v>
+        <x:v>obitsu-22-s</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="72" customHeight="1">
       <x:c r="A28" s="11" t="str">
-        <x:v>黏土人偶 · 男孩素体</x:v>
+        <x:v>OBITSU 24 cm · S 胸</x:v>
       </x:c>
       <x:c r="B28" s="11" t="str">
         <x:v>主来源</x:v>
@@ -18295,102 +18440,102 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D28" s="11" t="str">
-        <x:v>Nendoroid Doll archetype: Boy / Almond Milk</x:v>
+        <x:v>24BD-F02N-S / ナチュラル・マットスキン</x:v>
       </x:c>
       <x:c r="E28" s="11" t="str">
         <x:v>型号、交付形态与商品规格</x:v>
       </x:c>
       <x:c r="F28" s="11" t="str">
-        <x:v>https://www.goodsmile.info/en/product/8679/Nendoroid%2BDoll%2Barchetype%2BBoy%2BAlmond%2BMilk.html</x:v>
+        <x:v>https://obitsu.co.jp/doll-division/obitsu-body-and-parts/obitsu-body/obitsu-body-24/</x:v>
       </x:c>
       <x:c r="G28" s="11" t="str">
-        <x:v>2026-10-05</x:v>
+        <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="H28" s="11" t="str">
-        <x:v>nendoll-archetype-boy</x:v>
+        <x:v>obitsu-24-s-matte</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="72" customHeight="1">
       <x:c r="A29" s="11" t="str">
-        <x:v>Harmonia · 初音未来</x:v>
+        <x:v>OBITSU 24 cm · S 胸</x:v>
       </x:c>
       <x:c r="B29" s="11" t="str">
-        <x:v>主来源</x:v>
+        <x:v>补充来源</x:v>
       </x:c>
       <x:c r="C29" s="11" t="str">
-        <x:v>官方产品页</x:v>
+        <x:v>官方尺寸与配件表</x:v>
       </x:c>
       <x:c r="D29" s="11" t="str">
-        <x:v>Harmonia humming Hatsune Miku</x:v>
+        <x:v>OBITSU BODY 24：S 胸尺寸与附属件</x:v>
       </x:c>
       <x:c r="E29" s="11" t="str">
-        <x:v>型号、交付形态与商品规格</x:v>
+        <x:v>默认 S 胸的尺寸口径、换手、头部适配器与维护零件限制。</x:v>
       </x:c>
       <x:c r="F29" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/9727/Harmonia%2Bhumming%2BHatsune%2BMiku</x:v>
+        <x:v>https://obitsu.co.jp/doll-division/body-spec/obitsu-body-24/</x:v>
       </x:c>
       <x:c r="G29" s="11" t="str">
-        <x:v>2026-10-05</x:v>
+        <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="H29" s="11" t="str">
-        <x:v>harmonia-miku</x:v>
+        <x:v>obitsu-24-s-matte</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="72" customHeight="1">
       <x:c r="A30" s="11" t="str">
-        <x:v>初音 · 第 100 次冒险</x:v>
+        <x:v>OBITSU 24 cm · S 胸</x:v>
       </x:c>
       <x:c r="B30" s="11" t="str">
-        <x:v>主来源</x:v>
+        <x:v>补充来源</x:v>
       </x:c>
       <x:c r="C30" s="11" t="str">
-        <x:v>官方产品页</x:v>
+        <x:v>官方适配 FAQ</x:v>
       </x:c>
       <x:c r="D30" s="11" t="str">
-        <x:v>Nendoroid Hatsune Miku: 100th Adventure Ver.</x:v>
+        <x:v>OBITSU：跨厂商适配与关节说明</x:v>
       </x:c>
       <x:c r="E30" s="11" t="str">
-        <x:v>型号、交付形态与商品规格</x:v>
+        <x:v>官方未验证全部第三方头／服装适配；具体连接需核对。</x:v>
       </x:c>
       <x:c r="F30" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/60607/Nendoroid%2BHatsune%2BMiku%2B100th%2BAdventure%2BVer.</x:v>
+        <x:v>https://obitsu.co.jp/doll-division/faq/</x:v>
       </x:c>
       <x:c r="G30" s="11" t="str">
-        <x:v>2026-10-05</x:v>
+        <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="H30" s="11" t="str">
-        <x:v>nendoroid-miku-adventure</x:v>
+        <x:v>obitsu-24-s-matte</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="72" customHeight="1">
       <x:c r="A31" s="11" t="str">
-        <x:v>figma 初音未来 2.0</x:v>
+        <x:v>OBITSU 24 cm · S 胸</x:v>
       </x:c>
       <x:c r="B31" s="11" t="str">
-        <x:v>主来源</x:v>
+        <x:v>补充来源</x:v>
       </x:c>
       <x:c r="C31" s="11" t="str">
-        <x:v>官方产品页</x:v>
+        <x:v>官方厂商主页</x:v>
       </x:c>
       <x:c r="D31" s="11" t="str">
-        <x:v>figma Hatsune Miku 2.0</x:v>
+        <x:v>株式会社オビツ製作所</x:v>
       </x:c>
       <x:c r="E31" s="11" t="str">
-        <x:v>型号、交付形态与商品规格</x:v>
+        <x:v>厂商全称与所在地；不替代本款产地标示。</x:v>
       </x:c>
       <x:c r="F31" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1818/figma%2BHatsune%2BMiku%2B2.0</x:v>
+        <x:v>https://obitsu.co.jp/</x:v>
       </x:c>
       <x:c r="G31" s="11" t="str">
-        <x:v>2026-10-05</x:v>
+        <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="H31" s="11" t="str">
-        <x:v>figma-miku-2</x:v>
+        <x:v>obitsu-24-s-matte</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="72" customHeight="1">
       <x:c r="A32" s="11" t="str">
-        <x:v>THE BATMAN · One:12</x:v>
+        <x:v>OBITSU 50 cm 素体</x:v>
       </x:c>
       <x:c r="B32" s="11" t="str">
         <x:v>主来源</x:v>
@@ -18399,24 +18544,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D32" s="11" t="str">
-        <x:v>One:12 Collective The Batman</x:v>
+        <x:v>50BD-F01W-G / ホワイティ</x:v>
       </x:c>
       <x:c r="E32" s="11" t="str">
         <x:v>型号、交付形态与商品规格</x:v>
       </x:c>
       <x:c r="F32" s="11" t="str">
-        <x:v>https://www.mezcotoyz.com/one-12-collective-the-batman</x:v>
+        <x:v>https://obitsu.co.jp/doll-division/obitsu-body-and-parts/obitsu-body/obitsubody48-50/</x:v>
       </x:c>
       <x:c r="G32" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H32" s="11" t="str">
-        <x:v>mezco-the-batman</x:v>
+        <x:v>obitsu-50-white</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="72" customHeight="1">
       <x:c r="A33" s="11" t="str">
-        <x:v>孙悟空 · BEST SELECTION</x:v>
+        <x:v>黏土人偶 · 爱丽丝</x:v>
       </x:c>
       <x:c r="B33" s="11" t="str">
         <x:v>主来源</x:v>
@@ -18425,50 +18570,50 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D33" s="11" t="str">
-        <x:v>TAMASHII NATIONS：悟空 BEST SELECTION</x:v>
+        <x:v>Nendoroid Doll Alice</x:v>
       </x:c>
       <x:c r="E33" s="11" t="str">
-        <x:v>具体版本与发货记录</x:v>
+        <x:v>型号、交付形态与商品规格</x:v>
       </x:c>
       <x:c r="F33" s="11" t="str">
-        <x:v>https://tamashiiweb.com/item/15303/?wovn=zh-CHS</x:v>
+        <x:v>https://www.goodsmile.com/en/product/5336/Nendoroid%2BDoll%2BAlice</x:v>
       </x:c>
       <x:c r="G33" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H33" s="11" t="str">
-        <x:v>shf-goku-best</x:v>
+        <x:v>nendoll-alice</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="72" customHeight="1">
       <x:c r="A34" s="11" t="str">
-        <x:v>孙悟空 · BEST SELECTION</x:v>
+        <x:v>黏土人偶 · 男孩素体</x:v>
       </x:c>
       <x:c r="B34" s="11" t="str">
-        <x:v>补充来源</x:v>
+        <x:v>主来源</x:v>
       </x:c>
       <x:c r="C34" s="11" t="str">
-        <x:v>官方说明书</x:v>
+        <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D34" s="11" t="str">
-        <x:v>本件官方说明书</x:v>
+        <x:v>Nendoroid Doll archetype: Boy / Almond Milk</x:v>
       </x:c>
       <x:c r="E34" s="11" t="str">
-        <x:v>对应本款的脸、手型替换与操作。</x:v>
+        <x:v>型号、交付形态与商品规格</x:v>
       </x:c>
       <x:c r="F34" s="11" t="str">
-        <x:v>https://tamashiiweb.com/storage/images/products/imported/item_0000015303_WcTg8Ibr_300.pdf</x:v>
+        <x:v>https://www.goodsmile.info/en/product/8679/Nendoroid%2BDoll%2Barchetype%2BBoy%2BAlmond%2BMilk.html</x:v>
       </x:c>
       <x:c r="G34" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H34" s="11" t="str">
-        <x:v>shf-goku-best</x:v>
+        <x:v>nendoll-archetype-boy</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="72" customHeight="1">
       <x:c r="A35" s="11" t="str">
-        <x:v>DRESS UP BODY · S</x:v>
+        <x:v>Harmonia · 初音未来</x:v>
       </x:c>
       <x:c r="B35" s="11" t="str">
         <x:v>主来源</x:v>
@@ -18477,24 +18622,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D35" s="11" t="str">
-        <x:v>DRESS UP BODY [S] / JK016</x:v>
+        <x:v>Harmonia humming Hatsune Miku</x:v>
       </x:c>
       <x:c r="E35" s="11" t="str">
         <x:v>型号、交付形态与商品规格</x:v>
       </x:c>
       <x:c r="F35" s="11" t="str">
-        <x:v>https://www.kotobukiya.co.jp/en/product/detail/p4934054030910/</x:v>
+        <x:v>https://www.goodsmile.com/en/product/9727/Harmonia%2Bhumming%2BHatsune%2BMiku</x:v>
       </x:c>
       <x:c r="G35" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H35" s="11" t="str">
-        <x:v>sousai-dress-up-s</x:v>
+        <x:v>harmonia-miku</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="72" customHeight="1">
       <x:c r="A36" s="11" t="str">
-        <x:v>朱罗忍者 · 拼装版</x:v>
+        <x:v>初音 · 第 100 次冒险</x:v>
       </x:c>
       <x:c r="B36" s="11" t="str">
         <x:v>主来源</x:v>
@@ -18503,24 +18648,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D36" s="11" t="str">
-        <x:v>MEGAMI DEVICE ASRA NINJA / KP431X</x:v>
+        <x:v>Nendoroid Hatsune Miku: 100th Adventure Ver.</x:v>
       </x:c>
       <x:c r="E36" s="11" t="str">
         <x:v>型号、交付形态与商品规格</x:v>
       </x:c>
       <x:c r="F36" s="11" t="str">
-        <x:v>https://www.kotobukiya.co.jp/en/product/detail/p4934054063208/</x:v>
+        <x:v>https://www.goodsmile.com/en/product/60607/Nendoroid%2BHatsune%2BMiku%2B100th%2BAdventure%2BVer.</x:v>
       </x:c>
       <x:c r="G36" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H36" s="11" t="str">
-        <x:v>megami-asra-ninja-kit</x:v>
+        <x:v>nendoroid-miku-adventure</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="72" customHeight="1">
       <x:c r="A37" s="11" t="str">
-        <x:v>朱罗忍者 · 静态版</x:v>
+        <x:v>figma 初音未来 2.0</x:v>
       </x:c>
       <x:c r="B37" s="11" t="str">
         <x:v>主来源</x:v>
@@ -18529,24 +18674,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D37" s="11" t="str">
-        <x:v>MEGAMI DEVICE ASRA NINJA / PP956</x:v>
+        <x:v>figma Hatsune Miku 2.0</x:v>
       </x:c>
       <x:c r="E37" s="11" t="str">
         <x:v>型号、交付形态与商品规格</x:v>
       </x:c>
       <x:c r="F37" s="11" t="str">
-        <x:v>https://www.kotobukiya.co.jp/en/product/detail/p4934054032112/</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1818/figma%2BHatsune%2BMiku%2B2.0</x:v>
       </x:c>
       <x:c r="G37" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H37" s="11" t="str">
-        <x:v>megami-asra-ninja-statue</x:v>
+        <x:v>figma-miku-2</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="72" customHeight="1">
       <x:c r="A38" s="11" t="str">
-        <x:v>露米蒂亚 · AR001</x:v>
+        <x:v>THE BATMAN · One:12</x:v>
       </x:c>
       <x:c r="B38" s="11" t="str">
         <x:v>主来源</x:v>
@@ -18555,24 +18700,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D38" s="11" t="str">
-        <x:v>ARCANADEA LUMITEA / AR001</x:v>
+        <x:v>One:12 Collective The Batman</x:v>
       </x:c>
       <x:c r="E38" s="11" t="str">
         <x:v>型号、交付形态与商品规格</x:v>
       </x:c>
       <x:c r="F38" s="11" t="str">
-        <x:v>https://www.kotobukiya.co.jp/en/product/detail/p4934054038190/</x:v>
+        <x:v>https://www.mezcotoyz.com/one-12-collective-the-batman</x:v>
       </x:c>
       <x:c r="G38" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H38" s="11" t="str">
-        <x:v>arcanadea-lumitea</x:v>
+        <x:v>mezco-the-batman</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="72" customHeight="1">
       <x:c r="A39" s="11" t="str">
-        <x:v>きるプラ 结城圆 · 冬服</x:v>
+        <x:v>孙悟空 · BEST SELECTION</x:v>
       </x:c>
       <x:c r="B39" s="11" t="str">
         <x:v>主来源</x:v>
@@ -18581,50 +18726,50 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D39" s="11" t="str">
-        <x:v>KOTOBUKIYA USA：KiruPla Madoka</x:v>
+        <x:v>TAMASHII NATIONS：悟空 BEST SELECTION</x:v>
       </x:c>
       <x:c r="E39" s="11" t="str">
-        <x:v>比例、高度、套装组成与材料</x:v>
+        <x:v>具体版本与发货记录</x:v>
       </x:c>
       <x:c r="F39" s="11" t="str">
-        <x:v>https://kotobukiya-us.com/products/190526079779</x:v>
+        <x:v>https://tamashiiweb.com/item/15303/?wovn=zh-CHS</x:v>
       </x:c>
       <x:c r="G39" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H39" s="11" t="str">
-        <x:v>kirupla-madoka-winter</x:v>
+        <x:v>shf-goku-best</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="72" customHeight="1">
       <x:c r="A40" s="11" t="str">
-        <x:v>きるプラ 结城圆 · 冬服</x:v>
+        <x:v>孙悟空 · BEST SELECTION</x:v>
       </x:c>
       <x:c r="B40" s="11" t="str">
         <x:v>补充来源</x:v>
       </x:c>
       <x:c r="C40" s="11" t="str">
-        <x:v>官方计划记录</x:v>
+        <x:v>官方说明书</x:v>
       </x:c>
       <x:c r="D40" s="11" t="str">
-        <x:v>寿屋日本官方商店：结城圆冬服</x:v>
+        <x:v>本件官方说明书</x:v>
       </x:c>
       <x:c r="E40" s="11" t="str">
-        <x:v>确认计划发售月，不据此推断库存。</x:v>
+        <x:v>对应本款的脸、手型替换与操作。</x:v>
       </x:c>
       <x:c r="F40" s="11" t="str">
-        <x:v>https://shop.kotobukiya.co.jp/shop/g/g4934054088874/</x:v>
+        <x:v>https://tamashiiweb.com/storage/images/products/imported/item_0000015303_WcTg8Ibr_300.pdf</x:v>
       </x:c>
       <x:c r="G40" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H40" s="11" t="str">
-        <x:v>kirupla-madoka-winter</x:v>
+        <x:v>shf-goku-best</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="72" customHeight="1">
       <x:c r="A41" s="11" t="str">
-        <x:v>POP UP PARADE 初音</x:v>
+        <x:v>DRESS UP BODY · S</x:v>
       </x:c>
       <x:c r="B41" s="11" t="str">
         <x:v>主来源</x:v>
@@ -18633,24 +18778,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D41" s="11" t="str">
-        <x:v>POP UP PARADE Hatsune Miku（原版）</x:v>
+        <x:v>DRESS UP BODY [S] / JK016</x:v>
       </x:c>
       <x:c r="E41" s="11" t="str">
         <x:v>型号、交付形态与商品规格</x:v>
       </x:c>
       <x:c r="F41" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/5775/POP%2BUP%2BPARADE%2BHatsune%2BMiku</x:v>
+        <x:v>https://www.kotobukiya.co.jp/en/product/detail/p4934054030910/</x:v>
       </x:c>
       <x:c r="G41" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H41" s="11" t="str">
-        <x:v>pop-miku-original</x:v>
+        <x:v>sousai-dress-up-s</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="72" customHeight="1">
       <x:c r="A42" s="11" t="str">
-        <x:v>POP 初音 · 透明色 L</x:v>
+        <x:v>朱罗忍者 · 拼装版</x:v>
       </x:c>
       <x:c r="B42" s="11" t="str">
         <x:v>主来源</x:v>
@@ -18659,24 +18804,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D42" s="11" t="str">
-        <x:v>POP UP PARADE Hatsune Miku: Because You’re Here — Translucent Color Ver. L Size</x:v>
+        <x:v>MEGAMI DEVICE ASRA NINJA / KP431X</x:v>
       </x:c>
       <x:c r="E42" s="11" t="str">
         <x:v>型号、交付形态与商品规格</x:v>
       </x:c>
       <x:c r="F42" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1137555/POP%2BUP%2BPARADE%2BHatsune%2BMiku%2BBecause%2BYou%2Bre%2BHere%2B-%2BTranslucent%2BColor%2BVer.%2BL%2BSize</x:v>
+        <x:v>https://www.kotobukiya.co.jp/en/product/detail/p4934054063208/</x:v>
       </x:c>
       <x:c r="G42" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H42" s="11" t="str">
-        <x:v>pop-miku-translucent-l</x:v>
+        <x:v>megami-asra-ninja-kit</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="72" customHeight="1">
       <x:c r="A43" s="11" t="str">
-        <x:v>爱丽丝 · 衣装套件</x:v>
+        <x:v>朱罗忍者 · 静态版</x:v>
       </x:c>
       <x:c r="B43" s="11" t="str">
         <x:v>主来源</x:v>
@@ -18685,24 +18830,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D43" s="11" t="str">
-        <x:v>Nendoroid Doll Outfit Set: Alice</x:v>
+        <x:v>MEGAMI DEVICE ASRA NINJA / PP956</x:v>
       </x:c>
       <x:c r="E43" s="11" t="str">
         <x:v>型号、交付形态与商品规格</x:v>
       </x:c>
       <x:c r="F43" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/5338/Nendoroid%2BDoll%2BOutfit%2BSet%2BAlice%2B</x:v>
+        <x:v>https://www.kotobukiya.co.jp/en/product/detail/p4934054032112/</x:v>
       </x:c>
       <x:c r="G43" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H43" s="11" t="str">
-        <x:v>nendoll-alice-outfit</x:v>
+        <x:v>megami-asra-ninja-statue</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="72" customHeight="1">
       <x:c r="A44" s="11" t="str">
-        <x:v>CCSgirl 26SS ruruko PS</x:v>
+        <x:v>露米蒂亚 · AR001</x:v>
       </x:c>
       <x:c r="B44" s="11" t="str">
         <x:v>主来源</x:v>
@@ -18711,24 +18856,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D44" s="11" t="str">
-        <x:v>CCSgirl 26SS ruruko PS</x:v>
+        <x:v>ARCANADEA LUMITEA / AR001</x:v>
       </x:c>
       <x:c r="E44" s="11" t="str">
-        <x:v>本款全高、身体版本、衣装组成及产地分工。</x:v>
+        <x:v>型号、交付形态与商品规格</x:v>
       </x:c>
       <x:c r="F44" s="11" t="str">
-        <x:v>https://www.petworks.co.jp/doll/ruruko/11176/</x:v>
+        <x:v>https://www.kotobukiya.co.jp/en/product/detail/p4934054038190/</x:v>
       </x:c>
       <x:c r="G44" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H44" s="11" t="str">
-        <x:v>ruruko-11176</x:v>
+        <x:v>arcanadea-lumitea</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="72" customHeight="1">
       <x:c r="A45" s="11" t="str">
-        <x:v>タータンバニー ruruko</x:v>
+        <x:v>きるプラ 结城圆 · 冬服</x:v>
       </x:c>
       <x:c r="B45" s="11" t="str">
         <x:v>主来源</x:v>
@@ -18737,50 +18882,50 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D45" s="11" t="str">
-        <x:v>タータンバニー ruruko</x:v>
+        <x:v>KOTOBUKIYA USA：KiruPla Madoka</x:v>
       </x:c>
       <x:c r="E45" s="11" t="str">
-        <x:v>本款全高、身体版本、衣装组成及产地分工。</x:v>
+        <x:v>比例、高度、套装组成与材料</x:v>
       </x:c>
       <x:c r="F45" s="11" t="str">
-        <x:v>https://www.petworks.co.jp/doll/ruruko/11148/</x:v>
+        <x:v>https://kotobukiya-us.com/products/190526079779</x:v>
       </x:c>
       <x:c r="G45" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H45" s="11" t="str">
-        <x:v>ruruko-11148</x:v>
+        <x:v>kirupla-madoka-winter</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="72" customHeight="1">
       <x:c r="A46" s="11" t="str">
-        <x:v>朝霧のruruko PS</x:v>
+        <x:v>きるプラ 结城圆 · 冬服</x:v>
       </x:c>
       <x:c r="B46" s="11" t="str">
-        <x:v>主来源</x:v>
+        <x:v>补充来源</x:v>
       </x:c>
       <x:c r="C46" s="11" t="str">
-        <x:v>官方产品页</x:v>
+        <x:v>官方计划记录</x:v>
       </x:c>
       <x:c r="D46" s="11" t="str">
-        <x:v>朝霧のruruko PS</x:v>
+        <x:v>寿屋日本官方商店：结城圆冬服</x:v>
       </x:c>
       <x:c r="E46" s="11" t="str">
-        <x:v>本款全高、身体版本、衣装组成及产地分工。</x:v>
+        <x:v>确认计划发售月，不据此推断库存。</x:v>
       </x:c>
       <x:c r="F46" s="11" t="str">
-        <x:v>https://www.petworks.co.jp/doll/ruruko/11133/</x:v>
+        <x:v>https://shop.kotobukiya.co.jp/shop/g/g4934054088874/</x:v>
       </x:c>
       <x:c r="G46" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H46" s="11" t="str">
-        <x:v>ruruko-11133</x:v>
+        <x:v>kirupla-madoka-winter</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="72" customHeight="1">
       <x:c r="A47" s="11" t="str">
-        <x:v>Fresh ruruko 26AZ</x:v>
+        <x:v>POP UP PARADE 初音</x:v>
       </x:c>
       <x:c r="B47" s="11" t="str">
         <x:v>主来源</x:v>
@@ -18789,24 +18934,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D47" s="11" t="str">
-        <x:v>Fresh ruruko 26AZ</x:v>
+        <x:v>POP UP PARADE Hatsune Miku（原版）</x:v>
       </x:c>
       <x:c r="E47" s="11" t="str">
-        <x:v>本款全高、身体版本、衣装组成及产地分工。</x:v>
+        <x:v>型号、交付形态与商品规格</x:v>
       </x:c>
       <x:c r="F47" s="11" t="str">
-        <x:v>https://www.petworks.co.jp/doll/ruruko/11121/</x:v>
+        <x:v>https://www.goodsmile.com/en/product/5775/POP%2BUP%2BPARADE%2BHatsune%2BMiku</x:v>
       </x:c>
       <x:c r="G47" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H47" s="11" t="str">
-        <x:v>ruruko-11121</x:v>
+        <x:v>pop-miku-original</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="72" customHeight="1">
       <x:c r="A48" s="11" t="str">
-        <x:v>Fresh ruruko 26HB</x:v>
+        <x:v>POP 初音 · 透明色 L</x:v>
       </x:c>
       <x:c r="B48" s="11" t="str">
         <x:v>主来源</x:v>
@@ -18815,24 +18960,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D48" s="11" t="str">
-        <x:v>Fresh ruruko 26HB</x:v>
+        <x:v>POP UP PARADE Hatsune Miku: Because You’re Here — Translucent Color Ver. L Size</x:v>
       </x:c>
       <x:c r="E48" s="11" t="str">
-        <x:v>本款全高、身体版本、衣装组成及产地分工。</x:v>
+        <x:v>型号、交付形态与商品规格</x:v>
       </x:c>
       <x:c r="F48" s="11" t="str">
-        <x:v>https://www.petworks.co.jp/doll/ruruko/10989/</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1137555/POP%2BUP%2BPARADE%2BHatsune%2BMiku%2BBecause%2BYou%2Bre%2BHere%2B-%2BTranslucent%2BColor%2BVer.%2BL%2BSize</x:v>
       </x:c>
       <x:c r="G48" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H48" s="11" t="str">
-        <x:v>ruruko-10989</x:v>
+        <x:v>pop-miku-translucent-l</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="72" customHeight="1">
       <x:c r="A49" s="11" t="str">
-        <x:v>朝霧のruruko</x:v>
+        <x:v>爱丽丝 · 衣装套件</x:v>
       </x:c>
       <x:c r="B49" s="11" t="str">
         <x:v>主来源</x:v>
@@ -18841,24 +18986,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D49" s="11" t="str">
-        <x:v>朝霧のruruko</x:v>
+        <x:v>Nendoroid Doll Outfit Set: Alice</x:v>
       </x:c>
       <x:c r="E49" s="11" t="str">
-        <x:v>本款全高、身体版本、衣装组成及产地分工。</x:v>
+        <x:v>型号、交付形态与商品规格</x:v>
       </x:c>
       <x:c r="F49" s="11" t="str">
-        <x:v>https://www.petworks.co.jp/doll/ruruko/10899/</x:v>
+        <x:v>https://www.goodsmile.com/en/product/5338/Nendoroid%2BDoll%2BOutfit%2BSet%2BAlice%2B</x:v>
       </x:c>
       <x:c r="G49" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H49" s="11" t="str">
-        <x:v>ruruko-10899</x:v>
+        <x:v>nendoll-alice-outfit</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="72" customHeight="1">
       <x:c r="A50" s="11" t="str">
-        <x:v>CCSgirl 26干支 ruruko 午 PS</x:v>
+        <x:v>CCSgirl 26SS ruruko PS</x:v>
       </x:c>
       <x:c r="B50" s="11" t="str">
         <x:v>主来源</x:v>
@@ -18867,24 +19012,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D50" s="11" t="str">
-        <x:v>CCSgirl 26干支 ruruko 午 PS</x:v>
+        <x:v>CCSgirl 26SS ruruko PS</x:v>
       </x:c>
       <x:c r="E50" s="11" t="str">
         <x:v>本款全高、身体版本、衣装组成及产地分工。</x:v>
       </x:c>
       <x:c r="F50" s="11" t="str">
-        <x:v>https://www.petworks.co.jp/doll/ruruko/10439/</x:v>
+        <x:v>https://www.petworks.co.jp/doll/ruruko/11176/</x:v>
       </x:c>
       <x:c r="G50" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H50" s="11" t="str">
-        <x:v>ruruko-10439</x:v>
+        <x:v>ruruko-11176</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="72" customHeight="1">
       <x:c r="A51" s="11" t="str">
-        <x:v>ruruko ae［mimi décor］</x:v>
+        <x:v>タータンバニー ruruko</x:v>
       </x:c>
       <x:c r="B51" s="11" t="str">
         <x:v>主来源</x:v>
@@ -18893,24 +19038,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D51" s="11" t="str">
-        <x:v>ruruko ae［mimi décor］</x:v>
+        <x:v>タータンバニー ruruko</x:v>
       </x:c>
       <x:c r="E51" s="11" t="str">
         <x:v>本款全高、身体版本、衣装组成及产地分工。</x:v>
       </x:c>
       <x:c r="F51" s="11" t="str">
-        <x:v>https://www.petworks.co.jp/doll/ruruko/10499/</x:v>
+        <x:v>https://www.petworks.co.jp/doll/ruruko/11148/</x:v>
       </x:c>
       <x:c r="G51" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H51" s="11" t="str">
-        <x:v>ruruko-10499</x:v>
+        <x:v>ruruko-11148</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="72" customHeight="1">
       <x:c r="A52" s="11" t="str">
-        <x:v>ruruko ae［Candy Stripper］</x:v>
+        <x:v>朝霧のruruko PS</x:v>
       </x:c>
       <x:c r="B52" s="11" t="str">
         <x:v>主来源</x:v>
@@ -18919,24 +19064,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D52" s="11" t="str">
-        <x:v>ruruko ae［Candy Stripper］</x:v>
+        <x:v>朝霧のruruko PS</x:v>
       </x:c>
       <x:c r="E52" s="11" t="str">
         <x:v>本款全高、身体版本、衣装组成及产地分工。</x:v>
       </x:c>
       <x:c r="F52" s="11" t="str">
-        <x:v>https://www.petworks.co.jp/doll/ruruko/10495/</x:v>
+        <x:v>https://www.petworks.co.jp/doll/ruruko/11133/</x:v>
       </x:c>
       <x:c r="G52" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H52" s="11" t="str">
-        <x:v>ruruko-10495</x:v>
+        <x:v>ruruko-11133</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="72" customHeight="1">
       <x:c r="A53" s="11" t="str">
-        <x:v>CCSgirl 26SS ruruko</x:v>
+        <x:v>Fresh ruruko 26AZ</x:v>
       </x:c>
       <x:c r="B53" s="11" t="str">
         <x:v>主来源</x:v>
@@ -18945,24 +19090,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D53" s="11" t="str">
-        <x:v>CCSgirl 26SS ruruko</x:v>
+        <x:v>Fresh ruruko 26AZ</x:v>
       </x:c>
       <x:c r="E53" s="11" t="str">
         <x:v>本款全高、身体版本、衣装组成及产地分工。</x:v>
       </x:c>
       <x:c r="F53" s="11" t="str">
-        <x:v>https://www.petworks.co.jp/doll/ruruko/10354/</x:v>
+        <x:v>https://www.petworks.co.jp/doll/ruruko/11121/</x:v>
       </x:c>
       <x:c r="G53" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H53" s="11" t="str">
-        <x:v>ruruko-10354</x:v>
+        <x:v>ruruko-11121</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="72" customHeight="1">
       <x:c r="A54" s="11" t="str">
-        <x:v>Fresh ruruko 2603</x:v>
+        <x:v>Fresh ruruko 26HB</x:v>
       </x:c>
       <x:c r="B54" s="11" t="str">
         <x:v>主来源</x:v>
@@ -18971,24 +19116,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D54" s="11" t="str">
-        <x:v>Fresh ruruko 2603</x:v>
+        <x:v>Fresh ruruko 26HB</x:v>
       </x:c>
       <x:c r="E54" s="11" t="str">
         <x:v>本款全高、身体版本、衣装组成及产地分工。</x:v>
       </x:c>
       <x:c r="F54" s="11" t="str">
-        <x:v>https://www.petworks.co.jp/doll/ruruko/10352/</x:v>
+        <x:v>https://www.petworks.co.jp/doll/ruruko/10989/</x:v>
       </x:c>
       <x:c r="G54" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H54" s="11" t="str">
-        <x:v>ruruko-10352</x:v>
+        <x:v>ruruko-10989</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="72" customHeight="1">
       <x:c r="A55" s="11" t="str">
-        <x:v>CCSgirl 26干支 ruruko 午</x:v>
+        <x:v>朝霧のruruko</x:v>
       </x:c>
       <x:c r="B55" s="11" t="str">
         <x:v>主来源</x:v>
@@ -18997,24 +19142,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D55" s="11" t="str">
-        <x:v>CCSgirl 26干支 ruruko 午</x:v>
+        <x:v>朝霧のruruko</x:v>
       </x:c>
       <x:c r="E55" s="11" t="str">
         <x:v>本款全高、身体版本、衣装组成及产地分工。</x:v>
       </x:c>
       <x:c r="F55" s="11" t="str">
-        <x:v>https://www.petworks.co.jp/doll/ruruko/10147/</x:v>
+        <x:v>https://www.petworks.co.jp/doll/ruruko/10899/</x:v>
       </x:c>
       <x:c r="G55" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H55" s="11" t="str">
-        <x:v>ruruko-10147</x:v>
+        <x:v>ruruko-10899</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="72" customHeight="1">
       <x:c r="A56" s="11" t="str">
-        <x:v>CCSgirl 26VDAY ruruko</x:v>
+        <x:v>CCSgirl 26干支 ruruko 午 PS</x:v>
       </x:c>
       <x:c r="B56" s="11" t="str">
         <x:v>主来源</x:v>
@@ -19023,24 +19168,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D56" s="11" t="str">
-        <x:v>CCSgirl 26VDAY ruruko</x:v>
+        <x:v>CCSgirl 26干支 ruruko 午 PS</x:v>
       </x:c>
       <x:c r="E56" s="11" t="str">
         <x:v>本款全高、身体版本、衣装组成及产地分工。</x:v>
       </x:c>
       <x:c r="F56" s="11" t="str">
-        <x:v>https://www.petworks.co.jp/doll/ruruko/9994/</x:v>
+        <x:v>https://www.petworks.co.jp/doll/ruruko/10439/</x:v>
       </x:c>
       <x:c r="G56" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H56" s="11" t="str">
-        <x:v>ruruko-9994</x:v>
+        <x:v>ruruko-10439</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="72" customHeight="1">
       <x:c r="A57" s="11" t="str">
-        <x:v>Fresh ruruko 2512 PS</x:v>
+        <x:v>ruruko ae［mimi décor］</x:v>
       </x:c>
       <x:c r="B57" s="11" t="str">
         <x:v>主来源</x:v>
@@ -19049,24 +19194,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D57" s="11" t="str">
-        <x:v>Fresh ruruko 2512 PS</x:v>
+        <x:v>ruruko ae［mimi décor］</x:v>
       </x:c>
       <x:c r="E57" s="11" t="str">
         <x:v>本款全高、身体版本、衣装组成及产地分工。</x:v>
       </x:c>
       <x:c r="F57" s="11" t="str">
-        <x:v>https://www.petworks.co.jp/doll/ruruko/9937/</x:v>
+        <x:v>https://www.petworks.co.jp/doll/ruruko/10499/</x:v>
       </x:c>
       <x:c r="G57" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H57" s="11" t="str">
-        <x:v>ruruko-9937</x:v>
+        <x:v>ruruko-10499</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="72" customHeight="1">
       <x:c r="A58" s="11" t="str">
-        <x:v>屋根裏のruruko F.L.C. ver.</x:v>
+        <x:v>ruruko ae［Candy Stripper］</x:v>
       </x:c>
       <x:c r="B58" s="11" t="str">
         <x:v>主来源</x:v>
@@ -19075,24 +19220,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D58" s="11" t="str">
-        <x:v>屋根裏のruruko F.L.C. ver.</x:v>
+        <x:v>ruruko ae［Candy Stripper］</x:v>
       </x:c>
       <x:c r="E58" s="11" t="str">
         <x:v>本款全高、身体版本、衣装组成及产地分工。</x:v>
       </x:c>
       <x:c r="F58" s="11" t="str">
-        <x:v>https://www.petworks.co.jp/doll/ruruko/9736/</x:v>
+        <x:v>https://www.petworks.co.jp/doll/ruruko/10495/</x:v>
       </x:c>
       <x:c r="G58" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H58" s="11" t="str">
-        <x:v>ruruko-9736</x:v>
+        <x:v>ruruko-10495</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="72" customHeight="1">
       <x:c r="A59" s="11" t="str">
-        <x:v>りんご園のruruko F.L.C. ver.</x:v>
+        <x:v>CCSgirl 26SS ruruko</x:v>
       </x:c>
       <x:c r="B59" s="11" t="str">
         <x:v>主来源</x:v>
@@ -19101,24 +19246,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D59" s="11" t="str">
-        <x:v>りんご園のruruko F.L.C. ver.</x:v>
+        <x:v>CCSgirl 26SS ruruko</x:v>
       </x:c>
       <x:c r="E59" s="11" t="str">
         <x:v>本款全高、身体版本、衣装组成及产地分工。</x:v>
       </x:c>
       <x:c r="F59" s="11" t="str">
-        <x:v>https://www.petworks.co.jp/doll/ruruko/9738/</x:v>
+        <x:v>https://www.petworks.co.jp/doll/ruruko/10354/</x:v>
       </x:c>
       <x:c r="G59" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H59" s="11" t="str">
-        <x:v>ruruko-9738</x:v>
+        <x:v>ruruko-10354</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="72" customHeight="1">
       <x:c r="A60" s="11" t="str">
-        <x:v>十夜の夢 ruruko すみれ Azone Ex. bk</x:v>
+        <x:v>Fresh ruruko 2603</x:v>
       </x:c>
       <x:c r="B60" s="11" t="str">
         <x:v>主来源</x:v>
@@ -19127,24 +19272,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D60" s="11" t="str">
-        <x:v>十夜の夢 ruruko すみれ Azone Ex. bk</x:v>
+        <x:v>Fresh ruruko 2603</x:v>
       </x:c>
       <x:c r="E60" s="11" t="str">
         <x:v>本款全高、身体版本、衣装组成及产地分工。</x:v>
       </x:c>
       <x:c r="F60" s="11" t="str">
-        <x:v>https://www.petworks.co.jp/doll/ruruko/9754/</x:v>
+        <x:v>https://www.petworks.co.jp/doll/ruruko/10352/</x:v>
       </x:c>
       <x:c r="G60" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H60" s="11" t="str">
-        <x:v>ruruko-9754</x:v>
+        <x:v>ruruko-10352</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="72" customHeight="1">
       <x:c r="A61" s="11" t="str">
-        <x:v>十夜の夢 ruruko すみれ Azone Ex. wh</x:v>
+        <x:v>CCSgirl 26干支 ruruko 午</x:v>
       </x:c>
       <x:c r="B61" s="11" t="str">
         <x:v>主来源</x:v>
@@ -19153,24 +19298,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D61" s="11" t="str">
-        <x:v>十夜の夢 ruruko すみれ Azone Ex. wh</x:v>
+        <x:v>CCSgirl 26干支 ruruko 午</x:v>
       </x:c>
       <x:c r="E61" s="11" t="str">
         <x:v>本款全高、身体版本、衣装组成及产地分工。</x:v>
       </x:c>
       <x:c r="F61" s="11" t="str">
-        <x:v>https://www.petworks.co.jp/doll/ruruko/9758/</x:v>
+        <x:v>https://www.petworks.co.jp/doll/ruruko/10147/</x:v>
       </x:c>
       <x:c r="G61" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H61" s="11" t="str">
-        <x:v>ruruko-9758</x:v>
+        <x:v>ruruko-10147</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="72" customHeight="1">
       <x:c r="A62" s="11" t="str">
-        <x:v>Fresh ruruko 2507</x:v>
+        <x:v>CCSgirl 26VDAY ruruko</x:v>
       </x:c>
       <x:c r="B62" s="11" t="str">
         <x:v>主来源</x:v>
@@ -19179,24 +19324,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D62" s="11" t="str">
-        <x:v>Fresh ruruko 2507</x:v>
+        <x:v>CCSgirl 26VDAY ruruko</x:v>
       </x:c>
       <x:c r="E62" s="11" t="str">
         <x:v>本款全高、身体版本、衣装组成及产地分工。</x:v>
       </x:c>
       <x:c r="F62" s="11" t="str">
-        <x:v>https://www.petworks.co.jp/doll/ruruko/9390/</x:v>
+        <x:v>https://www.petworks.co.jp/doll/ruruko/9994/</x:v>
       </x:c>
       <x:c r="G62" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H62" s="11" t="str">
-        <x:v>ruruko-9390</x:v>
+        <x:v>ruruko-9994</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="72" customHeight="1">
       <x:c r="A63" s="11" t="str">
-        <x:v>CCSgirl 25SS ruruko PS</x:v>
+        <x:v>Fresh ruruko 2512 PS</x:v>
       </x:c>
       <x:c r="B63" s="11" t="str">
         <x:v>主来源</x:v>
@@ -19205,24 +19350,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D63" s="11" t="str">
-        <x:v>CCSgirl 25SS ruruko PS</x:v>
+        <x:v>Fresh ruruko 2512 PS</x:v>
       </x:c>
       <x:c r="E63" s="11" t="str">
         <x:v>本款全高、身体版本、衣装组成及产地分工。</x:v>
       </x:c>
       <x:c r="F63" s="11" t="str">
-        <x:v>https://www.petworks.co.jp/doll/ruruko/9379/</x:v>
+        <x:v>https://www.petworks.co.jp/doll/ruruko/9937/</x:v>
       </x:c>
       <x:c r="G63" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H63" s="11" t="str">
-        <x:v>ruruko-9379</x:v>
+        <x:v>ruruko-9937</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="72" customHeight="1">
       <x:c r="A64" s="11" t="str">
-        <x:v>Fresh ruruko 25HB</x:v>
+        <x:v>屋根裏のruruko F.L.C. ver.</x:v>
       </x:c>
       <x:c r="B64" s="11" t="str">
         <x:v>主来源</x:v>
@@ -19231,24 +19376,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D64" s="11" t="str">
-        <x:v>Fresh ruruko 25HB</x:v>
+        <x:v>屋根裏のruruko F.L.C. ver.</x:v>
       </x:c>
       <x:c r="E64" s="11" t="str">
         <x:v>本款全高、身体版本、衣装组成及产地分工。</x:v>
       </x:c>
       <x:c r="F64" s="11" t="str">
-        <x:v>https://www.petworks.co.jp/doll/ruruko/9377/</x:v>
+        <x:v>https://www.petworks.co.jp/doll/ruruko/9736/</x:v>
       </x:c>
       <x:c r="G64" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H64" s="11" t="str">
-        <x:v>ruruko-9377</x:v>
+        <x:v>ruruko-9736</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="72" customHeight="1">
       <x:c r="A65" s="11" t="str">
-        <x:v>CCSgirl 24AW ruruko PS</x:v>
+        <x:v>りんご園のruruko F.L.C. ver.</x:v>
       </x:c>
       <x:c r="B65" s="11" t="str">
         <x:v>主来源</x:v>
@@ -19257,24 +19402,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D65" s="11" t="str">
-        <x:v>CCSgirl 24AW ruruko PS</x:v>
+        <x:v>りんご園のruruko F.L.C. ver.</x:v>
       </x:c>
       <x:c r="E65" s="11" t="str">
         <x:v>本款全高、身体版本、衣装组成及产地分工。</x:v>
       </x:c>
       <x:c r="F65" s="11" t="str">
-        <x:v>https://www.petworks.co.jp/doll/ruruko/9198/</x:v>
+        <x:v>https://www.petworks.co.jp/doll/ruruko/9738/</x:v>
       </x:c>
       <x:c r="G65" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H65" s="11" t="str">
-        <x:v>ruruko-9198</x:v>
+        <x:v>ruruko-9738</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="72" customHeight="1">
       <x:c r="A66" s="11" t="str">
-        <x:v>イースターバニー ruruko boy PS</x:v>
+        <x:v>十夜の夢 ruruko すみれ Azone Ex. bk</x:v>
       </x:c>
       <x:c r="B66" s="11" t="str">
         <x:v>主来源</x:v>
@@ -19283,24 +19428,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D66" s="11" t="str">
-        <x:v>イースターバニー ruruko boy PS</x:v>
+        <x:v>十夜の夢 ruruko すみれ Azone Ex. bk</x:v>
       </x:c>
       <x:c r="E66" s="11" t="str">
         <x:v>本款全高、身体版本、衣装组成及产地分工。</x:v>
       </x:c>
       <x:c r="F66" s="11" t="str">
-        <x:v>https://www.petworks.co.jp/doll/ruruko/9124/</x:v>
+        <x:v>https://www.petworks.co.jp/doll/ruruko/9754/</x:v>
       </x:c>
       <x:c r="G66" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H66" s="11" t="str">
-        <x:v>ruruko-9124</x:v>
+        <x:v>ruruko-9754</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="72" customHeight="1">
       <x:c r="A67" s="11" t="str">
-        <x:v>イースターバニー ruruko girl PS</x:v>
+        <x:v>十夜の夢 ruruko すみれ Azone Ex. wh</x:v>
       </x:c>
       <x:c r="B67" s="11" t="str">
         <x:v>主来源</x:v>
@@ -19309,24 +19454,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D67" s="11" t="str">
-        <x:v>イースターバニー ruruko girl PS</x:v>
+        <x:v>十夜の夢 ruruko すみれ Azone Ex. wh</x:v>
       </x:c>
       <x:c r="E67" s="11" t="str">
         <x:v>本款全高、身体版本、衣装组成及产地分工。</x:v>
       </x:c>
       <x:c r="F67" s="11" t="str">
-        <x:v>https://www.petworks.co.jp/doll/ruruko/9127/</x:v>
+        <x:v>https://www.petworks.co.jp/doll/ruruko/9758/</x:v>
       </x:c>
       <x:c r="G67" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H67" s="11" t="str">
-        <x:v>ruruko-9127</x:v>
+        <x:v>ruruko-9758</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="72" customHeight="1">
       <x:c r="A68" s="11" t="str">
-        <x:v>CCSgirl 25SS ruruko</x:v>
+        <x:v>Fresh ruruko 2507</x:v>
       </x:c>
       <x:c r="B68" s="11" t="str">
         <x:v>主来源</x:v>
@@ -19335,180 +19480,180 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D68" s="11" t="str">
-        <x:v>CCSgirl 25SS ruruko</x:v>
+        <x:v>Fresh ruruko 2507</x:v>
       </x:c>
       <x:c r="E68" s="11" t="str">
         <x:v>本款全高、身体版本、衣装组成及产地分工。</x:v>
       </x:c>
       <x:c r="F68" s="11" t="str">
-        <x:v>https://www.petworks.co.jp/doll/ruruko/9028/</x:v>
+        <x:v>https://www.petworks.co.jp/doll/ruruko/9390/</x:v>
       </x:c>
       <x:c r="G68" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H68" s="11" t="str">
-        <x:v>ruruko-9028</x:v>
+        <x:v>ruruko-9390</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="72" customHeight="1">
       <x:c r="A69" s="11" t="str">
-        <x:v>Phantom · 裸娃</x:v>
+        <x:v>CCSgirl 25SS ruruko PS</x:v>
       </x:c>
       <x:c r="B69" s="11" t="str">
         <x:v>主来源</x:v>
       </x:c>
       <x:c r="C69" s="11" t="str">
-        <x:v>官方商品选项页</x:v>
+        <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D69" s="11" t="str">
-        <x:v>【Pre-sale】DollZone Phantom 1/3 Doll Full Set/nude doll/head Presale SD Doll  Spherical joint Dolls</x:v>
+        <x:v>CCSgirl 25SS ruruko PS</x:v>
       </x:c>
       <x:c r="E69" s="11" t="str">
-        <x:v>具体名称、比例、标题标称高度及裸娃／身体销售选项；图版参数尚待核对。</x:v>
+        <x:v>本款全高、身体版本、衣装组成及产地分工。</x:v>
       </x:c>
       <x:c r="F69" s="11" t="str">
-        <x:v>https://doll-zone.com/products/pre-saledollzone-phantom-1-3-doll-full-set-nude-doll-head-presale-sd-doll-spherical-joint-dolls</x:v>
+        <x:v>https://www.petworks.co.jp/doll/ruruko/9379/</x:v>
       </x:c>
       <x:c r="G69" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H69" s="11" t="str">
-        <x:v>dollzone-1-3-doll-pre-saledollzone-phantom-1-3-doll-full-set-nude-doll-head-presale-sd-doll-spherical-joint-</x:v>
+        <x:v>ruruko-9379</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="72" customHeight="1">
       <x:c r="A70" s="11" t="str">
-        <x:v>SUN · 裸娃</x:v>
+        <x:v>Fresh ruruko 25HB</x:v>
       </x:c>
       <x:c r="B70" s="11" t="str">
         <x:v>主来源</x:v>
       </x:c>
       <x:c r="C70" s="11" t="str">
-        <x:v>官方商品选项页</x:v>
+        <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D70" s="11" t="str">
-        <x:v>【Pre-sale】DollZone SUN 1/3 Doll Full Set/nude doll/head Presale SD Doll  Spherical joint Dolls</x:v>
+        <x:v>Fresh ruruko 25HB</x:v>
       </x:c>
       <x:c r="E70" s="11" t="str">
-        <x:v>具体名称、比例、标题标称高度及裸娃／身体销售选项；图版参数尚待核对。</x:v>
+        <x:v>本款全高、身体版本、衣装组成及产地分工。</x:v>
       </x:c>
       <x:c r="F70" s="11" t="str">
-        <x:v>https://doll-zone.com/products/pre-saledollzone-sun-1-3-doll-full-set-nude-doll-head-presale-sd-doll-spherical-joint-dolls</x:v>
+        <x:v>https://www.petworks.co.jp/doll/ruruko/9377/</x:v>
       </x:c>
       <x:c r="G70" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H70" s="11" t="str">
-        <x:v>dollzone-1-3-doll-pre-saledollzone-sun-1-3-doll-full-set-nude-doll-head-presale-sd-doll-spherical-joint-doll</x:v>
+        <x:v>ruruko-9377</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="72" customHeight="1">
       <x:c r="A71" s="11" t="str">
-        <x:v>Gorgon · 裸娃</x:v>
+        <x:v>CCSgirl 24AW ruruko PS</x:v>
       </x:c>
       <x:c r="B71" s="11" t="str">
         <x:v>主来源</x:v>
       </x:c>
       <x:c r="C71" s="11" t="str">
-        <x:v>官方商品选项页</x:v>
+        <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D71" s="11" t="str">
-        <x:v>【Pre-sale】DollZone Gorgon 1/3 Doll Full Set/nude doll/head Presale SD Doll  Spherical joint Dolls</x:v>
+        <x:v>CCSgirl 24AW ruruko PS</x:v>
       </x:c>
       <x:c r="E71" s="11" t="str">
-        <x:v>具体名称、比例、标题标称高度及裸娃／身体销售选项；图版参数尚待核对。</x:v>
+        <x:v>本款全高、身体版本、衣装组成及产地分工。</x:v>
       </x:c>
       <x:c r="F71" s="11" t="str">
-        <x:v>https://doll-zone.com/products/pre-saledollzone-gorgon-1-3-doll-full-set-nude-doll-head-presale-sd-doll-spherical-joint-dolls</x:v>
+        <x:v>https://www.petworks.co.jp/doll/ruruko/9198/</x:v>
       </x:c>
       <x:c r="G71" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H71" s="11" t="str">
-        <x:v>dollzone-1-3-doll-pre-saledollzone-gorgon-1-3-doll-full-set-nude-doll-head-presale-sd-doll-spherical-joint-d</x:v>
+        <x:v>ruruko-9198</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="72" customHeight="1">
       <x:c r="A72" s="11" t="str">
-        <x:v>Rock · 裸娃</x:v>
+        <x:v>イースターバニー ruruko boy PS</x:v>
       </x:c>
       <x:c r="B72" s="11" t="str">
         <x:v>主来源</x:v>
       </x:c>
       <x:c r="C72" s="11" t="str">
-        <x:v>官方商品选项页</x:v>
+        <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D72" s="11" t="str">
-        <x:v>【Pre-sale】DollZone Rock 1/3 Cooperation Description Doll Full Set/nude doll  Presale SD Doll 75cm Spherical joint Dolls</x:v>
+        <x:v>イースターバニー ruruko boy PS</x:v>
       </x:c>
       <x:c r="E72" s="11" t="str">
-        <x:v>具体名称、比例、标题标称高度及裸娃／身体销售选项；图版参数尚待核对。</x:v>
+        <x:v>本款全高、身体版本、衣装组成及产地分工。</x:v>
       </x:c>
       <x:c r="F72" s="11" t="str">
-        <x:v>https://doll-zone.com/products/%E3%80%90pre-sale%E3%80%91dollzone-rock-1-3-cooperation-description-doll-full-set-nude-doll-presale-sd-doll-75cm-spherical-joint-dolls</x:v>
+        <x:v>https://www.petworks.co.jp/doll/ruruko/9124/</x:v>
       </x:c>
       <x:c r="G72" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H72" s="11" t="str">
-        <x:v>dollzone-1-3-doll--pre-sale-dollzone-rock-1-3-cooperation-description-doll-full-set-nude-doll-presale-sd-dol</x:v>
+        <x:v>ruruko-9124</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="72" customHeight="1">
       <x:c r="A73" s="11" t="str">
-        <x:v>Light · 裸娃</x:v>
+        <x:v>イースターバニー ruruko girl PS</x:v>
       </x:c>
       <x:c r="B73" s="11" t="str">
         <x:v>主来源</x:v>
       </x:c>
       <x:c r="C73" s="11" t="str">
-        <x:v>官方商品选项页</x:v>
+        <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D73" s="11" t="str">
-        <x:v>【Pre-sale】DollZone Light 1/3 Cooperation Description Doll Full Set Presale SD Doll 73cm Spherical joint Dolls</x:v>
+        <x:v>イースターバニー ruruko girl PS</x:v>
       </x:c>
       <x:c r="E73" s="11" t="str">
-        <x:v>具体名称、比例、标题标称高度及裸娃／身体销售选项；图版参数尚待核对。</x:v>
+        <x:v>本款全高、身体版本、衣装组成及产地分工。</x:v>
       </x:c>
       <x:c r="F73" s="11" t="str">
-        <x:v>https://doll-zone.com/products/%E3%80%90pre-sale%E3%80%91dollzone-light-1-3-cooperation-description-doll-full-set-presale-sd-doll-73cm-spherical-joint-dolls</x:v>
+        <x:v>https://www.petworks.co.jp/doll/ruruko/9127/</x:v>
       </x:c>
       <x:c r="G73" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H73" s="11" t="str">
-        <x:v>dollzone-1-3-doll--pre-sale-dollzone-light-1-3-cooperation-description-doll-full-set-presale-sd-doll-73cm-sp</x:v>
+        <x:v>ruruko-9127</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="72" customHeight="1">
       <x:c r="A74" s="11" t="str">
-        <x:v>Troy · 裸娃</x:v>
+        <x:v>CCSgirl 25SS ruruko</x:v>
       </x:c>
       <x:c r="B74" s="11" t="str">
         <x:v>主来源</x:v>
       </x:c>
       <x:c r="C74" s="11" t="str">
-        <x:v>官方商品选项页</x:v>
+        <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D74" s="11" t="str">
-        <x:v>【Pre-sale】DollZone Troy 1/3 Cooperation Description Doll Full Set/nude doll  Presale SD Doll 73cm Spherical joint Dolls</x:v>
+        <x:v>CCSgirl 25SS ruruko</x:v>
       </x:c>
       <x:c r="E74" s="11" t="str">
-        <x:v>具体名称、比例、标题标称高度及裸娃／身体销售选项；图版参数尚待核对。</x:v>
+        <x:v>本款全高、身体版本、衣装组成及产地分工。</x:v>
       </x:c>
       <x:c r="F74" s="11" t="str">
-        <x:v>https://doll-zone.com/products/%E3%80%90pre-sale%E3%80%91dollzone-troy-1-3-cooperation-description-doll-full-set-nude-doll-presale-sd-doll-73cm-spherical-joint-dolls</x:v>
+        <x:v>https://www.petworks.co.jp/doll/ruruko/9028/</x:v>
       </x:c>
       <x:c r="G74" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H74" s="11" t="str">
-        <x:v>dollzone-1-3-doll--pre-sale-dollzone-troy-1-3-cooperation-description-doll-full-set-nude-doll-presale-sd-dol</x:v>
+        <x:v>ruruko-9028</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="72" customHeight="1">
       <x:c r="A75" s="11" t="str">
-        <x:v>Nona · 裸娃</x:v>
+        <x:v>Phantom · 裸娃</x:v>
       </x:c>
       <x:c r="B75" s="11" t="str">
         <x:v>主来源</x:v>
@@ -19517,24 +19662,24 @@
         <x:v>官方商品选项页</x:v>
       </x:c>
       <x:c r="D75" s="11" t="str">
-        <x:v>【Pre-sale】DollZone Nona 1/3 Cooperation Description Doll Full Set Presale SD Doll 70cm Spherical joint Dolls</x:v>
+        <x:v>【Pre-sale】DollZone Phantom 1/3 Doll Full Set/nude doll/head Presale SD Doll  Spherical joint Dolls</x:v>
       </x:c>
       <x:c r="E75" s="11" t="str">
         <x:v>具体名称、比例、标题标称高度及裸娃／身体销售选项；图版参数尚待核对。</x:v>
       </x:c>
       <x:c r="F75" s="11" t="str">
-        <x:v>https://doll-zone.com/products/%E3%80%90pre-sale%E3%80%91dollzone-nona-1-3-cooperation-description-doll-full-set-presale-sd-doll-70cm-spherical-joint-dolls</x:v>
+        <x:v>https://doll-zone.com/products/pre-saledollzone-phantom-1-3-doll-full-set-nude-doll-head-presale-sd-doll-spherical-joint-dolls</x:v>
       </x:c>
       <x:c r="G75" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H75" s="11" t="str">
-        <x:v>dollzone-1-3-doll--pre-sale-dollzone-nona-1-3-cooperation-description-doll-full-set-presale-sd-doll-70cm-sph</x:v>
+        <x:v>dollzone-1-3-doll-pre-saledollzone-phantom-1-3-doll-full-set-nude-doll-head-presale-sd-doll-spherical-joint-</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="72" customHeight="1">
       <x:c r="A76" s="11" t="str">
-        <x:v>moon · 裸娃</x:v>
+        <x:v>SUN · 裸娃</x:v>
       </x:c>
       <x:c r="B76" s="11" t="str">
         <x:v>主来源</x:v>
@@ -19543,24 +19688,24 @@
         <x:v>官方商品选项页</x:v>
       </x:c>
       <x:c r="D76" s="11" t="str">
-        <x:v>【Pre-sale】DollZone moon 1/3 Cooperation Description Doll Full Set Presale SD Doll 73cm Spherical joint Dolls</x:v>
+        <x:v>【Pre-sale】DollZone SUN 1/3 Doll Full Set/nude doll/head Presale SD Doll  Spherical joint Dolls</x:v>
       </x:c>
       <x:c r="E76" s="11" t="str">
         <x:v>具体名称、比例、标题标称高度及裸娃／身体销售选项；图版参数尚待核对。</x:v>
       </x:c>
       <x:c r="F76" s="11" t="str">
-        <x:v>https://doll-zone.com/products/%E3%80%90pre-sale%E3%80%91dollzone-moon-1-3-cooperation-description-doll-full-set-presale-sd-doll-73cm-spherical-joint-dolls</x:v>
+        <x:v>https://doll-zone.com/products/pre-saledollzone-sun-1-3-doll-full-set-nude-doll-head-presale-sd-doll-spherical-joint-dolls</x:v>
       </x:c>
       <x:c r="G76" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H76" s="11" t="str">
-        <x:v>dollzone-1-3-doll--pre-sale-dollzone-moon-1-3-cooperation-description-doll-full-set-presale-sd-doll-73cm-sph</x:v>
+        <x:v>dollzone-1-3-doll-pre-saledollzone-sun-1-3-doll-full-set-nude-doll-head-presale-sd-doll-spherical-joint-doll</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="72" customHeight="1">
       <x:c r="A77" s="11" t="str">
-        <x:v>75 Gray · 裸娃</x:v>
+        <x:v>Gorgon · 裸娃</x:v>
       </x:c>
       <x:c r="B77" s="11" t="str">
         <x:v>主来源</x:v>
@@ -19569,24 +19714,24 @@
         <x:v>官方商品选项页</x:v>
       </x:c>
       <x:c r="D77" s="11" t="str">
-        <x:v>【Pre-sale】DollZone 75 Gray 1/3 Doll Full Set Presale SD Doll 75cm Spherical joint Dolls</x:v>
+        <x:v>【Pre-sale】DollZone Gorgon 1/3 Doll Full Set/nude doll/head Presale SD Doll  Spherical joint Dolls</x:v>
       </x:c>
       <x:c r="E77" s="11" t="str">
         <x:v>具体名称、比例、标题标称高度及裸娃／身体销售选项；图版参数尚待核对。</x:v>
       </x:c>
       <x:c r="F77" s="11" t="str">
-        <x:v>https://doll-zone.com/products/dollzone-75-gray</x:v>
+        <x:v>https://doll-zone.com/products/pre-saledollzone-gorgon-1-3-doll-full-set-nude-doll-head-presale-sd-doll-spherical-joint-dolls</x:v>
       </x:c>
       <x:c r="G77" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H77" s="11" t="str">
-        <x:v>dollzone-1-3-doll-dollzone-75-gray</x:v>
+        <x:v>dollzone-1-3-doll-pre-saledollzone-gorgon-1-3-doll-full-set-nude-doll-head-presale-sd-doll-spherical-joint-d</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="72" customHeight="1">
       <x:c r="A78" s="11" t="str">
-        <x:v>Evan · 裸娃</x:v>
+        <x:v>Rock · 裸娃</x:v>
       </x:c>
       <x:c r="B78" s="11" t="str">
         <x:v>主来源</x:v>
@@ -19595,24 +19740,24 @@
         <x:v>官方商品选项页</x:v>
       </x:c>
       <x:c r="D78" s="11" t="str">
-        <x:v>【Pre-sale】DollZone Evan 1/3 Doll Full Set Presale SD Doll 75cm Spherical joint Dolls</x:v>
+        <x:v>【Pre-sale】DollZone Rock 1/3 Cooperation Description Doll Full Set/nude doll  Presale SD Doll 75cm Spherical joint Dolls</x:v>
       </x:c>
       <x:c r="E78" s="11" t="str">
         <x:v>具体名称、比例、标题标称高度及裸娃／身体销售选项；图版参数尚待核对。</x:v>
       </x:c>
       <x:c r="F78" s="11" t="str">
-        <x:v>https://doll-zone.com/products/evan</x:v>
+        <x:v>https://doll-zone.com/products/%E3%80%90pre-sale%E3%80%91dollzone-rock-1-3-cooperation-description-doll-full-set-nude-doll-presale-sd-doll-75cm-spherical-joint-dolls</x:v>
       </x:c>
       <x:c r="G78" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H78" s="11" t="str">
-        <x:v>dollzone-1-3-doll-evan</x:v>
+        <x:v>dollzone-1-3-doll--pre-sale-dollzone-rock-1-3-cooperation-description-doll-full-set-nude-doll-presale-sd-dol</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="72" customHeight="1">
       <x:c r="A79" s="11" t="str">
-        <x:v>Rosa · 裸娃</x:v>
+        <x:v>Light · 裸娃</x:v>
       </x:c>
       <x:c r="B79" s="11" t="str">
         <x:v>主来源</x:v>
@@ -19621,24 +19766,24 @@
         <x:v>官方商品选项页</x:v>
       </x:c>
       <x:c r="D79" s="11" t="str">
-        <x:v>【Pre-sale】DollZone Rosa 1/4  Doll Full Set/nude doll/head Presale SD Doll  Spherical joint Dolls</x:v>
+        <x:v>【Pre-sale】DollZone Light 1/3 Cooperation Description Doll Full Set Presale SD Doll 73cm Spherical joint Dolls</x:v>
       </x:c>
       <x:c r="E79" s="11" t="str">
         <x:v>具体名称、比例、标题标称高度及裸娃／身体销售选项；图版参数尚待核对。</x:v>
       </x:c>
       <x:c r="F79" s="11" t="str">
-        <x:v>https://doll-zone.com/products/%E3%80%90pre-sale%E3%80%91dollzone-rosa-1-4-doll-full-set-nude-doll-head-presale-sd-doll-spherical-joint-dolls</x:v>
+        <x:v>https://doll-zone.com/products/%E3%80%90pre-sale%E3%80%91dollzone-light-1-3-cooperation-description-doll-full-set-presale-sd-doll-73cm-spherical-joint-dolls</x:v>
       </x:c>
       <x:c r="G79" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H79" s="11" t="str">
-        <x:v>dollzone-1-4-doll--pre-sale-dollzone-rosa-1-4-doll-full-set-nude-doll-head-presale-sd-doll-spherical-joint-d</x:v>
+        <x:v>dollzone-1-3-doll--pre-sale-dollzone-light-1-3-cooperation-description-doll-full-set-presale-sd-doll-73cm-sp</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="72" customHeight="1">
       <x:c r="A80" s="11" t="str">
-        <x:v>XIAO YI · 裸娃</x:v>
+        <x:v>Troy · 裸娃</x:v>
       </x:c>
       <x:c r="B80" s="11" t="str">
         <x:v>主来源</x:v>
@@ -19647,24 +19792,24 @@
         <x:v>官方商品选项页</x:v>
       </x:c>
       <x:c r="D80" s="11" t="str">
-        <x:v>【Pre-sale】DollZone XIAO YI 1/4 Cooperation Description Doll Full Set/nude doll/head Presale SD Doll 45cm Spherical joint Dolls</x:v>
+        <x:v>【Pre-sale】DollZone Troy 1/3 Cooperation Description Doll Full Set/nude doll  Presale SD Doll 73cm Spherical joint Dolls</x:v>
       </x:c>
       <x:c r="E80" s="11" t="str">
         <x:v>具体名称、比例、标题标称高度及裸娃／身体销售选项；图版参数尚待核对。</x:v>
       </x:c>
       <x:c r="F80" s="11" t="str">
-        <x:v>https://doll-zone.com/products/pre-saledollzone-xiao-yi-1-4-cooperation-description-doll-full-set-nude-doll-head-presale-sd-doll-45cm-spherical-joint-dolls</x:v>
+        <x:v>https://doll-zone.com/products/%E3%80%90pre-sale%E3%80%91dollzone-troy-1-3-cooperation-description-doll-full-set-nude-doll-presale-sd-doll-73cm-spherical-joint-dolls</x:v>
       </x:c>
       <x:c r="G80" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H80" s="11" t="str">
-        <x:v>dollzone-1-4-doll-pre-saledollzone-xiao-yi-1-4-cooperation-description-doll-full-set-nude-doll-head-presale-</x:v>
+        <x:v>dollzone-1-3-doll--pre-sale-dollzone-troy-1-3-cooperation-description-doll-full-set-nude-doll-presale-sd-dol</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="72" customHeight="1">
       <x:c r="A81" s="11" t="str">
-        <x:v>XIAO CHU · 裸娃</x:v>
+        <x:v>Nona · 裸娃</x:v>
       </x:c>
       <x:c r="B81" s="11" t="str">
         <x:v>主来源</x:v>
@@ -19673,24 +19818,24 @@
         <x:v>官方商品选项页</x:v>
       </x:c>
       <x:c r="D81" s="11" t="str">
-        <x:v>【Pre-sale】DollZone XIAO CHU 1/4 Cooperation Description Doll Full Set/nude doll/head Presale SD Doll 45cm Spherical joint Dolls</x:v>
+        <x:v>【Pre-sale】DollZone Nona 1/3 Cooperation Description Doll Full Set Presale SD Doll 70cm Spherical joint Dolls</x:v>
       </x:c>
       <x:c r="E81" s="11" t="str">
         <x:v>具体名称、比例、标题标称高度及裸娃／身体销售选项；图版参数尚待核对。</x:v>
       </x:c>
       <x:c r="F81" s="11" t="str">
-        <x:v>https://doll-zone.com/products/%E3%80%90pre-sale%E3%80%91dollzone-xiao-chu-1-4-cooperation-description-doll-full-set-nude-doll-head-presale-sd-doll-45cm-spherical-joint-dolls</x:v>
+        <x:v>https://doll-zone.com/products/%E3%80%90pre-sale%E3%80%91dollzone-nona-1-3-cooperation-description-doll-full-set-presale-sd-doll-70cm-spherical-joint-dolls</x:v>
       </x:c>
       <x:c r="G81" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H81" s="11" t="str">
-        <x:v>dollzone-1-4-doll--pre-sale-dollzone-xiao-chu-1-4-cooperation-description-doll-full-set-nude-doll-head-presa</x:v>
+        <x:v>dollzone-1-3-doll--pre-sale-dollzone-nona-1-3-cooperation-description-doll-full-set-presale-sd-doll-70cm-sph</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="72" customHeight="1">
       <x:c r="A82" s="11" t="str">
-        <x:v>The world · 裸娃</x:v>
+        <x:v>moon · 裸娃</x:v>
       </x:c>
       <x:c r="B82" s="11" t="str">
         <x:v>主来源</x:v>
@@ -19699,24 +19844,24 @@
         <x:v>官方商品选项页</x:v>
       </x:c>
       <x:c r="D82" s="11" t="str">
-        <x:v>【Pre-sale】DollZone The world 1/4 Doll Full Set/nude doll/head Presale SD Doll  Spherical joint Dolls</x:v>
+        <x:v>【Pre-sale】DollZone moon 1/3 Cooperation Description Doll Full Set Presale SD Doll 73cm Spherical joint Dolls</x:v>
       </x:c>
       <x:c r="E82" s="11" t="str">
         <x:v>具体名称、比例、标题标称高度及裸娃／身体销售选项；图版参数尚待核对。</x:v>
       </x:c>
       <x:c r="F82" s="11" t="str">
-        <x:v>https://doll-zone.com/products/pre-saledollzone-the-world-1-4-doll-full-set-nude-doll-head-presale-sd-doll-spherical-joint-dolls</x:v>
+        <x:v>https://doll-zone.com/products/%E3%80%90pre-sale%E3%80%91dollzone-moon-1-3-cooperation-description-doll-full-set-presale-sd-doll-73cm-spherical-joint-dolls</x:v>
       </x:c>
       <x:c r="G82" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H82" s="11" t="str">
-        <x:v>dollzone-body-2-pre-saledollzone-the-world-1-4-doll-full-set-nude-doll-head-presale-sd-doll-spherical-join</x:v>
+        <x:v>dollzone-1-3-doll--pre-sale-dollzone-moon-1-3-cooperation-description-doll-full-set-presale-sd-doll-73cm-sph</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="72" customHeight="1">
       <x:c r="A83" s="11" t="str">
-        <x:v>B77-001 · 素体</x:v>
+        <x:v>75 Gray · 裸娃</x:v>
       </x:c>
       <x:c r="B83" s="11" t="str">
         <x:v>主来源</x:v>
@@ -19725,24 +19870,24 @@
         <x:v>官方商品选项页</x:v>
       </x:c>
       <x:c r="D83" s="11" t="str">
-        <x:v>【Pre-sale】DollZone B77-001 1/3 Body Presale SD Doll 77cm Spherical joint Dolls</x:v>
+        <x:v>【Pre-sale】DollZone 75 Gray 1/3 Doll Full Set Presale SD Doll 75cm Spherical joint Dolls</x:v>
       </x:c>
       <x:c r="E83" s="11" t="str">
         <x:v>具体名称、比例、标题标称高度及裸娃／身体销售选项；图版参数尚待核对。</x:v>
       </x:c>
       <x:c r="F83" s="11" t="str">
-        <x:v>https://doll-zone.com/products/pre-saledollzone-b77-001-1-3-body-presale-sd-doll-77cm-spherical-joint-dolls</x:v>
+        <x:v>https://doll-zone.com/products/dollzone-75-gray</x:v>
       </x:c>
       <x:c r="G83" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H83" s="11" t="str">
-        <x:v>dollzone-body-2-pre-saledollzone-b77-001-1-3-body-presale-sd-doll-77cm-spherical-joint-dolls</x:v>
+        <x:v>dollzone-1-3-doll-dollzone-75-gray</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="72" customHeight="1">
       <x:c r="A84" s="11" t="str">
-        <x:v>B71-003-1/B71-003-2 · 素体</x:v>
+        <x:v>Evan · 裸娃</x:v>
       </x:c>
       <x:c r="B84" s="11" t="str">
         <x:v>主来源</x:v>
@@ -19751,24 +19896,24 @@
         <x:v>官方商品选项页</x:v>
       </x:c>
       <x:c r="D84" s="11" t="str">
-        <x:v>【Pre-sale】DollZone B71-003-1/B71-003-2 1/3 Body Presale SD Doll 71cm Spherical joint Dolls</x:v>
+        <x:v>【Pre-sale】DollZone Evan 1/3 Doll Full Set Presale SD Doll 75cm Spherical joint Dolls</x:v>
       </x:c>
       <x:c r="E84" s="11" t="str">
         <x:v>具体名称、比例、标题标称高度及裸娃／身体销售选项；图版参数尚待核对。</x:v>
       </x:c>
       <x:c r="F84" s="11" t="str">
-        <x:v>https://doll-zone.com/products/pre-saledollzone-b71-003-1-b71-003-2-1-3-body-presale-sd-doll-71cm-spherical-joint-dolls</x:v>
+        <x:v>https://doll-zone.com/products/evan</x:v>
       </x:c>
       <x:c r="G84" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H84" s="11" t="str">
-        <x:v>dollzone-body-2-pre-saledollzone-b71-003-1-b71-003-2-1-3-body-presale-sd-doll-71cm-spherical-joint-dolls</x:v>
+        <x:v>dollzone-1-3-doll-evan</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="72" customHeight="1">
       <x:c r="A85" s="11" t="str">
-        <x:v>bobo body · 素体</x:v>
+        <x:v>Rosa · 裸娃</x:v>
       </x:c>
       <x:c r="B85" s="11" t="str">
         <x:v>主来源</x:v>
@@ -19777,24 +19922,24 @@
         <x:v>官方商品选项页</x:v>
       </x:c>
       <x:c r="D85" s="11" t="str">
-        <x:v>【Pre-sale】DollZone bobo body 1/6 Body Presale SD Doll 24cm Spherical joint Dolls</x:v>
+        <x:v>【Pre-sale】DollZone Rosa 1/4  Doll Full Set/nude doll/head Presale SD Doll  Spherical joint Dolls</x:v>
       </x:c>
       <x:c r="E85" s="11" t="str">
         <x:v>具体名称、比例、标题标称高度及裸娃／身体销售选项；图版参数尚待核对。</x:v>
       </x:c>
       <x:c r="F85" s="11" t="str">
-        <x:v>https://doll-zone.com/products/%E3%80%90pre-sale%E3%80%91dollzone-bobo-body-1-6-body-presale-sd-doll-24cm-spherical-joint-dolls</x:v>
+        <x:v>https://doll-zone.com/products/%E3%80%90pre-sale%E3%80%91dollzone-rosa-1-4-doll-full-set-nude-doll-head-presale-sd-doll-spherical-joint-dolls</x:v>
       </x:c>
       <x:c r="G85" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H85" s="11" t="str">
-        <x:v>dollzone-body-2--pre-sale-dollzone-bobo-body-1-6-body-presale-sd-doll-24cm-spherical-joint-dolls</x:v>
+        <x:v>dollzone-1-4-doll--pre-sale-dollzone-rosa-1-4-doll-full-set-nude-doll-head-presale-sd-doll-spherical-joint-d</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="72" customHeight="1">
       <x:c r="A86" s="11" t="str">
-        <x:v>B75-002 · 素体</x:v>
+        <x:v>XIAO YI · 裸娃</x:v>
       </x:c>
       <x:c r="B86" s="11" t="str">
         <x:v>主来源</x:v>
@@ -19803,24 +19948,24 @@
         <x:v>官方商品选项页</x:v>
       </x:c>
       <x:c r="D86" s="11" t="str">
-        <x:v>【Pre-sale】DollZone B75-002 1/3 Body Presale SD Doll 75cm Spherical joint Dolls</x:v>
+        <x:v>【Pre-sale】DollZone XIAO YI 1/4 Cooperation Description Doll Full Set/nude doll/head Presale SD Doll 45cm Spherical joint Dolls</x:v>
       </x:c>
       <x:c r="E86" s="11" t="str">
         <x:v>具体名称、比例、标题标称高度及裸娃／身体销售选项；图版参数尚待核对。</x:v>
       </x:c>
       <x:c r="F86" s="11" t="str">
-        <x:v>https://doll-zone.com/products/pre-saledollzone-b75-002-1-3-body-presale-sd-doll-75cm-spherical-joint-dolls</x:v>
+        <x:v>https://doll-zone.com/products/pre-saledollzone-xiao-yi-1-4-cooperation-description-doll-full-set-nude-doll-head-presale-sd-doll-45cm-spherical-joint-dolls</x:v>
       </x:c>
       <x:c r="G86" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H86" s="11" t="str">
-        <x:v>dollzone-body-2-pre-saledollzone-b75-002-1-3-body-presale-sd-doll-75cm-spherical-joint-dolls</x:v>
+        <x:v>dollzone-1-4-doll-pre-saledollzone-xiao-yi-1-4-cooperation-description-doll-full-set-nude-doll-head-presale-</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="72" customHeight="1">
       <x:c r="A87" s="11" t="str">
-        <x:v>B45-022 · 素体</x:v>
+        <x:v>XIAO CHU · 裸娃</x:v>
       </x:c>
       <x:c r="B87" s="11" t="str">
         <x:v>主来源</x:v>
@@ -19829,24 +19974,24 @@
         <x:v>官方商品选项页</x:v>
       </x:c>
       <x:c r="D87" s="11" t="str">
-        <x:v>【Pre-sale】DollZone B45-022  1/4 girl  Body Presale SD Doll 43cm Spherical joint Dolls Hand Accessories Foot Accessories</x:v>
+        <x:v>【Pre-sale】DollZone XIAO CHU 1/4 Cooperation Description Doll Full Set/nude doll/head Presale SD Doll 45cm Spherical joint Dolls</x:v>
       </x:c>
       <x:c r="E87" s="11" t="str">
         <x:v>具体名称、比例、标题标称高度及裸娃／身体销售选项；图版参数尚待核对。</x:v>
       </x:c>
       <x:c r="F87" s="11" t="str">
-        <x:v>https://doll-zone.com/products/%E3%80%90pre-sale%E3%80%91dollzone-b45-022-1-4-girl-body-presale-sd-doll-43cm-spherical-joint-dolls-hand-accessories-foot-accessories</x:v>
+        <x:v>https://doll-zone.com/products/%E3%80%90pre-sale%E3%80%91dollzone-xiao-chu-1-4-cooperation-description-doll-full-set-nude-doll-head-presale-sd-doll-45cm-spherical-joint-dolls</x:v>
       </x:c>
       <x:c r="G87" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H87" s="11" t="str">
-        <x:v>dollzone-body-2--pre-sale-dollzone-b45-022-1-4-girl-body-presale-sd-doll-43cm-spherical-joint-dolls-hand-a</x:v>
+        <x:v>dollzone-1-4-doll--pre-sale-dollzone-xiao-chu-1-4-cooperation-description-doll-full-set-nude-doll-head-presa</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="72" customHeight="1">
       <x:c r="A88" s="11" t="str">
-        <x:v>73 cm 身体 · 素体</x:v>
+        <x:v>The world · 裸娃</x:v>
       </x:c>
       <x:c r="B88" s="11" t="str">
         <x:v>主来源</x:v>
@@ -19855,180 +20000,180 @@
         <x:v>官方商品选项页</x:v>
       </x:c>
       <x:c r="D88" s="11" t="str">
-        <x:v>73</x:v>
+        <x:v>【Pre-sale】DollZone The world 1/4 Doll Full Set/nude doll/head Presale SD Doll  Spherical joint Dolls</x:v>
       </x:c>
       <x:c r="E88" s="11" t="str">
         <x:v>具体名称、比例、标题标称高度及裸娃／身体销售选项；图版参数尚待核对。</x:v>
       </x:c>
       <x:c r="F88" s="11" t="str">
-        <x:v>https://doll-zone.com/products/73</x:v>
+        <x:v>https://doll-zone.com/products/pre-saledollzone-the-world-1-4-doll-full-set-nude-doll-head-presale-sd-doll-spherical-joint-dolls</x:v>
       </x:c>
       <x:c r="G88" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H88" s="11" t="str">
-        <x:v>dollzone-body-2-73</x:v>
+        <x:v>dollzone-body-2-pre-saledollzone-the-world-1-4-doll-full-set-nude-doll-head-presale-sd-doll-spherical-join</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="72" customHeight="1">
       <x:c r="A89" s="11" t="str">
-        <x:v>黏土人偶 Nagito Komaeda</x:v>
+        <x:v>B77-001 · 素体</x:v>
       </x:c>
       <x:c r="B89" s="11" t="str">
         <x:v>主来源</x:v>
       </x:c>
       <x:c r="C89" s="11" t="str">
-        <x:v>官方产品页</x:v>
+        <x:v>官方商品选项页</x:v>
       </x:c>
       <x:c r="D89" s="11" t="str">
-        <x:v>Nendoroid Doll Nagito Komaeda</x:v>
+        <x:v>【Pre-sale】DollZone B77-001 1/3 Body Presale SD Doll 77cm Spherical joint Dolls</x:v>
       </x:c>
       <x:c r="E89" s="11" t="str">
-        <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
+        <x:v>具体名称、比例、标题标称高度及裸娃／身体销售选项；图版参数尚待核对。</x:v>
       </x:c>
       <x:c r="F89" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1141832</x:v>
+        <x:v>https://doll-zone.com/products/pre-saledollzone-b77-001-1-3-body-presale-sd-doll-77cm-spherical-joint-dolls</x:v>
       </x:c>
       <x:c r="G89" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H89" s="11" t="str">
-        <x:v>gsc-doll-1141832</x:v>
+        <x:v>dollzone-body-2-pre-saledollzone-b77-001-1-3-body-presale-sd-doll-77cm-spherical-joint-dolls</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="72" customHeight="1">
       <x:c r="A90" s="11" t="str">
-        <x:v>黏土人偶服装: Nagito Komaeda</x:v>
+        <x:v>B71-003-1/B71-003-2 · 素体</x:v>
       </x:c>
       <x:c r="B90" s="11" t="str">
         <x:v>主来源</x:v>
       </x:c>
       <x:c r="C90" s="11" t="str">
-        <x:v>官方产品页</x:v>
+        <x:v>官方商品选项页</x:v>
       </x:c>
       <x:c r="D90" s="11" t="str">
-        <x:v>Nendoroid Doll Outfit Set: Nagito Komaeda</x:v>
+        <x:v>【Pre-sale】DollZone B71-003-1/B71-003-2 1/3 Body Presale SD Doll 71cm Spherical joint Dolls</x:v>
       </x:c>
       <x:c r="E90" s="11" t="str">
-        <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
+        <x:v>具体名称、比例、标题标称高度及裸娃／身体销售选项；图版参数尚待核对。</x:v>
       </x:c>
       <x:c r="F90" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1141833</x:v>
+        <x:v>https://doll-zone.com/products/pre-saledollzone-b71-003-1-b71-003-2-1-3-body-presale-sd-doll-71cm-spherical-joint-dolls</x:v>
       </x:c>
       <x:c r="G90" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H90" s="11" t="str">
-        <x:v>gsc-doll-1141833</x:v>
+        <x:v>dollzone-body-2-pre-saledollzone-b71-003-1-b71-003-2-1-3-body-presale-sd-doll-71cm-spherical-joint-dolls</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="72" customHeight="1">
       <x:c r="A91" s="11" t="str">
-        <x:v>黏土人偶 Monika</x:v>
+        <x:v>bobo body · 素体</x:v>
       </x:c>
       <x:c r="B91" s="11" t="str">
         <x:v>主来源</x:v>
       </x:c>
       <x:c r="C91" s="11" t="str">
-        <x:v>官方产品页</x:v>
+        <x:v>官方商品选项页</x:v>
       </x:c>
       <x:c r="D91" s="11" t="str">
-        <x:v>Nendoroid Doll Monika</x:v>
+        <x:v>【Pre-sale】DollZone bobo body 1/6 Body Presale SD Doll 24cm Spherical joint Dolls</x:v>
       </x:c>
       <x:c r="E91" s="11" t="str">
-        <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
+        <x:v>具体名称、比例、标题标称高度及裸娃／身体销售选项；图版参数尚待核对。</x:v>
       </x:c>
       <x:c r="F91" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1142668</x:v>
+        <x:v>https://doll-zone.com/products/%E3%80%90pre-sale%E3%80%91dollzone-bobo-body-1-6-body-presale-sd-doll-24cm-spherical-joint-dolls</x:v>
       </x:c>
       <x:c r="G91" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H91" s="11" t="str">
-        <x:v>gsc-doll-1142668</x:v>
+        <x:v>dollzone-body-2--pre-sale-dollzone-bobo-body-1-6-body-presale-sd-doll-24cm-spherical-joint-dolls</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="72" customHeight="1">
       <x:c r="A92" s="11" t="str">
-        <x:v>黏土人偶服装: Monika</x:v>
+        <x:v>B75-002 · 素体</x:v>
       </x:c>
       <x:c r="B92" s="11" t="str">
         <x:v>主来源</x:v>
       </x:c>
       <x:c r="C92" s="11" t="str">
-        <x:v>官方产品页</x:v>
+        <x:v>官方商品选项页</x:v>
       </x:c>
       <x:c r="D92" s="11" t="str">
-        <x:v>Nendoroid Doll Outfit Set: Monika</x:v>
+        <x:v>【Pre-sale】DollZone B75-002 1/3 Body Presale SD Doll 75cm Spherical joint Dolls</x:v>
       </x:c>
       <x:c r="E92" s="11" t="str">
-        <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
+        <x:v>具体名称、比例、标题标称高度及裸娃／身体销售选项；图版参数尚待核对。</x:v>
       </x:c>
       <x:c r="F92" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1142669</x:v>
+        <x:v>https://doll-zone.com/products/pre-saledollzone-b75-002-1-3-body-presale-sd-doll-75cm-spherical-joint-dolls</x:v>
       </x:c>
       <x:c r="G92" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H92" s="11" t="str">
-        <x:v>gsc-doll-1142669</x:v>
+        <x:v>dollzone-body-2-pre-saledollzone-b75-002-1-3-body-presale-sd-doll-75cm-spherical-joint-dolls</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="72" customHeight="1">
       <x:c r="A93" s="11" t="str">
-        <x:v>黏土人偶 Übel</x:v>
+        <x:v>B45-022 · 素体</x:v>
       </x:c>
       <x:c r="B93" s="11" t="str">
         <x:v>主来源</x:v>
       </x:c>
       <x:c r="C93" s="11" t="str">
-        <x:v>官方产品页</x:v>
+        <x:v>官方商品选项页</x:v>
       </x:c>
       <x:c r="D93" s="11" t="str">
-        <x:v>Nendoroid Doll Übel</x:v>
+        <x:v>【Pre-sale】DollZone B45-022  1/4 girl  Body Presale SD Doll 43cm Spherical joint Dolls Hand Accessories Foot Accessories</x:v>
       </x:c>
       <x:c r="E93" s="11" t="str">
-        <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
+        <x:v>具体名称、比例、标题标称高度及裸娃／身体销售选项；图版参数尚待核对。</x:v>
       </x:c>
       <x:c r="F93" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1143700</x:v>
+        <x:v>https://doll-zone.com/products/%E3%80%90pre-sale%E3%80%91dollzone-b45-022-1-4-girl-body-presale-sd-doll-43cm-spherical-joint-dolls-hand-accessories-foot-accessories</x:v>
       </x:c>
       <x:c r="G93" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H93" s="11" t="str">
-        <x:v>gsc-doll-1143700</x:v>
+        <x:v>dollzone-body-2--pre-sale-dollzone-b45-022-1-4-girl-body-presale-sd-doll-43cm-spherical-joint-dolls-hand-a</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="72" customHeight="1">
       <x:c r="A94" s="11" t="str">
-        <x:v>黏土人偶服装: Übel</x:v>
+        <x:v>73 cm 身体 · 素体</x:v>
       </x:c>
       <x:c r="B94" s="11" t="str">
         <x:v>主来源</x:v>
       </x:c>
       <x:c r="C94" s="11" t="str">
-        <x:v>官方产品页</x:v>
+        <x:v>官方商品选项页</x:v>
       </x:c>
       <x:c r="D94" s="11" t="str">
-        <x:v>Nendoroid Doll Outfit Set: Übel</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E94" s="11" t="str">
-        <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
+        <x:v>具体名称、比例、标题标称高度及裸娃／身体销售选项；图版参数尚待核对。</x:v>
       </x:c>
       <x:c r="F94" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1143701</x:v>
+        <x:v>https://doll-zone.com/products/73</x:v>
       </x:c>
       <x:c r="G94" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H94" s="11" t="str">
-        <x:v>gsc-doll-1143701</x:v>
+        <x:v>dollzone-body-2-73</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="72" customHeight="1">
       <x:c r="A95" s="11" t="str">
-        <x:v>黏土人偶 Arona</x:v>
+        <x:v>黏土人偶 Nagito Komaeda</x:v>
       </x:c>
       <x:c r="B95" s="11" t="str">
         <x:v>主来源</x:v>
@@ -20037,24 +20182,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D95" s="11" t="str">
-        <x:v>Nendoroid Doll Arona</x:v>
+        <x:v>Nendoroid Doll Nagito Komaeda</x:v>
       </x:c>
       <x:c r="E95" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F95" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1141869</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1141832</x:v>
       </x:c>
       <x:c r="G95" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H95" s="11" t="str">
-        <x:v>gsc-doll-1141869</x:v>
+        <x:v>gsc-doll-1141832</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="72" customHeight="1">
       <x:c r="A96" s="11" t="str">
-        <x:v>黏土人偶服装: Arona</x:v>
+        <x:v>黏土人偶服装: Nagito Komaeda</x:v>
       </x:c>
       <x:c r="B96" s="11" t="str">
         <x:v>主来源</x:v>
@@ -20063,24 +20208,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D96" s="11" t="str">
-        <x:v>Nendoroid Doll Outfit Set: Arona</x:v>
+        <x:v>Nendoroid Doll Outfit Set: Nagito Komaeda</x:v>
       </x:c>
       <x:c r="E96" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F96" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1141870</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1141833</x:v>
       </x:c>
       <x:c r="G96" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H96" s="11" t="str">
-        <x:v>gsc-doll-1141870</x:v>
+        <x:v>gsc-doll-1141833</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="72" customHeight="1">
       <x:c r="A97" s="11" t="str">
-        <x:v>黏土人偶 Plana</x:v>
+        <x:v>黏土人偶 Monika</x:v>
       </x:c>
       <x:c r="B97" s="11" t="str">
         <x:v>主来源</x:v>
@@ -20089,24 +20234,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D97" s="11" t="str">
-        <x:v>Nendoroid Doll Plana</x:v>
+        <x:v>Nendoroid Doll Monika</x:v>
       </x:c>
       <x:c r="E97" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F97" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1141871</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1142668</x:v>
       </x:c>
       <x:c r="G97" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H97" s="11" t="str">
-        <x:v>gsc-doll-1141871</x:v>
+        <x:v>gsc-doll-1142668</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="72" customHeight="1">
       <x:c r="A98" s="11" t="str">
-        <x:v>黏土人偶服装: Plana</x:v>
+        <x:v>黏土人偶服装: Monika</x:v>
       </x:c>
       <x:c r="B98" s="11" t="str">
         <x:v>主来源</x:v>
@@ -20115,24 +20260,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D98" s="11" t="str">
-        <x:v>Nendoroid Doll Outfit Set: Plana</x:v>
+        <x:v>Nendoroid Doll Outfit Set: Monika</x:v>
       </x:c>
       <x:c r="E98" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F98" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1141872</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1142669</x:v>
       </x:c>
       <x:c r="G98" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H98" s="11" t="str">
-        <x:v>gsc-doll-1141872</x:v>
+        <x:v>gsc-doll-1142669</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="72" customHeight="1">
       <x:c r="A99" s="11" t="str">
-        <x:v>黏土人偶 玛奇玛</x:v>
+        <x:v>黏土人偶 Übel</x:v>
       </x:c>
       <x:c r="B99" s="11" t="str">
         <x:v>主来源</x:v>
@@ -20141,24 +20286,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D99" s="11" t="str">
-        <x:v>Nendoroid Doll Makima</x:v>
+        <x:v>Nendoroid Doll Übel</x:v>
       </x:c>
       <x:c r="E99" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F99" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1142519</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1143700</x:v>
       </x:c>
       <x:c r="G99" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H99" s="11" t="str">
-        <x:v>gsc-doll-1142519</x:v>
+        <x:v>gsc-doll-1143700</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="72" customHeight="1">
       <x:c r="A100" s="11" t="str">
-        <x:v>黏土人偶服装: 玛奇玛</x:v>
+        <x:v>黏土人偶服装: Übel</x:v>
       </x:c>
       <x:c r="B100" s="11" t="str">
         <x:v>主来源</x:v>
@@ -20167,24 +20312,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D100" s="11" t="str">
-        <x:v>Nendoroid Doll Outfit Set: Makima</x:v>
+        <x:v>Nendoroid Doll Outfit Set: Übel</x:v>
       </x:c>
       <x:c r="E100" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F100" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1142520</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1143701</x:v>
       </x:c>
       <x:c r="G100" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H100" s="11" t="str">
-        <x:v>gsc-doll-1142520</x:v>
+        <x:v>gsc-doll-1143701</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="72" customHeight="1">
       <x:c r="A101" s="11" t="str">
-        <x:v>黏土人偶 Yuta Okkotsu: Execution Ver.</x:v>
+        <x:v>黏土人偶 Arona</x:v>
       </x:c>
       <x:c r="B101" s="11" t="str">
         <x:v>主来源</x:v>
@@ -20193,24 +20338,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D101" s="11" t="str">
-        <x:v>Nendoroid Doll Yuta Okkotsu: Execution Ver.</x:v>
+        <x:v>Nendoroid Doll Arona</x:v>
       </x:c>
       <x:c r="E101" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F101" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1142649</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1141869</x:v>
       </x:c>
       <x:c r="G101" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H101" s="11" t="str">
-        <x:v>gsc-doll-1142649</x:v>
+        <x:v>gsc-doll-1141869</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="72" customHeight="1">
       <x:c r="A102" s="11" t="str">
-        <x:v>黏土人偶服装: Yuta Okkotsu: Execution Ver.</x:v>
+        <x:v>黏土人偶服装: Arona</x:v>
       </x:c>
       <x:c r="B102" s="11" t="str">
         <x:v>主来源</x:v>
@@ -20219,24 +20364,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D102" s="11" t="str">
-        <x:v>Nendoroid Doll Outfit Set: Yuta Okkotsu: Execution Ver.</x:v>
+        <x:v>Nendoroid Doll Outfit Set: Arona</x:v>
       </x:c>
       <x:c r="E102" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F102" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1142650</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1141870</x:v>
       </x:c>
       <x:c r="G102" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H102" s="11" t="str">
-        <x:v>gsc-doll-1142650</x:v>
+        <x:v>gsc-doll-1141870</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="72" customHeight="1">
       <x:c r="A103" s="11" t="str">
-        <x:v>黏土人偶 Jinshi</x:v>
+        <x:v>黏土人偶 Plana</x:v>
       </x:c>
       <x:c r="B103" s="11" t="str">
         <x:v>主来源</x:v>
@@ -20245,24 +20390,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D103" s="11" t="str">
-        <x:v>Nendoroid Doll Jinshi</x:v>
+        <x:v>Nendoroid Doll Plana</x:v>
       </x:c>
       <x:c r="E103" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F103" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1142194</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1141871</x:v>
       </x:c>
       <x:c r="G103" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H103" s="11" t="str">
-        <x:v>gsc-doll-1142194</x:v>
+        <x:v>gsc-doll-1141871</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="72" customHeight="1">
       <x:c r="A104" s="11" t="str">
-        <x:v>黏土人偶服装: Jinshi</x:v>
+        <x:v>黏土人偶服装: Plana</x:v>
       </x:c>
       <x:c r="B104" s="11" t="str">
         <x:v>主来源</x:v>
@@ -20271,24 +20416,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D104" s="11" t="str">
-        <x:v>Nendoroid Doll Outfit Set: Jinshi</x:v>
+        <x:v>Nendoroid Doll Outfit Set: Plana</x:v>
       </x:c>
       <x:c r="E104" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F104" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1142195</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1141872</x:v>
       </x:c>
       <x:c r="G104" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H104" s="11" t="str">
-        <x:v>gsc-doll-1142195</x:v>
+        <x:v>gsc-doll-1141872</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="72" customHeight="1">
       <x:c r="A105" s="11" t="str">
-        <x:v>黏土人偶 England</x:v>
+        <x:v>黏土人偶 玛奇玛</x:v>
       </x:c>
       <x:c r="B105" s="11" t="str">
         <x:v>主来源</x:v>
@@ -20297,24 +20442,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D105" s="11" t="str">
-        <x:v>Nendoroid Doll England</x:v>
+        <x:v>Nendoroid Doll Makima</x:v>
       </x:c>
       <x:c r="E105" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F105" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1142502</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1142519</x:v>
       </x:c>
       <x:c r="G105" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H105" s="11" t="str">
-        <x:v>gsc-doll-1142502</x:v>
+        <x:v>gsc-doll-1142519</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="72" customHeight="1">
       <x:c r="A106" s="11" t="str">
-        <x:v>黏土人偶服装: England</x:v>
+        <x:v>黏土人偶服装: 玛奇玛</x:v>
       </x:c>
       <x:c r="B106" s="11" t="str">
         <x:v>主来源</x:v>
@@ -20323,24 +20468,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D106" s="11" t="str">
-        <x:v>Nendoroid Doll Outfit Set: England</x:v>
+        <x:v>Nendoroid Doll Outfit Set: Makima</x:v>
       </x:c>
       <x:c r="E106" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F106" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1142503</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1142520</x:v>
       </x:c>
       <x:c r="G106" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H106" s="11" t="str">
-        <x:v>gsc-doll-1142503</x:v>
+        <x:v>gsc-doll-1142520</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="72" customHeight="1">
       <x:c r="A107" s="11" t="str">
-        <x:v>黏土人偶 Aki Hayakawa</x:v>
+        <x:v>黏土人偶 Yuta Okkotsu: Execution Ver.</x:v>
       </x:c>
       <x:c r="B107" s="11" t="str">
         <x:v>主来源</x:v>
@@ -20349,24 +20494,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D107" s="11" t="str">
-        <x:v>Nendoroid Doll Aki Hayakawa</x:v>
+        <x:v>Nendoroid Doll Yuta Okkotsu: Execution Ver.</x:v>
       </x:c>
       <x:c r="E107" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F107" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1142517</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1142649</x:v>
       </x:c>
       <x:c r="G107" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H107" s="11" t="str">
-        <x:v>gsc-doll-1142517</x:v>
+        <x:v>gsc-doll-1142649</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="72" customHeight="1">
       <x:c r="A108" s="11" t="str">
-        <x:v>黏土人偶服装: Aki Hayakawa</x:v>
+        <x:v>黏土人偶服装: Yuta Okkotsu: Execution Ver.</x:v>
       </x:c>
       <x:c r="B108" s="11" t="str">
         <x:v>主来源</x:v>
@@ -20375,24 +20520,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D108" s="11" t="str">
-        <x:v>Nendoroid Doll Outfit Set: Aki Hayakawa</x:v>
+        <x:v>Nendoroid Doll Outfit Set: Yuta Okkotsu: Execution Ver.</x:v>
       </x:c>
       <x:c r="E108" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F108" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1142518</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1142650</x:v>
       </x:c>
       <x:c r="G108" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H108" s="11" t="str">
-        <x:v>gsc-doll-1142518</x:v>
+        <x:v>gsc-doll-1142650</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="72" customHeight="1">
       <x:c r="A109" s="11" t="str">
-        <x:v>黏土人偶 Goro Akechi: School Uniform Ver.</x:v>
+        <x:v>黏土人偶 Jinshi</x:v>
       </x:c>
       <x:c r="B109" s="11" t="str">
         <x:v>主来源</x:v>
@@ -20401,24 +20546,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D109" s="11" t="str">
-        <x:v>Nendoroid Doll Goro Akechi: School Uniform Ver.</x:v>
+        <x:v>Nendoroid Doll Jinshi</x:v>
       </x:c>
       <x:c r="E109" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F109" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1142666</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1142194</x:v>
       </x:c>
       <x:c r="G109" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H109" s="11" t="str">
-        <x:v>gsc-doll-1142666</x:v>
+        <x:v>gsc-doll-1142194</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="72" customHeight="1">
       <x:c r="A110" s="11" t="str">
-        <x:v>黏土人偶服装: Goro Akechi - School Uniform Ver.</x:v>
+        <x:v>黏土人偶服装: Jinshi</x:v>
       </x:c>
       <x:c r="B110" s="11" t="str">
         <x:v>主来源</x:v>
@@ -20427,24 +20572,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D110" s="11" t="str">
-        <x:v>Nendoroid Doll Outfit Set: Goro Akechi - School Uniform Ver.</x:v>
+        <x:v>Nendoroid Doll Outfit Set: Jinshi</x:v>
       </x:c>
       <x:c r="E110" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F110" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1142667</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1142195</x:v>
       </x:c>
       <x:c r="G110" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H110" s="11" t="str">
-        <x:v>gsc-doll-1142667</x:v>
+        <x:v>gsc-doll-1142195</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="72" customHeight="1">
       <x:c r="A111" s="11" t="str">
-        <x:v>黏土人偶 Yui Hirasawa</x:v>
+        <x:v>黏土人偶 England</x:v>
       </x:c>
       <x:c r="B111" s="11" t="str">
         <x:v>主来源</x:v>
@@ -20453,24 +20598,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D111" s="11" t="str">
-        <x:v>Nendoroid Doll Yui Hirasawa</x:v>
+        <x:v>Nendoroid Doll England</x:v>
       </x:c>
       <x:c r="E111" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F111" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1142843</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1142502</x:v>
       </x:c>
       <x:c r="G111" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H111" s="11" t="str">
-        <x:v>gsc-doll-1142843</x:v>
+        <x:v>gsc-doll-1142502</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="72" customHeight="1">
       <x:c r="A112" s="11" t="str">
-        <x:v>黏土人偶服装: Yui Hirasawa</x:v>
+        <x:v>黏土人偶服装: England</x:v>
       </x:c>
       <x:c r="B112" s="11" t="str">
         <x:v>主来源</x:v>
@@ -20479,24 +20624,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D112" s="11" t="str">
-        <x:v>Nendoroid Doll Outfit Set: Yui Hirasawa</x:v>
+        <x:v>Nendoroid Doll Outfit Set: England</x:v>
       </x:c>
       <x:c r="E112" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F112" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1142844</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1142503</x:v>
       </x:c>
       <x:c r="G112" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H112" s="11" t="str">
-        <x:v>gsc-doll-1142844</x:v>
+        <x:v>gsc-doll-1142503</x:v>
       </x:c>
     </x:row>
     <x:row r="113" ht="72" customHeight="1">
       <x:c r="A113" s="11" t="str">
-        <x:v>黏土人偶 America</x:v>
+        <x:v>黏土人偶 Aki Hayakawa</x:v>
       </x:c>
       <x:c r="B113" s="11" t="str">
         <x:v>主来源</x:v>
@@ -20505,24 +20650,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D113" s="11" t="str">
-        <x:v>Nendoroid Doll America</x:v>
+        <x:v>Nendoroid Doll Aki Hayakawa</x:v>
       </x:c>
       <x:c r="E113" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F113" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1142500</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1142517</x:v>
       </x:c>
       <x:c r="G113" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H113" s="11" t="str">
-        <x:v>gsc-doll-1142500</x:v>
+        <x:v>gsc-doll-1142517</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="72" customHeight="1">
       <x:c r="A114" s="11" t="str">
-        <x:v>黏土人偶服装: America</x:v>
+        <x:v>黏土人偶服装: Aki Hayakawa</x:v>
       </x:c>
       <x:c r="B114" s="11" t="str">
         <x:v>主来源</x:v>
@@ -20531,24 +20676,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D114" s="11" t="str">
-        <x:v>Nendoroid Doll Outfit Set: America</x:v>
+        <x:v>Nendoroid Doll Outfit Set: Aki Hayakawa</x:v>
       </x:c>
       <x:c r="E114" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F114" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1142501</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1142518</x:v>
       </x:c>
       <x:c r="G114" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H114" s="11" t="str">
-        <x:v>gsc-doll-1142501</x:v>
+        <x:v>gsc-doll-1142518</x:v>
       </x:c>
     </x:row>
     <x:row r="115" ht="72" customHeight="1">
       <x:c r="A115" s="11" t="str">
-        <x:v>黏土人偶 Sakura Kinomoto: Costume Ver.</x:v>
+        <x:v>黏土人偶 Goro Akechi: School Uniform Ver.</x:v>
       </x:c>
       <x:c r="B115" s="11" t="str">
         <x:v>主来源</x:v>
@@ -20557,24 +20702,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D115" s="11" t="str">
-        <x:v>Nendoroid Doll Sakura Kinomoto: Costume Ver.</x:v>
+        <x:v>Nendoroid Doll Goro Akechi: School Uniform Ver.</x:v>
       </x:c>
       <x:c r="E115" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F115" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1140621</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1142666</x:v>
       </x:c>
       <x:c r="G115" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H115" s="11" t="str">
-        <x:v>gsc-doll-1140621</x:v>
+        <x:v>gsc-doll-1142666</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="72" customHeight="1">
       <x:c r="A116" s="11" t="str">
-        <x:v>黏土人偶服装: Sakura Kinomoto: Costume Ver.</x:v>
+        <x:v>黏土人偶服装: Goro Akechi - School Uniform Ver.</x:v>
       </x:c>
       <x:c r="B116" s="11" t="str">
         <x:v>主来源</x:v>
@@ -20583,24 +20728,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D116" s="11" t="str">
-        <x:v>Nendoroid Doll Outfit Set: Sakura Kinomoto: Costume Ver.</x:v>
+        <x:v>Nendoroid Doll Outfit Set: Goro Akechi - School Uniform Ver.</x:v>
       </x:c>
       <x:c r="E116" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F116" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1140622</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1142667</x:v>
       </x:c>
       <x:c r="G116" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H116" s="11" t="str">
-        <x:v>gsc-doll-1140622</x:v>
+        <x:v>gsc-doll-1142667</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="72" customHeight="1">
       <x:c r="A117" s="11" t="str">
-        <x:v>黏土人偶 初音未来: ∞ Ver.</x:v>
+        <x:v>黏土人偶 Yui Hirasawa</x:v>
       </x:c>
       <x:c r="B117" s="11" t="str">
         <x:v>主来源</x:v>
@@ -20609,24 +20754,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D117" s="11" t="str">
-        <x:v>Nendoroid Doll Hatsune Miku: ∞ Ver.</x:v>
+        <x:v>Nendoroid Doll Yui Hirasawa</x:v>
       </x:c>
       <x:c r="E117" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F117" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1141536</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1142843</x:v>
       </x:c>
       <x:c r="G117" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H117" s="11" t="str">
-        <x:v>gsc-doll-1141536</x:v>
+        <x:v>gsc-doll-1142843</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="72" customHeight="1">
       <x:c r="A118" s="11" t="str">
-        <x:v>黏土人偶服装: 初音未来: ∞ Ver.</x:v>
+        <x:v>黏土人偶服装: Yui Hirasawa</x:v>
       </x:c>
       <x:c r="B118" s="11" t="str">
         <x:v>主来源</x:v>
@@ -20635,24 +20780,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D118" s="11" t="str">
-        <x:v>Nendoroid Doll Outfit Set: Hatsune Miku: ∞ Ver.</x:v>
+        <x:v>Nendoroid Doll Outfit Set: Yui Hirasawa</x:v>
       </x:c>
       <x:c r="E118" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F118" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1141537</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1142844</x:v>
       </x:c>
       <x:c r="G118" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H118" s="11" t="str">
-        <x:v>gsc-doll-1141537</x:v>
+        <x:v>gsc-doll-1142844</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="72" customHeight="1">
       <x:c r="A119" s="11" t="str">
-        <x:v>黏土人偶 Wing Parts Set</x:v>
+        <x:v>黏土人偶 America</x:v>
       </x:c>
       <x:c r="B119" s="11" t="str">
         <x:v>主来源</x:v>
@@ -20661,24 +20806,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D119" s="11" t="str">
-        <x:v>Nendoroid Doll Wing Parts Set</x:v>
+        <x:v>Nendoroid Doll America</x:v>
       </x:c>
       <x:c r="E119" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F119" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1141744</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1142500</x:v>
       </x:c>
       <x:c r="G119" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H119" s="11" t="str">
-        <x:v>gsc-doll-1141744</x:v>
+        <x:v>gsc-doll-1142500</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="72" customHeight="1">
       <x:c r="A120" s="11" t="str">
-        <x:v>黏土人偶 Ciel Phantomhive</x:v>
+        <x:v>黏土人偶服装: America</x:v>
       </x:c>
       <x:c r="B120" s="11" t="str">
         <x:v>主来源</x:v>
@@ -20687,24 +20832,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D120" s="11" t="str">
-        <x:v>Nendoroid Doll Ciel Phantomhive</x:v>
+        <x:v>Nendoroid Doll Outfit Set: America</x:v>
       </x:c>
       <x:c r="E120" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F120" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/9723</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1142501</x:v>
       </x:c>
       <x:c r="G120" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H120" s="11" t="str">
-        <x:v>gsc-doll-9723</x:v>
+        <x:v>gsc-doll-1142501</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="72" customHeight="1">
       <x:c r="A121" s="11" t="str">
-        <x:v>黏土人偶 Sebastian Michaelis</x:v>
+        <x:v>黏土人偶 Sakura Kinomoto: Costume Ver.</x:v>
       </x:c>
       <x:c r="B121" s="11" t="str">
         <x:v>主来源</x:v>
@@ -20713,24 +20858,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D121" s="11" t="str">
-        <x:v>Nendoroid Doll Sebastian Michaelis</x:v>
+        <x:v>Nendoroid Doll Sakura Kinomoto: Costume Ver.</x:v>
       </x:c>
       <x:c r="E121" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F121" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/9725</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1140621</x:v>
       </x:c>
       <x:c r="G121" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H121" s="11" t="str">
-        <x:v>gsc-doll-9725</x:v>
+        <x:v>gsc-doll-1140621</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="72" customHeight="1">
       <x:c r="A122" s="11" t="str">
-        <x:v>黏土人偶 Chocola</x:v>
+        <x:v>黏土人偶服装: Sakura Kinomoto: Costume Ver.</x:v>
       </x:c>
       <x:c r="B122" s="11" t="str">
         <x:v>主来源</x:v>
@@ -20739,24 +20884,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D122" s="11" t="str">
-        <x:v>Nendoroid Doll Chocola</x:v>
+        <x:v>Nendoroid Doll Outfit Set: Sakura Kinomoto: Costume Ver.</x:v>
       </x:c>
       <x:c r="E122" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F122" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1140127</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1140622</x:v>
       </x:c>
       <x:c r="G122" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H122" s="11" t="str">
-        <x:v>gsc-doll-1140127</x:v>
+        <x:v>gsc-doll-1140622</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="72" customHeight="1">
       <x:c r="A123" s="11" t="str">
-        <x:v>黏土人偶服装: Chocola</x:v>
+        <x:v>黏土人偶 初音未来: ∞ Ver.</x:v>
       </x:c>
       <x:c r="B123" s="11" t="str">
         <x:v>主来源</x:v>
@@ -20765,24 +20910,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D123" s="11" t="str">
-        <x:v>Nendoroid Doll Outfit Set: Chocola</x:v>
+        <x:v>Nendoroid Doll Hatsune Miku: ∞ Ver.</x:v>
       </x:c>
       <x:c r="E123" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F123" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1140128</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1141536</x:v>
       </x:c>
       <x:c r="G123" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H123" s="11" t="str">
-        <x:v>gsc-doll-1140128</x:v>
+        <x:v>gsc-doll-1141536</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="72" customHeight="1">
       <x:c r="A124" s="11" t="str">
-        <x:v>黏土人偶 Vanilla</x:v>
+        <x:v>黏土人偶服装: 初音未来: ∞ Ver.</x:v>
       </x:c>
       <x:c r="B124" s="11" t="str">
         <x:v>主来源</x:v>
@@ -20791,24 +20936,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D124" s="11" t="str">
-        <x:v>Nendoroid Doll Vanilla</x:v>
+        <x:v>Nendoroid Doll Outfit Set: Hatsune Miku: ∞ Ver.</x:v>
       </x:c>
       <x:c r="E124" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F124" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1140129</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1141537</x:v>
       </x:c>
       <x:c r="G124" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H124" s="11" t="str">
-        <x:v>gsc-doll-1140129</x:v>
+        <x:v>gsc-doll-1141537</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="72" customHeight="1">
       <x:c r="A125" s="11" t="str">
-        <x:v>黏土人偶服装: Vanilla</x:v>
+        <x:v>黏土人偶 Wing Parts Set</x:v>
       </x:c>
       <x:c r="B125" s="11" t="str">
         <x:v>主来源</x:v>
@@ -20817,24 +20962,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D125" s="11" t="str">
-        <x:v>Nendoroid Doll Outfit Set: Vanilla</x:v>
+        <x:v>Nendoroid Doll Wing Parts Set</x:v>
       </x:c>
       <x:c r="E125" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F125" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1140130</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1141744</x:v>
       </x:c>
       <x:c r="G125" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H125" s="11" t="str">
-        <x:v>gsc-doll-1140130</x:v>
+        <x:v>gsc-doll-1141744</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="72" customHeight="1">
       <x:c r="A126" s="11" t="str">
-        <x:v>黏土人偶 Picnic Parts Set</x:v>
+        <x:v>黏土人偶 Ciel Phantomhive</x:v>
       </x:c>
       <x:c r="B126" s="11" t="str">
         <x:v>主来源</x:v>
@@ -20843,24 +20988,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D126" s="11" t="str">
-        <x:v>Nendoroid Doll Picnic Parts Set</x:v>
+        <x:v>Nendoroid Doll Ciel Phantomhive</x:v>
       </x:c>
       <x:c r="E126" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F126" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1143950</x:v>
+        <x:v>https://www.goodsmile.com/en/product/9723</x:v>
       </x:c>
       <x:c r="G126" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H126" s="11" t="str">
-        <x:v>gsc-doll-1143950</x:v>
+        <x:v>gsc-doll-9723</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="72" customHeight="1">
       <x:c r="A127" s="11" t="str">
-        <x:v>黏土人偶 Saber: Casual Outfit Ver.</x:v>
+        <x:v>黏土人偶 Sebastian Michaelis</x:v>
       </x:c>
       <x:c r="B127" s="11" t="str">
         <x:v>主来源</x:v>
@@ -20869,24 +21014,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D127" s="11" t="str">
-        <x:v>Nendoroid Doll Saber: Casual Outfit Ver.</x:v>
+        <x:v>Nendoroid Doll Sebastian Michaelis</x:v>
       </x:c>
       <x:c r="E127" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F127" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1142290</x:v>
+        <x:v>https://www.goodsmile.com/en/product/9725</x:v>
       </x:c>
       <x:c r="G127" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H127" s="11" t="str">
-        <x:v>gsc-doll-1142290</x:v>
+        <x:v>gsc-doll-9725</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="72" customHeight="1">
       <x:c r="A128" s="11" t="str">
-        <x:v>黏土人偶服装: Saber - Casual Outfit Ver.</x:v>
+        <x:v>黏土人偶 Chocola</x:v>
       </x:c>
       <x:c r="B128" s="11" t="str">
         <x:v>主来源</x:v>
@@ -20895,24 +21040,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D128" s="11" t="str">
-        <x:v>Nendoroid Doll Outfit Set: Saber - Casual Outfit Ver.</x:v>
+        <x:v>Nendoroid Doll Chocola</x:v>
       </x:c>
       <x:c r="E128" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F128" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1142291</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1140127</x:v>
       </x:c>
       <x:c r="G128" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H128" s="11" t="str">
-        <x:v>gsc-doll-1142291</x:v>
+        <x:v>gsc-doll-1140127</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="72" customHeight="1">
       <x:c r="A129" s="11" t="str">
-        <x:v>Near Harmonia Sentimental Circus.</x:v>
+        <x:v>黏土人偶服装: Chocola</x:v>
       </x:c>
       <x:c r="B129" s="11" t="str">
         <x:v>主来源</x:v>
@@ -20921,24 +21066,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D129" s="11" t="str">
-        <x:v>Near Harmonia Sentimental Circus.</x:v>
+        <x:v>Nendoroid Doll Outfit Set: Chocola</x:v>
       </x:c>
       <x:c r="E129" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F129" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/60764</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1140128</x:v>
       </x:c>
       <x:c r="G129" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H129" s="11" t="str">
-        <x:v>gsc-harmonia-60764</x:v>
+        <x:v>gsc-doll-1140128</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="72" customHeight="1">
       <x:c r="A130" s="11" t="str">
-        <x:v>Near Harmonia Ebiten no Shippo: Idol Ver. From Sumikkogurashi / Ebifurai no Shippo: Idol Ver. From Sumikkogurashi</x:v>
+        <x:v>黏土人偶 Vanilla</x:v>
       </x:c>
       <x:c r="B130" s="11" t="str">
         <x:v>主来源</x:v>
@@ -20947,24 +21092,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D130" s="11" t="str">
-        <x:v>Near Harmonia Ebiten no Shippo: Idol Ver. From Sumikkogurashi / Ebifurai no Shippo: Idol Ver. From Sumikkogurashi</x:v>
+        <x:v>Nendoroid Doll Vanilla</x:v>
       </x:c>
       <x:c r="E130" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F130" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/60765</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1140129</x:v>
       </x:c>
       <x:c r="G130" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H130" s="11" t="str">
-        <x:v>gsc-harmonia-60765</x:v>
+        <x:v>gsc-doll-1140129</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="72" customHeight="1">
       <x:c r="A131" s="11" t="str">
-        <x:v>Near Harmonia Modoria/Lavina/Poppy</x:v>
+        <x:v>黏土人偶服装: Vanilla</x:v>
       </x:c>
       <x:c r="B131" s="11" t="str">
         <x:v>主来源</x:v>
@@ -20973,24 +21118,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D131" s="11" t="str">
-        <x:v>Near Harmonia Modoria/Lavina/Poppy</x:v>
+        <x:v>Nendoroid Doll Outfit Set: Vanilla</x:v>
       </x:c>
       <x:c r="E131" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F131" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1136213</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1140130</x:v>
       </x:c>
       <x:c r="G131" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H131" s="11" t="str">
-        <x:v>gsc-harmonia-1136213</x:v>
+        <x:v>gsc-doll-1140130</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="72" customHeight="1">
       <x:c r="A132" s="11" t="str">
-        <x:v>Near Harmonia Potato from Pui Pui Molcar</x:v>
+        <x:v>黏土人偶 Picnic Parts Set</x:v>
       </x:c>
       <x:c r="B132" s="11" t="str">
         <x:v>主来源</x:v>
@@ -20999,24 +21144,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D132" s="11" t="str">
-        <x:v>Near Harmonia Potato from Pui Pui Molcar</x:v>
+        <x:v>Nendoroid Doll Picnic Parts Set</x:v>
       </x:c>
       <x:c r="E132" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F132" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/55924</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1143950</x:v>
       </x:c>
       <x:c r="G132" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H132" s="11" t="str">
-        <x:v>gsc-harmonia-55924</x:v>
+        <x:v>gsc-doll-1143950</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="72" customHeight="1">
       <x:c r="A133" s="11" t="str">
-        <x:v>Near Harmonia Shiromo from Pui Pui Molcar</x:v>
+        <x:v>黏土人偶 Saber: Casual Outfit Ver.</x:v>
       </x:c>
       <x:c r="B133" s="11" t="str">
         <x:v>主来源</x:v>
@@ -21025,24 +21170,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D133" s="11" t="str">
-        <x:v>Near Harmonia Shiromo from Pui Pui Molcar</x:v>
+        <x:v>Nendoroid Doll Saber: Casual Outfit Ver.</x:v>
       </x:c>
       <x:c r="E133" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F133" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/55925</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1142290</x:v>
       </x:c>
       <x:c r="G133" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H133" s="11" t="str">
-        <x:v>gsc-harmonia-55925</x:v>
+        <x:v>gsc-doll-1142290</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="72" customHeight="1">
       <x:c r="A134" s="11" t="str">
-        <x:v>Near Harmonia Curious/Chatty/Mellow</x:v>
+        <x:v>黏土人偶服装: Saber - Casual Outfit Ver.</x:v>
       </x:c>
       <x:c r="B134" s="11" t="str">
         <x:v>主来源</x:v>
@@ -21051,24 +21196,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D134" s="11" t="str">
-        <x:v>Near Harmonia Curious/Chatty/Mellow</x:v>
+        <x:v>Nendoroid Doll Outfit Set: Saber - Casual Outfit Ver.</x:v>
       </x:c>
       <x:c r="E134" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F134" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/60130</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1142291</x:v>
       </x:c>
       <x:c r="G134" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H134" s="11" t="str">
-        <x:v>gsc-harmonia-60130</x:v>
+        <x:v>gsc-doll-1142291</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="72" customHeight="1">
       <x:c r="A135" s="11" t="str">
-        <x:v>Harmonia humming 雪初音</x:v>
+        <x:v>Near Harmonia Sentimental Circus.</x:v>
       </x:c>
       <x:c r="B135" s="11" t="str">
         <x:v>主来源</x:v>
@@ -21077,24 +21222,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D135" s="11" t="str">
-        <x:v>Harmonia humming Snow Miku</x:v>
+        <x:v>Near Harmonia Sentimental Circus.</x:v>
       </x:c>
       <x:c r="E135" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F135" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/45955</x:v>
+        <x:v>https://www.goodsmile.com/en/product/60764</x:v>
       </x:c>
       <x:c r="G135" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H135" s="11" t="str">
-        <x:v>gsc-harmonia-45955</x:v>
+        <x:v>gsc-harmonia-60764</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="72" customHeight="1">
       <x:c r="A136" s="11" t="str">
-        <x:v>Harmonia bloom Pretender/Oberon: First Ascension</x:v>
+        <x:v>Near Harmonia Ebiten no Shippo: Idol Ver. From Sumikkogurashi / Ebifurai no Shippo: Idol Ver. From Sumikkogurashi</x:v>
       </x:c>
       <x:c r="B136" s="11" t="str">
         <x:v>主来源</x:v>
@@ -21103,24 +21248,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D136" s="11" t="str">
-        <x:v>Harmonia bloom Pretender/Oberon: First Ascension</x:v>
+        <x:v>Near Harmonia Ebiten no Shippo: Idol Ver. From Sumikkogurashi / Ebifurai no Shippo: Idol Ver. From Sumikkogurashi</x:v>
       </x:c>
       <x:c r="E136" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F136" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/54164</x:v>
+        <x:v>https://www.goodsmile.com/en/product/60765</x:v>
       </x:c>
       <x:c r="G136" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H136" s="11" t="str">
-        <x:v>gsc-harmonia-54164</x:v>
+        <x:v>gsc-harmonia-60765</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="72" customHeight="1">
       <x:c r="A137" s="11" t="str">
-        <x:v>Harmonia bloom blooming doll root (Body/Sunrise）</x:v>
+        <x:v>Near Harmonia Modoria/Lavina/Poppy</x:v>
       </x:c>
       <x:c r="B137" s="11" t="str">
         <x:v>主来源</x:v>
@@ -21129,24 +21274,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D137" s="11" t="str">
-        <x:v>Harmonia bloom blooming doll root (Body/Sunrise）</x:v>
+        <x:v>Near Harmonia Modoria/Lavina/Poppy</x:v>
       </x:c>
       <x:c r="E137" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F137" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/36197</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1136213</x:v>
       </x:c>
       <x:c r="G137" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H137" s="11" t="str">
-        <x:v>gsc-harmonia-36197</x:v>
+        <x:v>gsc-harmonia-1136213</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="72" customHeight="1">
       <x:c r="A138" s="11" t="str">
-        <x:v>Harmonia bloom blooming doll root (Body/Sunset）</x:v>
+        <x:v>Near Harmonia Potato from Pui Pui Molcar</x:v>
       </x:c>
       <x:c r="B138" s="11" t="str">
         <x:v>主来源</x:v>
@@ -21155,24 +21300,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D138" s="11" t="str">
-        <x:v>Harmonia bloom blooming doll root (Body/Sunset）</x:v>
+        <x:v>Near Harmonia Potato from Pui Pui Molcar</x:v>
       </x:c>
       <x:c r="E138" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F138" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/36198</x:v>
+        <x:v>https://www.goodsmile.com/en/product/55924</x:v>
       </x:c>
       <x:c r="G138" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H138" s="11" t="str">
-        <x:v>gsc-harmonia-36198</x:v>
+        <x:v>gsc-harmonia-55924</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="72" customHeight="1">
       <x:c r="A139" s="11" t="str">
-        <x:v>Harmonia bloom Special Outfit Series (bloom/root) Designed by babydo</x:v>
+        <x:v>Near Harmonia Shiromo from Pui Pui Molcar</x:v>
       </x:c>
       <x:c r="B139" s="11" t="str">
         <x:v>主来源</x:v>
@@ -21181,24 +21326,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D139" s="11" t="str">
-        <x:v>Harmonia bloom Special Outfit Series (bloom/root) Designed by babydo</x:v>
+        <x:v>Near Harmonia Shiromo from Pui Pui Molcar</x:v>
       </x:c>
       <x:c r="E139" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F139" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/12310</x:v>
+        <x:v>https://www.goodsmile.com/en/product/55925</x:v>
       </x:c>
       <x:c r="G139" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H139" s="11" t="str">
-        <x:v>gsc-harmonia-12310</x:v>
+        <x:v>gsc-harmonia-55925</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="72" customHeight="1">
       <x:c r="A140" s="11" t="str">
-        <x:v>Harmonia bloom Make &amp; Body set root (Volker)</x:v>
+        <x:v>Near Harmonia Curious/Chatty/Mellow</x:v>
       </x:c>
       <x:c r="B140" s="11" t="str">
         <x:v>主来源</x:v>
@@ -21207,24 +21352,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D140" s="11" t="str">
-        <x:v>Harmonia bloom Make &amp; Body set root (Volker)</x:v>
+        <x:v>Near Harmonia Curious/Chatty/Mellow</x:v>
       </x:c>
       <x:c r="E140" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F140" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/12385</x:v>
+        <x:v>https://www.goodsmile.com/en/product/60130</x:v>
       </x:c>
       <x:c r="G140" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H140" s="11" t="str">
-        <x:v>gsc-harmonia-12385</x:v>
+        <x:v>gsc-harmonia-60130</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="72" customHeight="1">
       <x:c r="A141" s="11" t="str">
-        <x:v>Harmonia bloom Outfit set (root) Hunter</x:v>
+        <x:v>Harmonia humming 雪初音</x:v>
       </x:c>
       <x:c r="B141" s="11" t="str">
         <x:v>主来源</x:v>
@@ -21233,24 +21378,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D141" s="11" t="str">
-        <x:v>Harmonia bloom Outfit set (root) Hunter</x:v>
+        <x:v>Harmonia humming Snow Miku</x:v>
       </x:c>
       <x:c r="E141" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F141" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/12384</x:v>
+        <x:v>https://www.goodsmile.com/en/product/45955</x:v>
       </x:c>
       <x:c r="G141" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H141" s="11" t="str">
-        <x:v>gsc-harmonia-12384</x:v>
+        <x:v>gsc-harmonia-45955</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="72" customHeight="1">
       <x:c r="A142" s="11" t="str">
-        <x:v>Harmonia bloom Volker Honest hunter</x:v>
+        <x:v>Harmonia bloom Pretender/Oberon: First Ascension</x:v>
       </x:c>
       <x:c r="B142" s="11" t="str">
         <x:v>主来源</x:v>
@@ -21259,24 +21404,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D142" s="11" t="str">
-        <x:v>Harmonia bloom Volker Honest hunter</x:v>
+        <x:v>Harmonia bloom Pretender/Oberon: First Ascension</x:v>
       </x:c>
       <x:c r="E142" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F142" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/12383</x:v>
+        <x:v>https://www.goodsmile.com/en/product/54164</x:v>
       </x:c>
       <x:c r="G142" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H142" s="11" t="str">
-        <x:v>gsc-harmonia-12383</x:v>
+        <x:v>gsc-harmonia-54164</x:v>
       </x:c>
     </x:row>
     <x:row r="143" ht="72" customHeight="1">
       <x:c r="A143" s="11" t="str">
-        <x:v>Harmonia bloom Seasonal 服装套装 Charlotte (Melone)</x:v>
+        <x:v>Harmonia bloom blooming doll root (Body/Sunrise）</x:v>
       </x:c>
       <x:c r="B143" s="11" t="str">
         <x:v>主来源</x:v>
@@ -21285,24 +21430,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D143" s="11" t="str">
-        <x:v>Harmonia bloom Seasonal Outfit Set Charlotte (Melone)</x:v>
+        <x:v>Harmonia bloom blooming doll root (Body/Sunrise）</x:v>
       </x:c>
       <x:c r="E143" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F143" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/12085</x:v>
+        <x:v>https://www.goodsmile.com/en/product/36197</x:v>
       </x:c>
       <x:c r="G143" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H143" s="11" t="str">
-        <x:v>gsc-harmonia-12085</x:v>
+        <x:v>gsc-harmonia-36197</x:v>
       </x:c>
     </x:row>
     <x:row r="144" ht="72" customHeight="1">
       <x:c r="A144" s="11" t="str">
-        <x:v>Harmonia bloom Seasonal 服装套装 Charlotte (Kirsche)</x:v>
+        <x:v>Harmonia bloom blooming doll root (Body/Sunset）</x:v>
       </x:c>
       <x:c r="B144" s="11" t="str">
         <x:v>主来源</x:v>
@@ -21311,24 +21456,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D144" s="11" t="str">
-        <x:v>Harmonia bloom Seasonal Outfit Set Charlotte (Kirsche)</x:v>
+        <x:v>Harmonia bloom blooming doll root (Body/Sunset）</x:v>
       </x:c>
       <x:c r="E144" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F144" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/12086</x:v>
+        <x:v>https://www.goodsmile.com/en/product/36198</x:v>
       </x:c>
       <x:c r="G144" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H144" s="11" t="str">
-        <x:v>gsc-harmonia-12086</x:v>
+        <x:v>gsc-harmonia-36198</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="72" customHeight="1">
       <x:c r="A145" s="11" t="str">
-        <x:v>Harmonia humming Nadeshiko Kagamihara</x:v>
+        <x:v>Harmonia bloom Special Outfit Series (bloom/root) Designed by babydo</x:v>
       </x:c>
       <x:c r="B145" s="11" t="str">
         <x:v>主来源</x:v>
@@ -21337,24 +21482,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D145" s="11" t="str">
-        <x:v>Harmonia humming Nadeshiko Kagamihara</x:v>
+        <x:v>Harmonia bloom Special Outfit Series (bloom/root) Designed by babydo</x:v>
       </x:c>
       <x:c r="E145" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F145" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/11731</x:v>
+        <x:v>https://www.goodsmile.com/en/product/12310</x:v>
       </x:c>
       <x:c r="G145" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H145" s="11" t="str">
-        <x:v>gsc-harmonia-11731</x:v>
+        <x:v>gsc-harmonia-12310</x:v>
       </x:c>
     </x:row>
     <x:row r="146" ht="72" customHeight="1">
       <x:c r="A146" s="11" t="str">
-        <x:v>Harmonia humming Rin Shima</x:v>
+        <x:v>Harmonia bloom Make &amp; Body set root (Volker)</x:v>
       </x:c>
       <x:c r="B146" s="11" t="str">
         <x:v>主来源</x:v>
@@ -21363,24 +21508,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D146" s="11" t="str">
-        <x:v>Harmonia humming Rin Shima</x:v>
+        <x:v>Harmonia bloom Make &amp; Body set root (Volker)</x:v>
       </x:c>
       <x:c r="E146" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F146" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/11732</x:v>
+        <x:v>https://www.goodsmile.com/en/product/12385</x:v>
       </x:c>
       <x:c r="G146" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H146" s="11" t="str">
-        <x:v>gsc-harmonia-11732</x:v>
+        <x:v>gsc-harmonia-12385</x:v>
       </x:c>
     </x:row>
     <x:row r="147" ht="72" customHeight="1">
       <x:c r="A147" s="11" t="str">
-        <x:v>Harmonia bloom Seasonal Doll Gabriela</x:v>
+        <x:v>Harmonia bloom Outfit set (root) Hunter</x:v>
       </x:c>
       <x:c r="B147" s="11" t="str">
         <x:v>主来源</x:v>
@@ -21389,24 +21534,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D147" s="11" t="str">
-        <x:v>Harmonia bloom Seasonal Doll Gabriela</x:v>
+        <x:v>Harmonia bloom Outfit set (root) Hunter</x:v>
       </x:c>
       <x:c r="E147" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F147" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/11646</x:v>
+        <x:v>https://www.goodsmile.com/en/product/12384</x:v>
       </x:c>
       <x:c r="G147" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H147" s="11" t="str">
-        <x:v>gsc-harmonia-11646</x:v>
+        <x:v>gsc-harmonia-12384</x:v>
       </x:c>
     </x:row>
     <x:row r="148" ht="72" customHeight="1">
       <x:c r="A148" s="11" t="str">
-        <x:v>Harmonia bloom Seasonal 服装套装 Gabriela (Black)</x:v>
+        <x:v>Harmonia bloom Volker Honest hunter</x:v>
       </x:c>
       <x:c r="B148" s="11" t="str">
         <x:v>主来源</x:v>
@@ -21415,24 +21560,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D148" s="11" t="str">
-        <x:v>Harmonia bloom Seasonal Outfit Set Gabriela (Black)</x:v>
+        <x:v>Harmonia bloom Volker Honest hunter</x:v>
       </x:c>
       <x:c r="E148" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F148" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/11648</x:v>
+        <x:v>https://www.goodsmile.com/en/product/12383</x:v>
       </x:c>
       <x:c r="G148" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H148" s="11" t="str">
-        <x:v>gsc-harmonia-11648</x:v>
+        <x:v>gsc-harmonia-12383</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="72" customHeight="1">
       <x:c r="A149" s="11" t="str">
-        <x:v>Harmonia bloom Seasonal 服装套装 Gabriela (White)</x:v>
+        <x:v>Harmonia bloom Seasonal 服装套装 Charlotte (Melone)</x:v>
       </x:c>
       <x:c r="B149" s="11" t="str">
         <x:v>主来源</x:v>
@@ -21441,24 +21586,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D149" s="11" t="str">
-        <x:v>Harmonia bloom Seasonal Outfit Set Gabriela (White)</x:v>
+        <x:v>Harmonia bloom Seasonal Outfit Set Charlotte (Melone)</x:v>
       </x:c>
       <x:c r="E149" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F149" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/11649</x:v>
+        <x:v>https://www.goodsmile.com/en/product/12085</x:v>
       </x:c>
       <x:c r="G149" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H149" s="11" t="str">
-        <x:v>gsc-harmonia-11649</x:v>
+        <x:v>gsc-harmonia-12085</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="72" customHeight="1">
       <x:c r="A150" s="11" t="str">
-        <x:v>Harmonia bloom Masie Red Riding Hood</x:v>
+        <x:v>Harmonia bloom Seasonal 服装套装 Charlotte (Kirsche)</x:v>
       </x:c>
       <x:c r="B150" s="11" t="str">
         <x:v>主来源</x:v>
@@ -21467,24 +21612,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D150" s="11" t="str">
-        <x:v>Harmonia bloom Masie Red Riding Hood</x:v>
+        <x:v>Harmonia bloom Seasonal Outfit Set Charlotte (Kirsche)</x:v>
       </x:c>
       <x:c r="E150" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F150" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/11338</x:v>
+        <x:v>https://www.goodsmile.com/en/product/12086</x:v>
       </x:c>
       <x:c r="G150" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H150" s="11" t="str">
-        <x:v>gsc-harmonia-11338</x:v>
+        <x:v>gsc-harmonia-12086</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="72" customHeight="1">
       <x:c r="A151" s="11" t="str">
-        <x:v>Harmonia bloom Christmas Limited Box (Rose/Pansy/Somei Yoshino/Madonna Lily)</x:v>
+        <x:v>Harmonia humming Nadeshiko Kagamihara</x:v>
       </x:c>
       <x:c r="B151" s="11" t="str">
         <x:v>主来源</x:v>
@@ -21493,24 +21638,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D151" s="11" t="str">
-        <x:v>Harmonia bloom Christmas Limited Box (Rose/Pansy/Somei Yoshino/Madonna Lily)</x:v>
+        <x:v>Harmonia humming Nadeshiko Kagamihara</x:v>
       </x:c>
       <x:c r="E151" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F151" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/11307</x:v>
+        <x:v>https://www.goodsmile.com/en/product/11731</x:v>
       </x:c>
       <x:c r="G151" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H151" s="11" t="str">
-        <x:v>gsc-harmonia-11307</x:v>
+        <x:v>gsc-harmonia-11731</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="72" customHeight="1">
       <x:c r="A152" s="11" t="str">
-        <x:v>Harmonia humming humming doll (Natural) #0</x:v>
+        <x:v>Harmonia humming Rin Shima</x:v>
       </x:c>
       <x:c r="B152" s="11" t="str">
         <x:v>主来源</x:v>
@@ -21519,24 +21664,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D152" s="11" t="str">
-        <x:v>Harmonia humming humming doll (Natural) #0</x:v>
+        <x:v>Harmonia humming Rin Shima</x:v>
       </x:c>
       <x:c r="E152" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F152" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/10492</x:v>
+        <x:v>https://www.goodsmile.com/en/product/11732</x:v>
       </x:c>
       <x:c r="G152" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H152" s="11" t="str">
-        <x:v>gsc-harmonia-10492</x:v>
+        <x:v>gsc-harmonia-11732</x:v>
       </x:c>
     </x:row>
     <x:row r="153" ht="72" customHeight="1">
       <x:c r="A153" s="11" t="str">
-        <x:v>Harmonia humming humming doll (Sharp) #0</x:v>
+        <x:v>Harmonia bloom Seasonal Doll Gabriela</x:v>
       </x:c>
       <x:c r="B153" s="11" t="str">
         <x:v>主来源</x:v>
@@ -21545,24 +21690,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D153" s="11" t="str">
-        <x:v>Harmonia humming humming doll (Sharp) #0</x:v>
+        <x:v>Harmonia bloom Seasonal Doll Gabriela</x:v>
       </x:c>
       <x:c r="E153" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F153" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/10493</x:v>
+        <x:v>https://www.goodsmile.com/en/product/11646</x:v>
       </x:c>
       <x:c r="G153" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H153" s="11" t="str">
-        <x:v>gsc-harmonia-10493</x:v>
+        <x:v>gsc-harmonia-11646</x:v>
       </x:c>
     </x:row>
     <x:row r="154" ht="72" customHeight="1">
       <x:c r="A154" s="11" t="str">
-        <x:v>figma Hunter: The Old Hunters Edition</x:v>
+        <x:v>Harmonia bloom Seasonal 服装套装 Gabriela (Black)</x:v>
       </x:c>
       <x:c r="B154" s="11" t="str">
         <x:v>主来源</x:v>
@@ -21571,24 +21716,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D154" s="11" t="str">
-        <x:v>figma Hunter: The Old Hunters Edition</x:v>
+        <x:v>Harmonia bloom Seasonal Outfit Set Gabriela (Black)</x:v>
       </x:c>
       <x:c r="E154" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F154" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/8648</x:v>
+        <x:v>https://www.goodsmile.com/en/product/11648</x:v>
       </x:c>
       <x:c r="G154" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H154" s="11" t="str">
-        <x:v>gsc-figma-8648</x:v>
+        <x:v>gsc-harmonia-11648</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="72" customHeight="1">
       <x:c r="A155" s="11" t="str">
-        <x:v>figma 2B (YoRHa No.2 Type B)</x:v>
+        <x:v>Harmonia bloom Seasonal 服装套装 Gabriela (White)</x:v>
       </x:c>
       <x:c r="B155" s="11" t="str">
         <x:v>主来源</x:v>
@@ -21597,24 +21742,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D155" s="11" t="str">
-        <x:v>figma 2B (YoRHa No.2 Type B)</x:v>
+        <x:v>Harmonia bloom Seasonal Outfit Set Gabriela (White)</x:v>
       </x:c>
       <x:c r="E155" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F155" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/45954</x:v>
+        <x:v>https://www.goodsmile.com/en/product/11649</x:v>
       </x:c>
       <x:c r="G155" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H155" s="11" t="str">
-        <x:v>gsc-figma-45954</x:v>
+        <x:v>gsc-harmonia-11649</x:v>
       </x:c>
     </x:row>
     <x:row r="156" ht="72" customHeight="1">
       <x:c r="A156" s="11" t="str">
-        <x:v>figma Soda: Twinkling Bunny</x:v>
+        <x:v>Harmonia bloom Masie Red Riding Hood</x:v>
       </x:c>
       <x:c r="B156" s="11" t="str">
         <x:v>主来源</x:v>
@@ -21623,24 +21768,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D156" s="11" t="str">
-        <x:v>figma Soda: Twinkling Bunny</x:v>
+        <x:v>Harmonia bloom Masie Red Riding Hood</x:v>
       </x:c>
       <x:c r="E156" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F156" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1145974</x:v>
+        <x:v>https://www.goodsmile.com/en/product/11338</x:v>
       </x:c>
       <x:c r="G156" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H156" s="11" t="str">
-        <x:v>gsc-figma-1145974</x:v>
+        <x:v>gsc-harmonia-11338</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="72" customHeight="1">
       <x:c r="A157" s="11" t="str">
-        <x:v>figma Venus de Milo</x:v>
+        <x:v>Harmonia bloom Christmas Limited Box (Rose/Pansy/Somei Yoshino/Madonna Lily)</x:v>
       </x:c>
       <x:c r="B157" s="11" t="str">
         <x:v>主来源</x:v>
@@ -21649,24 +21794,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D157" s="11" t="str">
-        <x:v>figma Venus de Milo</x:v>
+        <x:v>Harmonia bloom Christmas Limited Box (Rose/Pansy/Somei Yoshino/Madonna Lily)</x:v>
       </x:c>
       <x:c r="E157" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F157" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/2857</x:v>
+        <x:v>https://www.goodsmile.com/en/product/11307</x:v>
       </x:c>
       <x:c r="G157" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H157" s="11" t="str">
-        <x:v>gsc-figma-2857</x:v>
+        <x:v>gsc-harmonia-11307</x:v>
       </x:c>
     </x:row>
     <x:row r="158" ht="72" customHeight="1">
       <x:c r="A158" s="11" t="str">
-        <x:v>figma Leopard</x:v>
+        <x:v>Harmonia humming humming doll (Natural) #0</x:v>
       </x:c>
       <x:c r="B158" s="11" t="str">
         <x:v>主来源</x:v>
@@ -21675,24 +21820,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D158" s="11" t="str">
-        <x:v>figma Leopard</x:v>
+        <x:v>Harmonia humming humming doll (Natural) #0</x:v>
       </x:c>
       <x:c r="E158" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F158" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1137608</x:v>
+        <x:v>https://www.goodsmile.com/en/product/10492</x:v>
       </x:c>
       <x:c r="G158" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H158" s="11" t="str">
-        <x:v>gsc-figma-1137608</x:v>
+        <x:v>gsc-harmonia-10492</x:v>
       </x:c>
     </x:row>
     <x:row r="159" ht="72" customHeight="1">
       <x:c r="A159" s="11" t="str">
-        <x:v>figma Kana</x:v>
+        <x:v>Harmonia humming humming doll (Sharp) #0</x:v>
       </x:c>
       <x:c r="B159" s="11" t="str">
         <x:v>主来源</x:v>
@@ -21701,24 +21846,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D159" s="11" t="str">
-        <x:v>figma Kana</x:v>
+        <x:v>Harmonia humming humming doll (Sharp) #0</x:v>
       </x:c>
       <x:c r="E159" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F159" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1146142</x:v>
+        <x:v>https://www.goodsmile.com/en/product/10493</x:v>
       </x:c>
       <x:c r="G159" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H159" s="11" t="str">
-        <x:v>gsc-figma-1146142</x:v>
+        <x:v>gsc-harmonia-10493</x:v>
       </x:c>
     </x:row>
     <x:row r="160" ht="72" customHeight="1">
       <x:c r="A160" s="11" t="str">
-        <x:v>figma Panty &amp; Stocking: Angel ver. Set</x:v>
+        <x:v>figma Hunter: The Old Hunters Edition</x:v>
       </x:c>
       <x:c r="B160" s="11" t="str">
         <x:v>主来源</x:v>
@@ -21727,24 +21872,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D160" s="11" t="str">
-        <x:v>figma Panty &amp; Stocking: Angel ver. Set</x:v>
+        <x:v>figma Hunter: The Old Hunters Edition</x:v>
       </x:c>
       <x:c r="E160" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F160" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1146353</x:v>
+        <x:v>https://www.goodsmile.com/en/product/8648</x:v>
       </x:c>
       <x:c r="G160" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H160" s="11" t="str">
-        <x:v>gsc-figma-1146353</x:v>
+        <x:v>gsc-figma-8648</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="72" customHeight="1">
       <x:c r="A161" s="11" t="str">
-        <x:v>figma Panty: Angel ver.</x:v>
+        <x:v>figma 2B (YoRHa No.2 Type B)</x:v>
       </x:c>
       <x:c r="B161" s="11" t="str">
         <x:v>主来源</x:v>
@@ -21753,24 +21898,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D161" s="11" t="str">
-        <x:v>figma Panty: Angel ver.</x:v>
+        <x:v>figma 2B (YoRHa No.2 Type B)</x:v>
       </x:c>
       <x:c r="E161" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F161" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1137998</x:v>
+        <x:v>https://www.goodsmile.com/en/product/45954</x:v>
       </x:c>
       <x:c r="G161" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H161" s="11" t="str">
-        <x:v>gsc-figma-1137998</x:v>
+        <x:v>gsc-figma-45954</x:v>
       </x:c>
     </x:row>
     <x:row r="162" ht="72" customHeight="1">
       <x:c r="A162" s="11" t="str">
-        <x:v>figma Stocking: Angel ver.</x:v>
+        <x:v>figma Soda: Twinkling Bunny</x:v>
       </x:c>
       <x:c r="B162" s="11" t="str">
         <x:v>主来源</x:v>
@@ -21779,24 +21924,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D162" s="11" t="str">
-        <x:v>figma Stocking: Angel ver.</x:v>
+        <x:v>figma Soda: Twinkling Bunny</x:v>
       </x:c>
       <x:c r="E162" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F162" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1137999</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1145974</x:v>
       </x:c>
       <x:c r="G162" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H162" s="11" t="str">
-        <x:v>gsc-figma-1137999</x:v>
+        <x:v>gsc-figma-1145974</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="72" customHeight="1">
       <x:c r="A163" s="11" t="str">
-        <x:v>figma Noa Ushio</x:v>
+        <x:v>figma Venus de Milo</x:v>
       </x:c>
       <x:c r="B163" s="11" t="str">
         <x:v>主来源</x:v>
@@ -21805,24 +21950,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D163" s="11" t="str">
-        <x:v>figma Noa Ushio</x:v>
+        <x:v>figma Venus de Milo</x:v>
       </x:c>
       <x:c r="E163" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F163" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1137995</x:v>
+        <x:v>https://www.goodsmile.com/en/product/2857</x:v>
       </x:c>
       <x:c r="G163" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H163" s="11" t="str">
-        <x:v>gsc-figma-1137995</x:v>
+        <x:v>gsc-figma-2857</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="72" customHeight="1">
       <x:c r="A164" s="11" t="str">
-        <x:v>figma Anis: Sparkling Summer</x:v>
+        <x:v>figma Leopard</x:v>
       </x:c>
       <x:c r="B164" s="11" t="str">
         <x:v>主来源</x:v>
@@ -21831,24 +21976,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D164" s="11" t="str">
-        <x:v>figma Anis: Sparkling Summer</x:v>
+        <x:v>figma Leopard</x:v>
       </x:c>
       <x:c r="E164" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F164" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1145947</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1137608</x:v>
       </x:c>
       <x:c r="G164" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H164" s="11" t="str">
-        <x:v>gsc-figma-1145947</x:v>
+        <x:v>gsc-figma-1137608</x:v>
       </x:c>
     </x:row>
     <x:row r="165" ht="72" customHeight="1">
       <x:c r="A165" s="11" t="str">
-        <x:v>figma Nekomata Okayu</x:v>
+        <x:v>figma Kana</x:v>
       </x:c>
       <x:c r="B165" s="11" t="str">
         <x:v>主来源</x:v>
@@ -21857,24 +22002,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D165" s="11" t="str">
-        <x:v>figma Nekomata Okayu</x:v>
+        <x:v>figma Kana</x:v>
       </x:c>
       <x:c r="E165" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F165" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1143910</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1146142</x:v>
       </x:c>
       <x:c r="G165" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H165" s="11" t="str">
-        <x:v>gsc-figma-1143910</x:v>
+        <x:v>gsc-figma-1146142</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="72" customHeight="1">
       <x:c r="A166" s="11" t="str">
-        <x:v>figma Umamusume: Pretty Derby Nice Nature</x:v>
+        <x:v>figma Panty &amp; Stocking: Angel ver. Set</x:v>
       </x:c>
       <x:c r="B166" s="11" t="str">
         <x:v>主来源</x:v>
@@ -21883,24 +22028,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D166" s="11" t="str">
-        <x:v>figma Umamusume: Pretty Derby Nice Nature</x:v>
+        <x:v>figma Panty &amp; Stocking: Angel ver. Set</x:v>
       </x:c>
       <x:c r="E166" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F166" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/12485</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1146353</x:v>
       </x:c>
       <x:c r="G166" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H166" s="11" t="str">
-        <x:v>gsc-figma-12485</x:v>
+        <x:v>gsc-figma-1146353</x:v>
       </x:c>
     </x:row>
     <x:row r="167" ht="72" customHeight="1">
       <x:c r="A167" s="11" t="str">
-        <x:v>figma Lucifer</x:v>
+        <x:v>figma Panty: Angel ver.</x:v>
       </x:c>
       <x:c r="B167" s="11" t="str">
         <x:v>主来源</x:v>
@@ -21909,24 +22054,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D167" s="11" t="str">
-        <x:v>figma Lucifer</x:v>
+        <x:v>figma Panty: Angel ver.</x:v>
       </x:c>
       <x:c r="E167" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F167" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1137486</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1137998</x:v>
       </x:c>
       <x:c r="G167" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H167" s="11" t="str">
-        <x:v>gsc-figma-1137486</x:v>
+        <x:v>gsc-figma-1137998</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="72" customHeight="1">
       <x:c r="A168" s="11" t="str">
-        <x:v>figma Veronica Sweetheart: Swimsuit Ver.</x:v>
+        <x:v>figma Stocking: Angel ver.</x:v>
       </x:c>
       <x:c r="B168" s="11" t="str">
         <x:v>主来源</x:v>
@@ -21935,24 +22080,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D168" s="11" t="str">
-        <x:v>figma Veronica Sweetheart: Swimsuit Ver.</x:v>
+        <x:v>figma Stocking: Angel ver.</x:v>
       </x:c>
       <x:c r="E168" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F168" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1142705</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1137999</x:v>
       </x:c>
       <x:c r="G168" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H168" s="11" t="str">
-        <x:v>gsc-figma-1142705</x:v>
+        <x:v>gsc-figma-1137999</x:v>
       </x:c>
     </x:row>
     <x:row r="169" ht="72" customHeight="1">
       <x:c r="A169" s="11" t="str">
-        <x:v>figma Ena Toyosaki ver. 1.5</x:v>
+        <x:v>figma Noa Ushio</x:v>
       </x:c>
       <x:c r="B169" s="11" t="str">
         <x:v>主来源</x:v>
@@ -21961,24 +22106,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D169" s="11" t="str">
-        <x:v>figma Ena Toyosaki ver. 1.5</x:v>
+        <x:v>figma Noa Ushio</x:v>
       </x:c>
       <x:c r="E169" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F169" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1146176</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1137995</x:v>
       </x:c>
       <x:c r="G169" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H169" s="11" t="str">
-        <x:v>gsc-figma-1146176</x:v>
+        <x:v>gsc-figma-1137995</x:v>
       </x:c>
     </x:row>
     <x:row r="170" ht="72" customHeight="1">
       <x:c r="A170" s="11" t="str">
-        <x:v>figma Miyo Asato: Summer Uniform ver. 1.5</x:v>
+        <x:v>figma Anis: Sparkling Summer</x:v>
       </x:c>
       <x:c r="B170" s="11" t="str">
         <x:v>主来源</x:v>
@@ -21987,24 +22132,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D170" s="11" t="str">
-        <x:v>figma Miyo Asato: Summer Uniform ver. 1.5</x:v>
+        <x:v>figma Anis: Sparkling Summer</x:v>
       </x:c>
       <x:c r="E170" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F170" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1146175</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1145947</x:v>
       </x:c>
       <x:c r="G170" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H170" s="11" t="str">
-        <x:v>gsc-figma-1146175</x:v>
+        <x:v>gsc-figma-1145947</x:v>
       </x:c>
     </x:row>
     <x:row r="171" ht="72" customHeight="1">
       <x:c r="A171" s="11" t="str">
-        <x:v>figma Albedo</x:v>
+        <x:v>figma Nekomata Okayu</x:v>
       </x:c>
       <x:c r="B171" s="11" t="str">
         <x:v>主来源</x:v>
@@ -22013,24 +22158,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D171" s="11" t="str">
-        <x:v>figma Albedo</x:v>
+        <x:v>figma Nekomata Okayu</x:v>
       </x:c>
       <x:c r="E171" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F171" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/62125</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1143910</x:v>
       </x:c>
       <x:c r="G171" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H171" s="11" t="str">
-        <x:v>gsc-figma-62125</x:v>
+        <x:v>gsc-figma-1143910</x:v>
       </x:c>
     </x:row>
     <x:row r="172" ht="72" customHeight="1">
       <x:c r="A172" s="11" t="str">
-        <x:v>figma Angel Statues</x:v>
+        <x:v>figma Umamusume: Pretty Derby Nice Nature</x:v>
       </x:c>
       <x:c r="B172" s="11" t="str">
         <x:v>主来源</x:v>
@@ -22039,24 +22184,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D172" s="11" t="str">
-        <x:v>figma Angel Statues</x:v>
+        <x:v>figma Umamusume: Pretty Derby Nice Nature</x:v>
       </x:c>
       <x:c r="E172" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F172" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/3509</x:v>
+        <x:v>https://www.goodsmile.com/en/product/12485</x:v>
       </x:c>
       <x:c r="G172" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H172" s="11" t="str">
-        <x:v>gsc-figma-3509</x:v>
+        <x:v>gsc-figma-12485</x:v>
       </x:c>
     </x:row>
     <x:row r="173" ht="72" customHeight="1">
       <x:c r="A173" s="11" t="str">
-        <x:v>figma Nanachi</x:v>
+        <x:v>figma Lucifer</x:v>
       </x:c>
       <x:c r="B173" s="11" t="str">
         <x:v>主来源</x:v>
@@ -22065,24 +22210,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D173" s="11" t="str">
-        <x:v>figma Nanachi</x:v>
+        <x:v>figma Lucifer</x:v>
       </x:c>
       <x:c r="E173" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F173" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/60700</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1137486</x:v>
       </x:c>
       <x:c r="G173" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H173" s="11" t="str">
-        <x:v>gsc-figma-60700</x:v>
+        <x:v>gsc-figma-1137486</x:v>
       </x:c>
     </x:row>
     <x:row r="174" ht="72" customHeight="1">
       <x:c r="A174" s="11" t="str">
-        <x:v>figma Magia Baiser</x:v>
+        <x:v>figma Veronica Sweetheart: Swimsuit Ver.</x:v>
       </x:c>
       <x:c r="B174" s="11" t="str">
         <x:v>主来源</x:v>
@@ -22091,24 +22236,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D174" s="11" t="str">
-        <x:v>figma Magia Baiser</x:v>
+        <x:v>figma Veronica Sweetheart: Swimsuit Ver.</x:v>
       </x:c>
       <x:c r="E174" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F174" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1137492</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1142705</x:v>
       </x:c>
       <x:c r="G174" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H174" s="11" t="str">
-        <x:v>gsc-figma-1137492</x:v>
+        <x:v>gsc-figma-1142705</x:v>
       </x:c>
     </x:row>
     <x:row r="175" ht="72" customHeight="1">
       <x:c r="A175" s="11" t="str">
-        <x:v>figma Yuriko Okada: Electro-Wave Human Tackle Ver.</x:v>
+        <x:v>figma Ena Toyosaki ver. 1.5</x:v>
       </x:c>
       <x:c r="B175" s="11" t="str">
         <x:v>主来源</x:v>
@@ -22117,24 +22262,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D175" s="11" t="str">
-        <x:v>figma Yuriko Okada: Electro-Wave Human Tackle Ver.</x:v>
+        <x:v>figma Ena Toyosaki ver. 1.5</x:v>
       </x:c>
       <x:c r="E175" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F175" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1141915</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1146176</x:v>
       </x:c>
       <x:c r="G175" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H175" s="11" t="str">
-        <x:v>gsc-figma-1141915</x:v>
+        <x:v>gsc-figma-1146176</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="72" customHeight="1">
       <x:c r="A176" s="11" t="str">
-        <x:v>figma Seia Yurizono</x:v>
+        <x:v>figma Miyo Asato: Summer Uniform ver. 1.5</x:v>
       </x:c>
       <x:c r="B176" s="11" t="str">
         <x:v>主来源</x:v>
@@ -22143,24 +22288,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D176" s="11" t="str">
-        <x:v>figma Seia Yurizono</x:v>
+        <x:v>figma Miyo Asato: Summer Uniform ver. 1.5</x:v>
       </x:c>
       <x:c r="E176" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F176" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1144554</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1146175</x:v>
       </x:c>
       <x:c r="G176" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H176" s="11" t="str">
-        <x:v>gsc-figma-1144554</x:v>
+        <x:v>gsc-figma-1146175</x:v>
       </x:c>
     </x:row>
     <x:row r="177" ht="72" customHeight="1">
       <x:c r="A177" s="11" t="str">
-        <x:v>figma Guyver III: Ultimate Edition</x:v>
+        <x:v>figma Albedo</x:v>
       </x:c>
       <x:c r="B177" s="11" t="str">
         <x:v>主来源</x:v>
@@ -22169,24 +22314,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D177" s="11" t="str">
-        <x:v>figma Guyver III: Ultimate Edition</x:v>
+        <x:v>figma Albedo</x:v>
       </x:c>
       <x:c r="E177" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F177" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1143909</x:v>
+        <x:v>https://www.goodsmile.com/en/product/62125</x:v>
       </x:c>
       <x:c r="G177" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H177" s="11" t="str">
-        <x:v>gsc-figma-1143909</x:v>
+        <x:v>gsc-figma-62125</x:v>
       </x:c>
     </x:row>
     <x:row r="178" ht="72" customHeight="1">
       <x:c r="A178" s="11" t="str">
-        <x:v>figma Tanya Degurechaff</x:v>
+        <x:v>figma Angel Statues</x:v>
       </x:c>
       <x:c r="B178" s="11" t="str">
         <x:v>主来源</x:v>
@@ -22195,24 +22340,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D178" s="11" t="str">
-        <x:v>figma Tanya Degurechaff</x:v>
+        <x:v>figma Angel Statues</x:v>
       </x:c>
       <x:c r="E178" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F178" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/6055</x:v>
+        <x:v>https://www.goodsmile.com/en/product/3509</x:v>
       </x:c>
       <x:c r="G178" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H178" s="11" t="str">
-        <x:v>gsc-figma-6055</x:v>
+        <x:v>gsc-figma-3509</x:v>
       </x:c>
     </x:row>
     <x:row r="179" ht="72" customHeight="1">
       <x:c r="A179" s="11" t="str">
-        <x:v>figma Kayoko Onikata</x:v>
+        <x:v>figma Nanachi</x:v>
       </x:c>
       <x:c r="B179" s="11" t="str">
         <x:v>主来源</x:v>
@@ -22221,24 +22366,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D179" s="11" t="str">
-        <x:v>figma Kayoko Onikata</x:v>
+        <x:v>figma Nanachi</x:v>
       </x:c>
       <x:c r="E179" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F179" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1142700</x:v>
+        <x:v>https://www.goodsmile.com/en/product/60700</x:v>
       </x:c>
       <x:c r="G179" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H179" s="11" t="str">
-        <x:v>gsc-figma-1142700</x:v>
+        <x:v>gsc-figma-60700</x:v>
       </x:c>
     </x:row>
     <x:row r="180" ht="72" customHeight="1">
       <x:c r="A180" s="11" t="str">
-        <x:v>figma Valby</x:v>
+        <x:v>figma Magia Baiser</x:v>
       </x:c>
       <x:c r="B180" s="11" t="str">
         <x:v>主来源</x:v>
@@ -22247,24 +22392,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D180" s="11" t="str">
-        <x:v>figma Valby</x:v>
+        <x:v>figma Magia Baiser</x:v>
       </x:c>
       <x:c r="E180" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F180" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1144552</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1137492</x:v>
       </x:c>
       <x:c r="G180" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H180" s="11" t="str">
-        <x:v>gsc-figma-1144552</x:v>
+        <x:v>gsc-figma-1137492</x:v>
       </x:c>
     </x:row>
     <x:row r="181" ht="72" customHeight="1">
       <x:c r="A181" s="11" t="str">
-        <x:v>figma Shiroko*Terror</x:v>
+        <x:v>figma Yuriko Okada: Electro-Wave Human Tackle Ver.</x:v>
       </x:c>
       <x:c r="B181" s="11" t="str">
         <x:v>主来源</x:v>
@@ -22273,24 +22418,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D181" s="11" t="str">
-        <x:v>figma Shiroko*Terror</x:v>
+        <x:v>figma Yuriko Okada: Electro-Wave Human Tackle Ver.</x:v>
       </x:c>
       <x:c r="E181" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F181" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1137994</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1141915</x:v>
       </x:c>
       <x:c r="G181" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H181" s="11" t="str">
-        <x:v>gsc-figma-1137994</x:v>
+        <x:v>gsc-figma-1141915</x:v>
       </x:c>
     </x:row>
     <x:row r="182" ht="72" customHeight="1">
       <x:c r="A182" s="11" t="str">
-        <x:v>figma Klukai</x:v>
+        <x:v>figma Seia Yurizono</x:v>
       </x:c>
       <x:c r="B182" s="11" t="str">
         <x:v>主来源</x:v>
@@ -22299,24 +22444,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D182" s="11" t="str">
-        <x:v>figma Klukai</x:v>
+        <x:v>figma Seia Yurizono</x:v>
       </x:c>
       <x:c r="E182" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F182" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1142692</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1144554</x:v>
       </x:c>
       <x:c r="G182" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H182" s="11" t="str">
-        <x:v>gsc-figma-1142692</x:v>
+        <x:v>gsc-figma-1144554</x:v>
       </x:c>
     </x:row>
     <x:row r="183" ht="72" customHeight="1">
       <x:c r="A183" s="11" t="str">
-        <x:v>figma Winged Victory of Samothrace</x:v>
+        <x:v>figma Guyver III: Ultimate Edition</x:v>
       </x:c>
       <x:c r="B183" s="11" t="str">
         <x:v>主来源</x:v>
@@ -22325,24 +22470,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D183" s="11" t="str">
-        <x:v>figma Winged Victory of Samothrace</x:v>
+        <x:v>figma Guyver III: Ultimate Edition</x:v>
       </x:c>
       <x:c r="E183" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F183" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/5038</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1143909</x:v>
       </x:c>
       <x:c r="G183" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H183" s="11" t="str">
-        <x:v>gsc-figma-5038</x:v>
+        <x:v>gsc-figma-1143909</x:v>
       </x:c>
     </x:row>
     <x:row r="184" ht="72" customHeight="1">
       <x:c r="A184" s="11" t="str">
-        <x:v>figma Silva Barrelline</x:v>
+        <x:v>figma Tanya Degurechaff</x:v>
       </x:c>
       <x:c r="B184" s="11" t="str">
         <x:v>主来源</x:v>
@@ -22351,24 +22496,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D184" s="11" t="str">
-        <x:v>figma Silva Barrelline</x:v>
+        <x:v>figma Tanya Degurechaff</x:v>
       </x:c>
       <x:c r="E184" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F184" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1142704</x:v>
+        <x:v>https://www.goodsmile.com/en/product/6055</x:v>
       </x:c>
       <x:c r="G184" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H184" s="11" t="str">
-        <x:v>gsc-figma-1142704</x:v>
+        <x:v>gsc-figma-6055</x:v>
       </x:c>
     </x:row>
     <x:row r="185" ht="72" customHeight="1">
       <x:c r="A185" s="11" t="str">
-        <x:v>figma Bridget</x:v>
+        <x:v>figma Kayoko Onikata</x:v>
       </x:c>
       <x:c r="B185" s="11" t="str">
         <x:v>主来源</x:v>
@@ -22377,24 +22522,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D185" s="11" t="str">
-        <x:v>figma Bridget</x:v>
+        <x:v>figma Kayoko Onikata</x:v>
       </x:c>
       <x:c r="E185" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F185" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1137488</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1142700</x:v>
       </x:c>
       <x:c r="G185" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H185" s="11" t="str">
-        <x:v>gsc-figma-1137488</x:v>
+        <x:v>gsc-figma-1142700</x:v>
       </x:c>
     </x:row>
     <x:row r="186" ht="72" customHeight="1">
       <x:c r="A186" s="11" t="str">
-        <x:v>figma Yuuka Hayase</x:v>
+        <x:v>figma Valby</x:v>
       </x:c>
       <x:c r="B186" s="11" t="str">
         <x:v>主来源</x:v>
@@ -22403,24 +22548,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D186" s="11" t="str">
-        <x:v>figma Yuuka Hayase</x:v>
+        <x:v>figma Valby</x:v>
       </x:c>
       <x:c r="E186" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F186" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/60342</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1144552</x:v>
       </x:c>
       <x:c r="G186" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H186" s="11" t="str">
-        <x:v>gsc-figma-60342</x:v>
+        <x:v>gsc-figma-1144552</x:v>
       </x:c>
     </x:row>
     <x:row r="187" ht="72" customHeight="1">
       <x:c r="A187" s="11" t="str">
-        <x:v>figma Ruka</x:v>
+        <x:v>figma Shiroko*Terror</x:v>
       </x:c>
       <x:c r="B187" s="11" t="str">
         <x:v>主来源</x:v>
@@ -22429,24 +22574,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D187" s="11" t="str">
-        <x:v>figma Ruka</x:v>
+        <x:v>figma Shiroko*Terror</x:v>
       </x:c>
       <x:c r="E187" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F187" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1142693</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1137994</x:v>
       </x:c>
       <x:c r="G187" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H187" s="11" t="str">
-        <x:v>gsc-figma-1142693</x:v>
+        <x:v>gsc-figma-1137994</x:v>
       </x:c>
     </x:row>
     <x:row r="188" ht="72" customHeight="1">
       <x:c r="A188" s="11" t="str">
-        <x:v>figma Saori Joumae</x:v>
+        <x:v>figma Klukai</x:v>
       </x:c>
       <x:c r="B188" s="11" t="str">
         <x:v>主来源</x:v>
@@ -22455,24 +22600,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D188" s="11" t="str">
-        <x:v>figma Saori Joumae</x:v>
+        <x:v>figma Klukai</x:v>
       </x:c>
       <x:c r="E188" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F188" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1137997</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1142692</x:v>
       </x:c>
       <x:c r="G188" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H188" s="11" t="str">
-        <x:v>gsc-figma-1137997</x:v>
+        <x:v>gsc-figma-1142692</x:v>
       </x:c>
     </x:row>
     <x:row r="189" ht="72" customHeight="1">
       <x:c r="A189" s="11" t="str">
-        <x:v>figma Raging Wolf</x:v>
+        <x:v>figma Winged Victory of Samothrace</x:v>
       </x:c>
       <x:c r="B189" s="11" t="str">
         <x:v>主来源</x:v>
@@ -22481,24 +22626,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D189" s="11" t="str">
-        <x:v>figma Raging Wolf</x:v>
+        <x:v>figma Winged Victory of Samothrace</x:v>
       </x:c>
       <x:c r="E189" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F189" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/55941</x:v>
+        <x:v>https://www.goodsmile.com/en/product/5038</x:v>
       </x:c>
       <x:c r="G189" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H189" s="11" t="str">
-        <x:v>gsc-figma-55941</x:v>
+        <x:v>gsc-figma-5038</x:v>
       </x:c>
     </x:row>
     <x:row r="190" ht="72" customHeight="1">
       <x:c r="A190" s="11" t="str">
-        <x:v>figma Lancer/Scáthach</x:v>
+        <x:v>figma Silva Barrelline</x:v>
       </x:c>
       <x:c r="B190" s="11" t="str">
         <x:v>主来源</x:v>
@@ -22507,24 +22652,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D190" s="11" t="str">
-        <x:v>figma Lancer/Scáthach</x:v>
+        <x:v>figma Silva Barrelline</x:v>
       </x:c>
       <x:c r="E190" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F190" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/4722</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1142704</x:v>
       </x:c>
       <x:c r="G190" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H190" s="11" t="str">
-        <x:v>gsc-figma-4722</x:v>
+        <x:v>gsc-figma-1142704</x:v>
       </x:c>
     </x:row>
     <x:row r="191" ht="72" customHeight="1">
       <x:c r="A191" s="11" t="str">
-        <x:v>figma Pomni</x:v>
+        <x:v>figma Bridget</x:v>
       </x:c>
       <x:c r="B191" s="11" t="str">
         <x:v>主来源</x:v>
@@ -22533,24 +22678,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D191" s="11" t="str">
-        <x:v>figma Pomni</x:v>
+        <x:v>figma Bridget</x:v>
       </x:c>
       <x:c r="E191" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F191" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1144248</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1137488</x:v>
       </x:c>
       <x:c r="G191" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H191" s="11" t="str">
-        <x:v>gsc-figma-1144248</x:v>
+        <x:v>gsc-figma-1137488</x:v>
       </x:c>
     </x:row>
     <x:row r="192" ht="72" customHeight="1">
       <x:c r="A192" s="11" t="str">
-        <x:v>figma Tololo</x:v>
+        <x:v>figma Yuuka Hayase</x:v>
       </x:c>
       <x:c r="B192" s="11" t="str">
         <x:v>主来源</x:v>
@@ -22559,24 +22704,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D192" s="11" t="str">
-        <x:v>figma Tololo</x:v>
+        <x:v>figma Yuuka Hayase</x:v>
       </x:c>
       <x:c r="E192" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F192" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1142689</x:v>
+        <x:v>https://www.goodsmile.com/en/product/60342</x:v>
       </x:c>
       <x:c r="G192" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H192" s="11" t="str">
-        <x:v>gsc-figma-1142689</x:v>
+        <x:v>gsc-figma-60342</x:v>
       </x:c>
     </x:row>
     <x:row r="193" ht="72" customHeight="1">
       <x:c r="A193" s="11" t="str">
-        <x:v>POP UP PARADE Louise L Size</x:v>
+        <x:v>figma Ruka</x:v>
       </x:c>
       <x:c r="B193" s="11" t="str">
         <x:v>主来源</x:v>
@@ -22585,24 +22730,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D193" s="11" t="str">
-        <x:v>POP UP PARADE Louise L Size</x:v>
+        <x:v>figma Ruka</x:v>
       </x:c>
       <x:c r="E193" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F193" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1141520</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1142693</x:v>
       </x:c>
       <x:c r="G193" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H193" s="11" t="str">
-        <x:v>gsc-pop-1141520</x:v>
+        <x:v>gsc-figma-1142693</x:v>
       </x:c>
     </x:row>
     <x:row r="194" ht="72" customHeight="1">
       <x:c r="A194" s="11" t="str">
-        <x:v>POP UP PARADE lain iwakura L Size</x:v>
+        <x:v>figma Saori Joumae</x:v>
       </x:c>
       <x:c r="B194" s="11" t="str">
         <x:v>主来源</x:v>
@@ -22611,24 +22756,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D194" s="11" t="str">
-        <x:v>POP UP PARADE lain iwakura L Size</x:v>
+        <x:v>figma Saori Joumae</x:v>
       </x:c>
       <x:c r="E194" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F194" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1137445</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1137997</x:v>
       </x:c>
       <x:c r="G194" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H194" s="11" t="str">
-        <x:v>gsc-pop-1137445</x:v>
+        <x:v>gsc-figma-1137997</x:v>
       </x:c>
     </x:row>
     <x:row r="195" ht="72" customHeight="1">
       <x:c r="A195" s="11" t="str">
-        <x:v>POP UP PARADE 初音未来: DecoMiku (Lightness) L Size</x:v>
+        <x:v>figma Raging Wolf</x:v>
       </x:c>
       <x:c r="B195" s="11" t="str">
         <x:v>主来源</x:v>
@@ -22637,24 +22782,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D195" s="11" t="str">
-        <x:v>POP UP PARADE Hatsune Miku: DecoMiku (Lightness) L Size</x:v>
+        <x:v>figma Raging Wolf</x:v>
       </x:c>
       <x:c r="E195" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F195" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1141247</x:v>
+        <x:v>https://www.goodsmile.com/en/product/55941</x:v>
       </x:c>
       <x:c r="G195" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H195" s="11" t="str">
-        <x:v>gsc-pop-1141247</x:v>
+        <x:v>gsc-figma-55941</x:v>
       </x:c>
     </x:row>
     <x:row r="196" ht="72" customHeight="1">
       <x:c r="A196" s="11" t="str">
-        <x:v>POP UP PARADE 初音未来: DecoMiku (Darkness) L Size</x:v>
+        <x:v>figma Lancer/Scáthach</x:v>
       </x:c>
       <x:c r="B196" s="11" t="str">
         <x:v>主来源</x:v>
@@ -22663,24 +22808,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D196" s="11" t="str">
-        <x:v>POP UP PARADE Hatsune Miku: DecoMiku (Darkness) L Size</x:v>
+        <x:v>figma Lancer/Scáthach</x:v>
       </x:c>
       <x:c r="E196" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F196" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1141248</x:v>
+        <x:v>https://www.goodsmile.com/en/product/4722</x:v>
       </x:c>
       <x:c r="G196" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H196" s="11" t="str">
-        <x:v>gsc-pop-1141248</x:v>
+        <x:v>gsc-figma-4722</x:v>
       </x:c>
     </x:row>
     <x:row r="197" ht="72" customHeight="1">
       <x:c r="A197" s="11" t="str">
-        <x:v>POP UP PARADE Kasane Teto: Synthesizer V AI Ver. L Size</x:v>
+        <x:v>figma Pomni</x:v>
       </x:c>
       <x:c r="B197" s="11" t="str">
         <x:v>主来源</x:v>
@@ -22689,24 +22834,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D197" s="11" t="str">
-        <x:v>POP UP PARADE Kasane Teto: Synthesizer V AI Ver. L Size</x:v>
+        <x:v>figma Pomni</x:v>
       </x:c>
       <x:c r="E197" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F197" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1144430</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1144248</x:v>
       </x:c>
       <x:c r="G197" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H197" s="11" t="str">
-        <x:v>gsc-pop-1144430</x:v>
+        <x:v>gsc-figma-1144248</x:v>
       </x:c>
     </x:row>
     <x:row r="198" ht="72" customHeight="1">
       <x:c r="A198" s="11" t="str">
-        <x:v>POP UP PARADE Swacchao! Rikka Takarada: Pajamas Ver. XL Size</x:v>
+        <x:v>figma Tololo</x:v>
       </x:c>
       <x:c r="B198" s="11" t="str">
         <x:v>主来源</x:v>
@@ -22715,24 +22860,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D198" s="11" t="str">
-        <x:v>POP UP PARADE Swacchao! Rikka Takarada: Pajamas Ver. XL Size</x:v>
+        <x:v>figma Tololo</x:v>
       </x:c>
       <x:c r="E198" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F198" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1144464</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1142689</x:v>
       </x:c>
       <x:c r="G198" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H198" s="11" t="str">
-        <x:v>gsc-pop-1144464</x:v>
+        <x:v>gsc-figma-1142689</x:v>
       </x:c>
     </x:row>
     <x:row r="199" ht="72" customHeight="1">
       <x:c r="A199" s="11" t="str">
-        <x:v>POP UP PARADE Petite Speaki</x:v>
+        <x:v>POP UP PARADE Louise L Size</x:v>
       </x:c>
       <x:c r="B199" s="11" t="str">
         <x:v>主来源</x:v>
@@ -22741,24 +22886,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D199" s="11" t="str">
-        <x:v>POP UP PARADE Petite Speaki</x:v>
+        <x:v>POP UP PARADE Louise L Size</x:v>
       </x:c>
       <x:c r="E199" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F199" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1144852</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1141520</x:v>
       </x:c>
       <x:c r="G199" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H199" s="11" t="str">
-        <x:v>gsc-pop-1144852</x:v>
+        <x:v>gsc-pop-1141520</x:v>
       </x:c>
     </x:row>
     <x:row r="200" ht="72" customHeight="1">
       <x:c r="A200" s="11" t="str">
-        <x:v>POP UP PARADE Loona L Size</x:v>
+        <x:v>POP UP PARADE lain iwakura L Size</x:v>
       </x:c>
       <x:c r="B200" s="11" t="str">
         <x:v>主来源</x:v>
@@ -22767,24 +22912,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D200" s="11" t="str">
-        <x:v>POP UP PARADE Loona L Size</x:v>
+        <x:v>POP UP PARADE lain iwakura L Size</x:v>
       </x:c>
       <x:c r="E200" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F200" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1144959</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1137445</x:v>
       </x:c>
       <x:c r="G200" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H200" s="11" t="str">
-        <x:v>gsc-pop-1144959</x:v>
+        <x:v>gsc-pop-1137445</x:v>
       </x:c>
     </x:row>
     <x:row r="201" ht="72" customHeight="1">
       <x:c r="A201" s="11" t="str">
-        <x:v>POP UP PARADE SP Mihono Bourbon</x:v>
+        <x:v>POP UP PARADE 初音未来: DecoMiku (Lightness) L Size</x:v>
       </x:c>
       <x:c r="B201" s="11" t="str">
         <x:v>主来源</x:v>
@@ -22793,24 +22938,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D201" s="11" t="str">
-        <x:v>POP UP PARADE SP Mihono Bourbon</x:v>
+        <x:v>POP UP PARADE Hatsune Miku: DecoMiku (Lightness) L Size</x:v>
       </x:c>
       <x:c r="E201" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F201" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1136847</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1141247</x:v>
       </x:c>
       <x:c r="G201" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H201" s="11" t="str">
-        <x:v>gsc-pop-1136847</x:v>
+        <x:v>gsc-pop-1141247</x:v>
       </x:c>
     </x:row>
     <x:row r="202" ht="72" customHeight="1">
       <x:c r="A202" s="11" t="str">
-        <x:v>POP UP PARADE SP Jett</x:v>
+        <x:v>POP UP PARADE 初音未来: DecoMiku (Darkness) L Size</x:v>
       </x:c>
       <x:c r="B202" s="11" t="str">
         <x:v>主来源</x:v>
@@ -22819,24 +22964,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D202" s="11" t="str">
-        <x:v>POP UP PARADE SP Jett</x:v>
+        <x:v>POP UP PARADE Hatsune Miku: DecoMiku (Darkness) L Size</x:v>
       </x:c>
       <x:c r="E202" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F202" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1141572</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1141248</x:v>
       </x:c>
       <x:c r="G202" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H202" s="11" t="str">
-        <x:v>gsc-pop-1141572</x:v>
+        <x:v>gsc-pop-1141248</x:v>
       </x:c>
     </x:row>
     <x:row r="203" ht="72" customHeight="1">
       <x:c r="A203" s="11" t="str">
-        <x:v>POP UP PARADE Lucy L Size</x:v>
+        <x:v>POP UP PARADE Kasane Teto: Synthesizer V AI Ver. L Size</x:v>
       </x:c>
       <x:c r="B203" s="11" t="str">
         <x:v>主来源</x:v>
@@ -22845,24 +22990,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D203" s="11" t="str">
-        <x:v>POP UP PARADE Lucy L Size</x:v>
+        <x:v>POP UP PARADE Kasane Teto: Synthesizer V AI Ver. L Size</x:v>
       </x:c>
       <x:c r="E203" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F203" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1137607</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1144430</x:v>
       </x:c>
       <x:c r="G203" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H203" s="11" t="str">
-        <x:v>gsc-pop-1137607</x:v>
+        <x:v>gsc-pop-1144430</x:v>
       </x:c>
     </x:row>
     <x:row r="204" ht="72" customHeight="1">
       <x:c r="A204" s="11" t="str">
-        <x:v>POP UP PARADE Guts (Berserker Armor): Bloody Paint Ver. L Size</x:v>
+        <x:v>POP UP PARADE Swacchao! Rikka Takarada: Pajamas Ver. XL Size</x:v>
       </x:c>
       <x:c r="B204" s="11" t="str">
         <x:v>主来源</x:v>
@@ -22871,24 +23016,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D204" s="11" t="str">
-        <x:v>POP UP PARADE Guts (Berserker Armor): Bloody Paint Ver. L Size</x:v>
+        <x:v>POP UP PARADE Swacchao! Rikka Takarada: Pajamas Ver. XL Size</x:v>
       </x:c>
       <x:c r="E204" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F204" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1145852</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1144464</x:v>
       </x:c>
       <x:c r="G204" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H204" s="11" t="str">
-        <x:v>gsc-pop-1145852</x:v>
+        <x:v>gsc-pop-1144464</x:v>
       </x:c>
     </x:row>
     <x:row r="205" ht="72" customHeight="1">
       <x:c r="A205" s="11" t="str">
-        <x:v>POP UP PARADE 赛车初音: 2023 Ver.</x:v>
+        <x:v>POP UP PARADE Petite Speaki</x:v>
       </x:c>
       <x:c r="B205" s="11" t="str">
         <x:v>主来源</x:v>
@@ -22897,24 +23042,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D205" s="11" t="str">
-        <x:v>POP UP PARADE Racing Miku: 2023 Ver.</x:v>
+        <x:v>POP UP PARADE Petite Speaki</x:v>
       </x:c>
       <x:c r="E205" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F205" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/55958</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1144852</x:v>
       </x:c>
       <x:c r="G205" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H205" s="11" t="str">
-        <x:v>gsc-pop-55958</x:v>
+        <x:v>gsc-pop-1144852</x:v>
       </x:c>
     </x:row>
     <x:row r="206" ht="72" customHeight="1">
       <x:c r="A206" s="11" t="str">
-        <x:v>POP UP PARADE SP Momon</x:v>
+        <x:v>POP UP PARADE Loona L Size</x:v>
       </x:c>
       <x:c r="B206" s="11" t="str">
         <x:v>主来源</x:v>
@@ -22923,24 +23068,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D206" s="11" t="str">
-        <x:v>POP UP PARADE SP Momon</x:v>
+        <x:v>POP UP PARADE Loona L Size</x:v>
       </x:c>
       <x:c r="E206" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F206" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1139935</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1144959</x:v>
       </x:c>
       <x:c r="G206" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H206" s="11" t="str">
-        <x:v>gsc-pop-1139935</x:v>
+        <x:v>gsc-pop-1144959</x:v>
       </x:c>
     </x:row>
     <x:row r="207" ht="72" customHeight="1">
       <x:c r="A207" s="11" t="str">
-        <x:v>POP UP PARADE Daiwa Scarlet L Size</x:v>
+        <x:v>POP UP PARADE SP Mihono Bourbon</x:v>
       </x:c>
       <x:c r="B207" s="11" t="str">
         <x:v>主来源</x:v>
@@ -22949,24 +23094,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D207" s="11" t="str">
-        <x:v>POP UP PARADE Daiwa Scarlet L Size</x:v>
+        <x:v>POP UP PARADE SP Mihono Bourbon</x:v>
       </x:c>
       <x:c r="E207" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F207" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1136848</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1136847</x:v>
       </x:c>
       <x:c r="G207" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H207" s="11" t="str">
-        <x:v>gsc-pop-1136848</x:v>
+        <x:v>gsc-pop-1136847</x:v>
       </x:c>
     </x:row>
     <x:row r="208" ht="72" customHeight="1">
       <x:c r="A208" s="11" t="str">
-        <x:v>POP UP PARADE Dorothy Haze L Size</x:v>
+        <x:v>POP UP PARADE SP Jett</x:v>
       </x:c>
       <x:c r="B208" s="11" t="str">
         <x:v>主来源</x:v>
@@ -22975,24 +23120,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D208" s="11" t="str">
-        <x:v>POP UP PARADE Dorothy Haze L Size</x:v>
+        <x:v>POP UP PARADE SP Jett</x:v>
       </x:c>
       <x:c r="E208" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F208" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1139391</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1141572</x:v>
       </x:c>
       <x:c r="G208" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H208" s="11" t="str">
-        <x:v>gsc-pop-1139391</x:v>
+        <x:v>gsc-pop-1141572</x:v>
       </x:c>
     </x:row>
     <x:row r="209" ht="72" customHeight="1">
       <x:c r="A209" s="11" t="str">
-        <x:v>POP UP PARADE Dorothy Haze: Another Skin Ver. L Size</x:v>
+        <x:v>POP UP PARADE Lucy L Size</x:v>
       </x:c>
       <x:c r="B209" s="11" t="str">
         <x:v>主来源</x:v>
@@ -23001,24 +23146,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D209" s="11" t="str">
-        <x:v>POP UP PARADE Dorothy Haze: Another Skin Ver. L Size</x:v>
+        <x:v>POP UP PARADE Lucy L Size</x:v>
       </x:c>
       <x:c r="E209" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F209" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1139433</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1137607</x:v>
       </x:c>
       <x:c r="G209" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H209" s="11" t="str">
-        <x:v>gsc-pop-1139433</x:v>
+        <x:v>gsc-pop-1137607</x:v>
       </x:c>
     </x:row>
     <x:row r="210" ht="72" customHeight="1">
       <x:c r="A210" s="11" t="str">
-        <x:v>POP UP PARADE Saya L Size</x:v>
+        <x:v>POP UP PARADE Guts (Berserker Armor): Bloody Paint Ver. L Size</x:v>
       </x:c>
       <x:c r="B210" s="11" t="str">
         <x:v>主来源</x:v>
@@ -23027,24 +23172,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D210" s="11" t="str">
-        <x:v>POP UP PARADE Saya L Size</x:v>
+        <x:v>POP UP PARADE Guts (Berserker Armor): Bloody Paint Ver. L Size</x:v>
       </x:c>
       <x:c r="E210" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F210" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1136656</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1145852</x:v>
       </x:c>
       <x:c r="G210" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H210" s="11" t="str">
-        <x:v>gsc-pop-1136656</x:v>
+        <x:v>gsc-pop-1145852</x:v>
       </x:c>
     </x:row>
     <x:row r="211" ht="72" customHeight="1">
       <x:c r="A211" s="11" t="str">
-        <x:v>POP UP PARADE Sherry Tachibana L Size</x:v>
+        <x:v>POP UP PARADE 赛车初音: 2023 Ver.</x:v>
       </x:c>
       <x:c r="B211" s="11" t="str">
         <x:v>主来源</x:v>
@@ -23053,24 +23198,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D211" s="11" t="str">
-        <x:v>POP UP PARADE Sherry Tachibana L Size</x:v>
+        <x:v>POP UP PARADE Racing Miku: 2023 Ver.</x:v>
       </x:c>
       <x:c r="E211" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F211" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1144886</x:v>
+        <x:v>https://www.goodsmile.com/en/product/55958</x:v>
       </x:c>
       <x:c r="G211" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H211" s="11" t="str">
-        <x:v>gsc-pop-1144886</x:v>
+        <x:v>gsc-pop-55958</x:v>
       </x:c>
     </x:row>
     <x:row r="212" ht="72" customHeight="1">
       <x:c r="A212" s="11" t="str">
-        <x:v>POP UP PARADE SP Assassin/"First Hassan"</x:v>
+        <x:v>POP UP PARADE SP Momon</x:v>
       </x:c>
       <x:c r="B212" s="11" t="str">
         <x:v>主来源</x:v>
@@ -23079,24 +23224,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D212" s="11" t="str">
-        <x:v>POP UP PARADE SP Assassin/"First Hassan"</x:v>
+        <x:v>POP UP PARADE SP Momon</x:v>
       </x:c>
       <x:c r="E212" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F212" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/61723</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1139935</x:v>
       </x:c>
       <x:c r="G212" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H212" s="11" t="str">
-        <x:v>gsc-pop-61723</x:v>
+        <x:v>gsc-pop-1139935</x:v>
       </x:c>
     </x:row>
     <x:row r="213" ht="72" customHeight="1">
       <x:c r="A213" s="11" t="str">
-        <x:v>POP UP PARADE Hiro Nikaido L Size</x:v>
+        <x:v>POP UP PARADE Daiwa Scarlet L Size</x:v>
       </x:c>
       <x:c r="B213" s="11" t="str">
         <x:v>主来源</x:v>
@@ -23105,24 +23250,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D213" s="11" t="str">
-        <x:v>POP UP PARADE Hiro Nikaido L Size</x:v>
+        <x:v>POP UP PARADE Daiwa Scarlet L Size</x:v>
       </x:c>
       <x:c r="E213" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F213" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1144885</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1136848</x:v>
       </x:c>
       <x:c r="G213" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H213" s="11" t="str">
-        <x:v>gsc-pop-1144885</x:v>
+        <x:v>gsc-pop-1136848</x:v>
       </x:c>
     </x:row>
     <x:row r="214" ht="72" customHeight="1">
       <x:c r="A214" s="11" t="str">
-        <x:v>POP UP PARADE Yuzu (Maid)</x:v>
+        <x:v>POP UP PARADE Dorothy Haze L Size</x:v>
       </x:c>
       <x:c r="B214" s="11" t="str">
         <x:v>主来源</x:v>
@@ -23131,24 +23276,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D214" s="11" t="str">
-        <x:v>POP UP PARADE Yuzu (Maid)</x:v>
+        <x:v>POP UP PARADE Dorothy Haze L Size</x:v>
       </x:c>
       <x:c r="E214" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F214" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1143802</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1139391</x:v>
       </x:c>
       <x:c r="G214" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H214" s="11" t="str">
-        <x:v>gsc-pop-1143802</x:v>
+        <x:v>gsc-pop-1139391</x:v>
       </x:c>
     </x:row>
     <x:row r="215" ht="72" customHeight="1">
       <x:c r="A215" s="11" t="str">
-        <x:v>POP UP PARADE Zero Two L Size</x:v>
+        <x:v>POP UP PARADE Dorothy Haze: Another Skin Ver. L Size</x:v>
       </x:c>
       <x:c r="B215" s="11" t="str">
         <x:v>主来源</x:v>
@@ -23157,24 +23302,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D215" s="11" t="str">
-        <x:v>POP UP PARADE Zero Two L Size</x:v>
+        <x:v>POP UP PARADE Dorothy Haze: Another Skin Ver. L Size</x:v>
       </x:c>
       <x:c r="E215" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F215" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1137698</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1139433</x:v>
       </x:c>
       <x:c r="G215" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H215" s="11" t="str">
-        <x:v>gsc-pop-1137698</x:v>
+        <x:v>gsc-pop-1139433</x:v>
       </x:c>
     </x:row>
     <x:row r="216" ht="72" customHeight="1">
       <x:c r="A216" s="11" t="str">
-        <x:v>POP UP PARADE SP Void</x:v>
+        <x:v>POP UP PARADE Saya L Size</x:v>
       </x:c>
       <x:c r="B216" s="11" t="str">
         <x:v>主来源</x:v>
@@ -23183,24 +23328,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D216" s="11" t="str">
-        <x:v>POP UP PARADE SP Void</x:v>
+        <x:v>POP UP PARADE Saya L Size</x:v>
       </x:c>
       <x:c r="E216" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F216" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1145188</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1136656</x:v>
       </x:c>
       <x:c r="G216" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H216" s="11" t="str">
-        <x:v>gsc-pop-1145188</x:v>
+        <x:v>gsc-pop-1136656</x:v>
       </x:c>
     </x:row>
     <x:row r="217" ht="72" customHeight="1">
       <x:c r="A217" s="11" t="str">
-        <x:v>POP UP PARADE Alastor: Another Color Ver.</x:v>
+        <x:v>POP UP PARADE Sherry Tachibana L Size</x:v>
       </x:c>
       <x:c r="B217" s="11" t="str">
         <x:v>主来源</x:v>
@@ -23209,24 +23354,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D217" s="11" t="str">
-        <x:v>POP UP PARADE Alastor: Another Color Ver.</x:v>
+        <x:v>POP UP PARADE Sherry Tachibana L Size</x:v>
       </x:c>
       <x:c r="E217" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F217" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1143892</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1144886</x:v>
       </x:c>
       <x:c r="G217" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H217" s="11" t="str">
-        <x:v>gsc-pop-1143892</x:v>
+        <x:v>gsc-pop-1144886</x:v>
       </x:c>
     </x:row>
     <x:row r="218" ht="72" customHeight="1">
       <x:c r="A218" s="11" t="str">
-        <x:v>POP UP PARADE Polyester &amp; Polyurethane Set</x:v>
+        <x:v>POP UP PARADE SP Assassin/"First Hassan"</x:v>
       </x:c>
       <x:c r="B218" s="11" t="str">
         <x:v>主来源</x:v>
@@ -23235,24 +23380,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D218" s="11" t="str">
-        <x:v>POP UP PARADE Polyester &amp; Polyurethane Set</x:v>
+        <x:v>POP UP PARADE SP Assassin/"First Hassan"</x:v>
       </x:c>
       <x:c r="E218" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F218" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1142460</x:v>
+        <x:v>https://www.goodsmile.com/en/product/61723</x:v>
       </x:c>
       <x:c r="G218" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H218" s="11" t="str">
-        <x:v>gsc-pop-1142460</x:v>
+        <x:v>gsc-pop-61723</x:v>
       </x:c>
     </x:row>
     <x:row r="219" ht="72" customHeight="1">
       <x:c r="A219" s="11" t="str">
-        <x:v>POP UP PARADE Polyester</x:v>
+        <x:v>POP UP PARADE Hiro Nikaido L Size</x:v>
       </x:c>
       <x:c r="B219" s="11" t="str">
         <x:v>主来源</x:v>
@@ -23261,24 +23406,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D219" s="11" t="str">
-        <x:v>POP UP PARADE Polyester</x:v>
+        <x:v>POP UP PARADE Hiro Nikaido L Size</x:v>
       </x:c>
       <x:c r="E219" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F219" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1142459</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1144885</x:v>
       </x:c>
       <x:c r="G219" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H219" s="11" t="str">
-        <x:v>gsc-pop-1142459</x:v>
+        <x:v>gsc-pop-1144885</x:v>
       </x:c>
     </x:row>
     <x:row r="220" ht="72" customHeight="1">
       <x:c r="A220" s="11" t="str">
-        <x:v>POP UP PARADE Polyurethane</x:v>
+        <x:v>POP UP PARADE Yuzu (Maid)</x:v>
       </x:c>
       <x:c r="B220" s="11" t="str">
         <x:v>主来源</x:v>
@@ -23287,24 +23432,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D220" s="11" t="str">
-        <x:v>POP UP PARADE Polyurethane</x:v>
+        <x:v>POP UP PARADE Yuzu (Maid)</x:v>
       </x:c>
       <x:c r="E220" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F220" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1142458</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1143802</x:v>
       </x:c>
       <x:c r="G220" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H220" s="11" t="str">
-        <x:v>gsc-pop-1142458</x:v>
+        <x:v>gsc-pop-1143802</x:v>
       </x:c>
     </x:row>
     <x:row r="221" ht="72" customHeight="1">
       <x:c r="A221" s="11" t="str">
-        <x:v>POP UP PARADE Aura</x:v>
+        <x:v>POP UP PARADE Zero Two L Size</x:v>
       </x:c>
       <x:c r="B221" s="11" t="str">
         <x:v>主来源</x:v>
@@ -23313,24 +23458,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D221" s="11" t="str">
-        <x:v>POP UP PARADE Aura</x:v>
+        <x:v>POP UP PARADE Zero Two L Size</x:v>
       </x:c>
       <x:c r="E221" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F221" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1137013</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1137698</x:v>
       </x:c>
       <x:c r="G221" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H221" s="11" t="str">
-        <x:v>gsc-pop-1137013</x:v>
+        <x:v>gsc-pop-1137698</x:v>
       </x:c>
     </x:row>
     <x:row r="222" ht="72" customHeight="1">
       <x:c r="A222" s="11" t="str">
-        <x:v>POP UP PARADE SP Cutie Honey</x:v>
+        <x:v>POP UP PARADE SP Void</x:v>
       </x:c>
       <x:c r="B222" s="11" t="str">
         <x:v>主来源</x:v>
@@ -23339,24 +23484,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D222" s="11" t="str">
-        <x:v>POP UP PARADE SP Cutie Honey</x:v>
+        <x:v>POP UP PARADE SP Void</x:v>
       </x:c>
       <x:c r="E222" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F222" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1142837</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1145188</x:v>
       </x:c>
       <x:c r="G222" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H222" s="11" t="str">
-        <x:v>gsc-pop-1142837</x:v>
+        <x:v>gsc-pop-1145188</x:v>
       </x:c>
     </x:row>
     <x:row r="223" ht="72" customHeight="1">
       <x:c r="A223" s="11" t="str">
-        <x:v>chitocerium chirality I-hydra</x:v>
+        <x:v>POP UP PARADE Alastor: Another Color Ver.</x:v>
       </x:c>
       <x:c r="B223" s="11" t="str">
         <x:v>主来源</x:v>
@@ -23365,24 +23510,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D223" s="11" t="str">
-        <x:v>chitocerium chirality I-hydra</x:v>
+        <x:v>POP UP PARADE Alastor: Another Color Ver.</x:v>
       </x:c>
       <x:c r="E223" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F223" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1138464</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1143892</x:v>
       </x:c>
       <x:c r="G223" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H223" s="11" t="str">
-        <x:v>gsc-chito-1138464</x:v>
+        <x:v>gsc-pop-1143892</x:v>
       </x:c>
     </x:row>
     <x:row r="224" ht="72" customHeight="1">
       <x:c r="A224" s="11" t="str">
-        <x:v>chitocerium I-hydra</x:v>
+        <x:v>POP UP PARADE Polyester &amp; Polyurethane Set</x:v>
       </x:c>
       <x:c r="B224" s="11" t="str">
         <x:v>主来源</x:v>
@@ -23391,24 +23536,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D224" s="11" t="str">
-        <x:v>chitocerium I-hydra</x:v>
+        <x:v>POP UP PARADE Polyester &amp; Polyurethane Set</x:v>
       </x:c>
       <x:c r="E224" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F224" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/59941</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1142460</x:v>
       </x:c>
       <x:c r="G224" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H224" s="11" t="str">
-        <x:v>gsc-chito-59941</x:v>
+        <x:v>gsc-pop-1142460</x:v>
       </x:c>
     </x:row>
     <x:row r="225" ht="72" customHeight="1">
       <x:c r="A225" s="11" t="str">
-        <x:v>chitocerium VI-carbonia graphites</x:v>
+        <x:v>POP UP PARADE Polyester</x:v>
       </x:c>
       <x:c r="B225" s="11" t="str">
         <x:v>主来源</x:v>
@@ -23417,24 +23562,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D225" s="11" t="str">
-        <x:v>chitocerium VI-carbonia graphites</x:v>
+        <x:v>POP UP PARADE Polyester</x:v>
       </x:c>
       <x:c r="E225" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F225" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/12146</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1142459</x:v>
       </x:c>
       <x:c r="G225" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H225" s="11" t="str">
-        <x:v>gsc-chito-12146</x:v>
+        <x:v>gsc-pop-1142459</x:v>
       </x:c>
     </x:row>
     <x:row r="226" ht="72" customHeight="1">
       <x:c r="A226" s="11" t="str">
-        <x:v>chitocerium LXXVIII-platinum 1.5</x:v>
+        <x:v>POP UP PARADE Polyurethane</x:v>
       </x:c>
       <x:c r="B226" s="11" t="str">
         <x:v>主来源</x:v>
@@ -23443,24 +23588,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D226" s="11" t="str">
-        <x:v>chitocerium LXXVIII-platinum 1.5</x:v>
+        <x:v>POP UP PARADE Polyurethane</x:v>
       </x:c>
       <x:c r="E226" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F226" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/10892</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1142458</x:v>
       </x:c>
       <x:c r="G226" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H226" s="11" t="str">
-        <x:v>gsc-chito-10892</x:v>
+        <x:v>gsc-pop-1142458</x:v>
       </x:c>
     </x:row>
     <x:row r="227" ht="72" customHeight="1">
       <x:c r="A227" s="11" t="str">
-        <x:v>chitocerium nightmare XCIX-albere &amp; C-efer</x:v>
+        <x:v>POP UP PARADE Aura</x:v>
       </x:c>
       <x:c r="B227" s="11" t="str">
         <x:v>主来源</x:v>
@@ -23469,24 +23614,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D227" s="11" t="str">
-        <x:v>chitocerium nightmare XCIX-albere &amp; C-efer</x:v>
+        <x:v>POP UP PARADE Aura</x:v>
       </x:c>
       <x:c r="E227" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F227" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/10241</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1137013</x:v>
       </x:c>
       <x:c r="G227" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H227" s="11" t="str">
-        <x:v>gsc-chito-10241</x:v>
+        <x:v>gsc-pop-1137013</x:v>
       </x:c>
     </x:row>
     <x:row r="228" ht="72" customHeight="1">
       <x:c r="A228" s="11" t="str">
-        <x:v>chitocerium XCII-urania</x:v>
+        <x:v>POP UP PARADE SP Cutie Honey</x:v>
       </x:c>
       <x:c r="B228" s="11" t="str">
         <x:v>主来源</x:v>
@@ -23495,24 +23640,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D228" s="11" t="str">
-        <x:v>chitocerium XCII-urania</x:v>
+        <x:v>POP UP PARADE SP Cutie Honey</x:v>
       </x:c>
       <x:c r="E228" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F228" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/9766</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1142837</x:v>
       </x:c>
       <x:c r="G228" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H228" s="11" t="str">
-        <x:v>gsc-chito-9766</x:v>
+        <x:v>gsc-pop-1142837</x:v>
       </x:c>
     </x:row>
     <x:row r="229" ht="72" customHeight="1">
       <x:c r="A229" s="11" t="str">
-        <x:v>chitocerium VI-carbonia adamas</x:v>
+        <x:v>chitocerium chirality I-hydra</x:v>
       </x:c>
       <x:c r="B229" s="11" t="str">
         <x:v>主来源</x:v>
@@ -23521,24 +23666,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D229" s="11" t="str">
-        <x:v>chitocerium VI-carbonia adamas</x:v>
+        <x:v>chitocerium chirality I-hydra</x:v>
       </x:c>
       <x:c r="E229" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F229" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/6300</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1138464</x:v>
       </x:c>
       <x:c r="G229" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H229" s="11" t="str">
-        <x:v>gsc-chito-6300</x:v>
+        <x:v>gsc-chito-1138464</x:v>
       </x:c>
     </x:row>
     <x:row r="230" ht="72" customHeight="1">
       <x:c r="A230" s="11" t="str">
-        <x:v>chitocerium XCIX-albere &amp; C-efer</x:v>
+        <x:v>chitocerium I-hydra</x:v>
       </x:c>
       <x:c r="B230" s="11" t="str">
         <x:v>主来源</x:v>
@@ -23547,24 +23692,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D230" s="11" t="str">
-        <x:v>chitocerium XCIX-albere &amp; C-efer</x:v>
+        <x:v>chitocerium I-hydra</x:v>
       </x:c>
       <x:c r="E230" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F230" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/32646</x:v>
+        <x:v>https://www.goodsmile.com/en/product/59941</x:v>
       </x:c>
       <x:c r="G230" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H230" s="11" t="str">
-        <x:v>gsc-chito-32646</x:v>
+        <x:v>gsc-chito-59941</x:v>
       </x:c>
     </x:row>
     <x:row r="231" ht="72" customHeight="1">
       <x:c r="A231" s="11" t="str">
-        <x:v>chitocerium LXXVIII-platinum</x:v>
+        <x:v>chitocerium VI-carbonia graphites</x:v>
       </x:c>
       <x:c r="B231" s="11" t="str">
         <x:v>主来源</x:v>
@@ -23573,24 +23718,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D231" s="11" t="str">
-        <x:v>chitocerium LXXVIII-platinum</x:v>
+        <x:v>chitocerium VI-carbonia graphites</x:v>
       </x:c>
       <x:c r="E231" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F231" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/5770</x:v>
+        <x:v>https://www.goodsmile.com/en/product/12146</x:v>
       </x:c>
       <x:c r="G231" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H231" s="11" t="str">
-        <x:v>gsc-chito-5770</x:v>
+        <x:v>gsc-chito-12146</x:v>
       </x:c>
     </x:row>
     <x:row r="232" ht="72" customHeight="1">
       <x:c r="A232" s="11" t="str">
-        <x:v>chitocerium VI-carbonia lonsdaleite</x:v>
+        <x:v>chitocerium LXXVIII-platinum 1.5</x:v>
       </x:c>
       <x:c r="B232" s="11" t="str">
         <x:v>主来源</x:v>
@@ -23599,24 +23744,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D232" s="11" t="str">
-        <x:v>chitocerium VI-carbonia lonsdaleite</x:v>
+        <x:v>chitocerium LXXVIII-platinum 1.5</x:v>
       </x:c>
       <x:c r="E232" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F232" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/7116</x:v>
+        <x:v>https://www.goodsmile.com/en/product/10892</x:v>
       </x:c>
       <x:c r="G232" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H232" s="11" t="str">
-        <x:v>gsc-chito-7116</x:v>
+        <x:v>gsc-chito-10892</x:v>
       </x:c>
     </x:row>
     <x:row r="233" ht="72" customHeight="1">
       <x:c r="A233" s="11" t="str">
-        <x:v>PLAMATEA Mari Makinami Illustrious</x:v>
+        <x:v>chitocerium nightmare XCIX-albere &amp; C-efer</x:v>
       </x:c>
       <x:c r="B233" s="11" t="str">
         <x:v>主来源</x:v>
@@ -23625,24 +23770,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D233" s="11" t="str">
-        <x:v>PLAMATEA Mari Makinami Illustrious</x:v>
+        <x:v>chitocerium nightmare XCIX-albere &amp; C-efer</x:v>
       </x:c>
       <x:c r="E233" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F233" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1139093</x:v>
+        <x:v>https://www.goodsmile.com/en/product/10241</x:v>
       </x:c>
       <x:c r="G233" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H233" s="11" t="str">
-        <x:v>gsc-plamatea-1139093</x:v>
+        <x:v>gsc-chito-10241</x:v>
       </x:c>
     </x:row>
     <x:row r="234" ht="72" customHeight="1">
       <x:c r="A234" s="11" t="str">
-        <x:v>PLAMATEA Armored Soldier of Unknown Affiliation</x:v>
+        <x:v>chitocerium XCII-urania</x:v>
       </x:c>
       <x:c r="B234" s="11" t="str">
         <x:v>主来源</x:v>
@@ -23651,24 +23796,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D234" s="11" t="str">
-        <x:v>PLAMATEA Armored Soldier of Unknown Affiliation</x:v>
+        <x:v>chitocerium XCII-urania</x:v>
       </x:c>
       <x:c r="E234" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F234" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1139114</x:v>
+        <x:v>https://www.goodsmile.com/en/product/9766</x:v>
       </x:c>
       <x:c r="G234" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H234" s="11" t="str">
-        <x:v>gsc-plamatea-1139114</x:v>
+        <x:v>gsc-chito-9766</x:v>
       </x:c>
     </x:row>
     <x:row r="235" ht="72" customHeight="1">
       <x:c r="A235" s="11" t="str">
-        <x:v>PLAMATEA Hurricane Honey</x:v>
+        <x:v>chitocerium VI-carbonia adamas</x:v>
       </x:c>
       <x:c r="B235" s="11" t="str">
         <x:v>主来源</x:v>
@@ -23677,24 +23822,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D235" s="11" t="str">
-        <x:v>PLAMATEA Hurricane Honey</x:v>
+        <x:v>chitocerium VI-carbonia adamas</x:v>
       </x:c>
       <x:c r="E235" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F235" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1145409</x:v>
+        <x:v>https://www.goodsmile.com/en/product/6300</x:v>
       </x:c>
       <x:c r="G235" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H235" s="11" t="str">
-        <x:v>gsc-plamatea-1145409</x:v>
+        <x:v>gsc-chito-6300</x:v>
       </x:c>
     </x:row>
     <x:row r="236" ht="72" customHeight="1">
       <x:c r="A236" s="11" t="str">
-        <x:v>PLAMATEA Honey Chaser</x:v>
+        <x:v>chitocerium XCIX-albere &amp; C-efer</x:v>
       </x:c>
       <x:c r="B236" s="11" t="str">
         <x:v>主来源</x:v>
@@ -23703,24 +23848,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D236" s="11" t="str">
-        <x:v>PLAMATEA Honey Chaser</x:v>
+        <x:v>chitocerium XCIX-albere &amp; C-efer</x:v>
       </x:c>
       <x:c r="E236" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F236" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1138610</x:v>
+        <x:v>https://www.goodsmile.com/en/product/32646</x:v>
       </x:c>
       <x:c r="G236" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H236" s="11" t="str">
-        <x:v>gsc-plamatea-1138610</x:v>
+        <x:v>gsc-chito-32646</x:v>
       </x:c>
     </x:row>
     <x:row r="237" ht="72" customHeight="1">
       <x:c r="A237" s="11" t="str">
-        <x:v>PLAMATEA Kongo Kai-II C</x:v>
+        <x:v>chitocerium LXXVIII-platinum</x:v>
       </x:c>
       <x:c r="B237" s="11" t="str">
         <x:v>主来源</x:v>
@@ -23729,24 +23874,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D237" s="11" t="str">
-        <x:v>PLAMATEA Kongo Kai-II C</x:v>
+        <x:v>chitocerium LXXVIII-platinum</x:v>
       </x:c>
       <x:c r="E237" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F237" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1137954</x:v>
+        <x:v>https://www.goodsmile.com/en/product/5770</x:v>
       </x:c>
       <x:c r="G237" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H237" s="11" t="str">
-        <x:v>gsc-plamatea-1137954</x:v>
+        <x:v>gsc-chito-5770</x:v>
       </x:c>
     </x:row>
     <x:row r="238" ht="72" customHeight="1">
       <x:c r="A238" s="11" t="str">
-        <x:v>PLAMATEA Yachiyo</x:v>
+        <x:v>chitocerium VI-carbonia lonsdaleite</x:v>
       </x:c>
       <x:c r="B238" s="11" t="str">
         <x:v>主来源</x:v>
@@ -23755,24 +23900,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D238" s="11" t="str">
-        <x:v>PLAMATEA Yachiyo</x:v>
+        <x:v>chitocerium VI-carbonia lonsdaleite</x:v>
       </x:c>
       <x:c r="E238" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F238" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1142817</x:v>
+        <x:v>https://www.goodsmile.com/en/product/7116</x:v>
       </x:c>
       <x:c r="G238" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H238" s="11" t="str">
-        <x:v>gsc-plamatea-1142817</x:v>
+        <x:v>gsc-chito-7116</x:v>
       </x:c>
     </x:row>
     <x:row r="239" ht="72" customHeight="1">
       <x:c r="A239" s="11" t="str">
-        <x:v>PLAMATEA Cutie Honey: Prism Crystal Ver.</x:v>
+        <x:v>PLAMATEA Mari Makinami Illustrious</x:v>
       </x:c>
       <x:c r="B239" s="11" t="str">
         <x:v>主来源</x:v>
@@ -23781,24 +23926,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D239" s="11" t="str">
-        <x:v>PLAMATEA Cutie Honey: Prism Crystal Ver.</x:v>
+        <x:v>PLAMATEA Mari Makinami Illustrious</x:v>
       </x:c>
       <x:c r="E239" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F239" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1142140</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1139093</x:v>
       </x:c>
       <x:c r="G239" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H239" s="11" t="str">
-        <x:v>gsc-plamatea-1142140</x:v>
+        <x:v>gsc-plamatea-1139093</x:v>
       </x:c>
     </x:row>
     <x:row r="240" ht="72" customHeight="1">
       <x:c r="A240" s="11" t="str">
-        <x:v>PLAMATEA Guy Shishioh</x:v>
+        <x:v>PLAMATEA Armored Soldier of Unknown Affiliation</x:v>
       </x:c>
       <x:c r="B240" s="11" t="str">
         <x:v>主来源</x:v>
@@ -23807,24 +23952,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D240" s="11" t="str">
-        <x:v>PLAMATEA Guy Shishioh</x:v>
+        <x:v>PLAMATEA Armored Soldier of Unknown Affiliation</x:v>
       </x:c>
       <x:c r="E240" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F240" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1136972</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1139114</x:v>
       </x:c>
       <x:c r="G240" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H240" s="11" t="str">
-        <x:v>gsc-plamatea-1136972</x:v>
+        <x:v>gsc-plamatea-1139114</x:v>
       </x:c>
     </x:row>
     <x:row r="241" ht="72" customHeight="1">
       <x:c r="A241" s="11" t="str">
-        <x:v>PLAMATEA MX-chan</x:v>
+        <x:v>PLAMATEA Hurricane Honey</x:v>
       </x:c>
       <x:c r="B241" s="11" t="str">
         <x:v>主来源</x:v>
@@ -23833,24 +23978,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D241" s="11" t="str">
-        <x:v>PLAMATEA MX-chan</x:v>
+        <x:v>PLAMATEA Hurricane Honey</x:v>
       </x:c>
       <x:c r="E241" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F241" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1145848</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1145409</x:v>
       </x:c>
       <x:c r="G241" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H241" s="11" t="str">
-        <x:v>gsc-plamatea-1145848</x:v>
+        <x:v>gsc-plamatea-1145409</x:v>
       </x:c>
     </x:row>
     <x:row r="242" ht="72" customHeight="1">
       <x:c r="A242" s="11" t="str">
-        <x:v>PLAMATEA Arika Yumemiya</x:v>
+        <x:v>PLAMATEA Honey Chaser</x:v>
       </x:c>
       <x:c r="B242" s="11" t="str">
         <x:v>主来源</x:v>
@@ -23859,24 +24004,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D242" s="11" t="str">
-        <x:v>PLAMATEA Arika Yumemiya</x:v>
+        <x:v>PLAMATEA Honey Chaser</x:v>
       </x:c>
       <x:c r="E242" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F242" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1138558</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1138610</x:v>
       </x:c>
       <x:c r="G242" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H242" s="11" t="str">
-        <x:v>gsc-plamatea-1138558</x:v>
+        <x:v>gsc-plamatea-1138610</x:v>
       </x:c>
     </x:row>
     <x:row r="243" ht="72" customHeight="1">
       <x:c r="A243" s="11" t="str">
-        <x:v>PLAMATEA Shielder/Mash Kyrielight (Ortinax)</x:v>
+        <x:v>PLAMATEA Kongo Kai-II C</x:v>
       </x:c>
       <x:c r="B243" s="11" t="str">
         <x:v>主来源</x:v>
@@ -23885,24 +24030,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D243" s="11" t="str">
-        <x:v>PLAMATEA Shielder/Mash Kyrielight (Ortinax)</x:v>
+        <x:v>PLAMATEA Kongo Kai-II C</x:v>
       </x:c>
       <x:c r="E243" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F243" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1144549</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1137954</x:v>
       </x:c>
       <x:c r="G243" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H243" s="11" t="str">
-        <x:v>gsc-plamatea-1144549</x:v>
+        <x:v>gsc-plamatea-1137954</x:v>
       </x:c>
     </x:row>
     <x:row r="244" ht="72" customHeight="1">
       <x:c r="A244" s="11" t="str">
-        <x:v>PLAMATEA Shielder/Mash Kyrielight (Ortinax) Black Barrel Edition</x:v>
+        <x:v>PLAMATEA Yachiyo</x:v>
       </x:c>
       <x:c r="B244" s="11" t="str">
         <x:v>主来源</x:v>
@@ -23911,24 +24056,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D244" s="11" t="str">
-        <x:v>PLAMATEA Shielder/Mash Kyrielight (Ortinax) Black Barrel Edition</x:v>
+        <x:v>PLAMATEA Yachiyo</x:v>
       </x:c>
       <x:c r="E244" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F244" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1144550</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1142817</x:v>
       </x:c>
       <x:c r="G244" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H244" s="11" t="str">
-        <x:v>gsc-plamatea-1144550</x:v>
+        <x:v>gsc-plamatea-1142817</x:v>
       </x:c>
     </x:row>
     <x:row r="245" ht="72" customHeight="1">
       <x:c r="A245" s="11" t="str">
-        <x:v>PLAMATEA Al Azif</x:v>
+        <x:v>PLAMATEA Cutie Honey: Prism Crystal Ver.</x:v>
       </x:c>
       <x:c r="B245" s="11" t="str">
         <x:v>主来源</x:v>
@@ -23937,24 +24082,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D245" s="11" t="str">
-        <x:v>PLAMATEA Al Azif</x:v>
+        <x:v>PLAMATEA Cutie Honey: Prism Crystal Ver.</x:v>
       </x:c>
       <x:c r="E245" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F245" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1137892</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1142140</x:v>
       </x:c>
       <x:c r="G245" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H245" s="11" t="str">
-        <x:v>gsc-plamatea-1137892</x:v>
+        <x:v>gsc-plamatea-1142140</x:v>
       </x:c>
     </x:row>
     <x:row r="246" ht="72" customHeight="1">
       <x:c r="A246" s="11" t="str">
-        <x:v>PLAMATEA 初音未来</x:v>
+        <x:v>PLAMATEA Guy Shishioh</x:v>
       </x:c>
       <x:c r="B246" s="11" t="str">
         <x:v>主来源</x:v>
@@ -23963,24 +24108,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D246" s="11" t="str">
-        <x:v>PLAMATEA Hatsune Miku</x:v>
+        <x:v>PLAMATEA Guy Shishioh</x:v>
       </x:c>
       <x:c r="E246" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F246" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1137327</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1136972</x:v>
       </x:c>
       <x:c r="G246" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H246" s="11" t="str">
-        <x:v>gsc-plamatea-1137327</x:v>
+        <x:v>gsc-plamatea-1136972</x:v>
       </x:c>
     </x:row>
     <x:row r="247" ht="72" customHeight="1">
       <x:c r="A247" s="11" t="str">
-        <x:v>PLAMATEA Kerry: Bunny Ver.</x:v>
+        <x:v>PLAMATEA MX-chan</x:v>
       </x:c>
       <x:c r="B247" s="11" t="str">
         <x:v>主来源</x:v>
@@ -23989,24 +24134,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D247" s="11" t="str">
-        <x:v>PLAMATEA Kerry: Bunny Ver.</x:v>
+        <x:v>PLAMATEA MX-chan</x:v>
       </x:c>
       <x:c r="E247" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F247" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1141570</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1145848</x:v>
       </x:c>
       <x:c r="G247" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H247" s="11" t="str">
-        <x:v>gsc-plamatea-1141570</x:v>
+        <x:v>gsc-plamatea-1145848</x:v>
       </x:c>
     </x:row>
     <x:row r="248" ht="72" customHeight="1">
       <x:c r="A248" s="11" t="str">
-        <x:v>PLAMATEA Rei Ayanami</x:v>
+        <x:v>PLAMATEA Arika Yumemiya</x:v>
       </x:c>
       <x:c r="B248" s="11" t="str">
         <x:v>主来源</x:v>
@@ -24015,24 +24160,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D248" s="11" t="str">
-        <x:v>PLAMATEA Rei Ayanami</x:v>
+        <x:v>PLAMATEA Arika Yumemiya</x:v>
       </x:c>
       <x:c r="E248" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F248" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1137923</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1138558</x:v>
       </x:c>
       <x:c r="G248" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H248" s="11" t="str">
-        <x:v>gsc-plamatea-1137923</x:v>
+        <x:v>gsc-plamatea-1138558</x:v>
       </x:c>
     </x:row>
     <x:row r="249" ht="72" customHeight="1">
       <x:c r="A249" s="11" t="str">
-        <x:v>PLAMATEA Asuka Shikinami Langley</x:v>
+        <x:v>PLAMATEA Shielder/Mash Kyrielight (Ortinax)</x:v>
       </x:c>
       <x:c r="B249" s="11" t="str">
         <x:v>主来源</x:v>
@@ -24041,24 +24186,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D249" s="11" t="str">
-        <x:v>PLAMATEA Asuka Shikinami Langley</x:v>
+        <x:v>PLAMATEA Shielder/Mash Kyrielight (Ortinax)</x:v>
       </x:c>
       <x:c r="E249" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F249" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1137924</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1144549</x:v>
       </x:c>
       <x:c r="G249" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H249" s="11" t="str">
-        <x:v>gsc-plamatea-1137924</x:v>
+        <x:v>gsc-plamatea-1144549</x:v>
       </x:c>
     </x:row>
     <x:row r="250" ht="72" customHeight="1">
       <x:c r="A250" s="11" t="str">
-        <x:v>PLAMATEA Black Honey</x:v>
+        <x:v>PLAMATEA Shielder/Mash Kyrielight (Ortinax) Black Barrel Edition</x:v>
       </x:c>
       <x:c r="B250" s="11" t="str">
         <x:v>主来源</x:v>
@@ -24067,24 +24212,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D250" s="11" t="str">
-        <x:v>PLAMATEA Black Honey</x:v>
+        <x:v>PLAMATEA Shielder/Mash Kyrielight (Ortinax) Black Barrel Edition</x:v>
       </x:c>
       <x:c r="E250" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F250" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1136218</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1144550</x:v>
       </x:c>
       <x:c r="G250" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H250" s="11" t="str">
-        <x:v>gsc-plamatea-1136218</x:v>
+        <x:v>gsc-plamatea-1144550</x:v>
       </x:c>
     </x:row>
     <x:row r="251" ht="72" customHeight="1">
       <x:c r="A251" s="11" t="str">
-        <x:v>PLAMATEA T-60 帕瓦 Armor</x:v>
+        <x:v>PLAMATEA Al Azif</x:v>
       </x:c>
       <x:c r="B251" s="11" t="str">
         <x:v>主来源</x:v>
@@ -24093,24 +24238,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D251" s="11" t="str">
-        <x:v>PLAMATEA T-60 Power Armor</x:v>
+        <x:v>PLAMATEA Al Azif</x:v>
       </x:c>
       <x:c r="E251" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F251" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1138002</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1137892</x:v>
       </x:c>
       <x:c r="G251" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H251" s="11" t="str">
-        <x:v>gsc-plamatea-1138002</x:v>
+        <x:v>gsc-plamatea-1137892</x:v>
       </x:c>
     </x:row>
     <x:row r="252" ht="72" customHeight="1">
       <x:c r="A252" s="11" t="str">
-        <x:v>PLAMATEA Muse Body: Ichika - Silver Bikini Ver.</x:v>
+        <x:v>PLAMATEA 初音未来</x:v>
       </x:c>
       <x:c r="B252" s="11" t="str">
         <x:v>主来源</x:v>
@@ -24119,24 +24264,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D252" s="11" t="str">
-        <x:v>PLAMATEA Muse Body: Ichika - Silver Bikini Ver.</x:v>
+        <x:v>PLAMATEA Hatsune Miku</x:v>
       </x:c>
       <x:c r="E252" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F252" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1141879</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1137327</x:v>
       </x:c>
       <x:c r="G252" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H252" s="11" t="str">
-        <x:v>gsc-plamatea-1141879</x:v>
+        <x:v>gsc-plamatea-1137327</x:v>
       </x:c>
     </x:row>
     <x:row r="253" ht="72" customHeight="1">
       <x:c r="A253" s="11" t="str">
-        <x:v>PLAMATEA Cutie Honey</x:v>
+        <x:v>PLAMATEA Kerry: Bunny Ver.</x:v>
       </x:c>
       <x:c r="B253" s="11" t="str">
         <x:v>主来源</x:v>
@@ -24145,24 +24290,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D253" s="11" t="str">
-        <x:v>PLAMATEA Cutie Honey</x:v>
+        <x:v>PLAMATEA Kerry: Bunny Ver.</x:v>
       </x:c>
       <x:c r="E253" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F253" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/36286</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1141570</x:v>
       </x:c>
       <x:c r="G253" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H253" s="11" t="str">
-        <x:v>gsc-plamatea-36286</x:v>
+        <x:v>gsc-plamatea-1141570</x:v>
       </x:c>
     </x:row>
     <x:row r="254" ht="72" customHeight="1">
       <x:c r="A254" s="11" t="str">
-        <x:v>PLAMATEA Guts: Berserker Armor Ver.</x:v>
+        <x:v>PLAMATEA Rei Ayanami</x:v>
       </x:c>
       <x:c r="B254" s="11" t="str">
         <x:v>主来源</x:v>
@@ -24171,24 +24316,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D254" s="11" t="str">
-        <x:v>PLAMATEA Guts: Berserker Armor Ver.</x:v>
+        <x:v>PLAMATEA Rei Ayanami</x:v>
       </x:c>
       <x:c r="E254" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F254" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/60249</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1137923</x:v>
       </x:c>
       <x:c r="G254" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H254" s="11" t="str">
-        <x:v>gsc-plamatea-60249</x:v>
+        <x:v>gsc-plamatea-1137923</x:v>
       </x:c>
     </x:row>
     <x:row r="255" ht="72" customHeight="1">
       <x:c r="A255" s="11" t="str">
-        <x:v>PLAMATEA Yuki Yuna</x:v>
+        <x:v>PLAMATEA Asuka Shikinami Langley</x:v>
       </x:c>
       <x:c r="B255" s="11" t="str">
         <x:v>主来源</x:v>
@@ -24197,24 +24342,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D255" s="11" t="str">
-        <x:v>PLAMATEA Yuki Yuna</x:v>
+        <x:v>PLAMATEA Asuka Shikinami Langley</x:v>
       </x:c>
       <x:c r="E255" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F255" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/1137794</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1137924</x:v>
       </x:c>
       <x:c r="G255" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H255" s="11" t="str">
-        <x:v>gsc-plamatea-1137794</x:v>
+        <x:v>gsc-plamatea-1137924</x:v>
       </x:c>
     </x:row>
     <x:row r="256" ht="72" customHeight="1">
       <x:c r="A256" s="11" t="str">
-        <x:v>PLAMATEA Shigure Kai San</x:v>
+        <x:v>PLAMATEA Black Honey</x:v>
       </x:c>
       <x:c r="B256" s="11" t="str">
         <x:v>主来源</x:v>
@@ -24223,24 +24368,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D256" s="11" t="str">
-        <x:v>PLAMATEA Shigure Kai San</x:v>
+        <x:v>PLAMATEA Black Honey</x:v>
       </x:c>
       <x:c r="E256" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F256" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/34684</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1136218</x:v>
       </x:c>
       <x:c r="G256" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H256" s="11" t="str">
-        <x:v>gsc-plamatea-34684</x:v>
+        <x:v>gsc-plamatea-1136218</x:v>
       </x:c>
     </x:row>
     <x:row r="257" ht="72" customHeight="1">
       <x:c r="A257" s="11" t="str">
-        <x:v>PLAMATEA 初音未来: Happy 16th Birthday Ver.</x:v>
+        <x:v>PLAMATEA T-60 帕瓦 Armor</x:v>
       </x:c>
       <x:c r="B257" s="11" t="str">
         <x:v>主来源</x:v>
@@ -24249,24 +24394,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D257" s="11" t="str">
-        <x:v>PLAMATEA Hatsune Miku: Happy 16th Birthday Ver.</x:v>
+        <x:v>PLAMATEA T-60 Power Armor</x:v>
       </x:c>
       <x:c r="E257" s="11" t="str">
         <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F257" s="11" t="str">
-        <x:v>https://www.goodsmile.com/en/product/57238</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1138002</x:v>
       </x:c>
       <x:c r="G257" s="11" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H257" s="11" t="str">
-        <x:v>gsc-plamatea-57238</x:v>
+        <x:v>gsc-plamatea-1138002</x:v>
       </x:c>
     </x:row>
     <x:row r="258" ht="72" customHeight="1">
       <x:c r="A258" s="11" t="str">
-        <x:v>Pure Neemo 2 Feel · S · 白肌</x:v>
+        <x:v>PLAMATEA Muse Body: Ichika - Silver Bikini Ver.</x:v>
       </x:c>
       <x:c r="B258" s="11" t="str">
         <x:v>主来源</x:v>
@@ -24275,50 +24420,50 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D258" s="11" t="str">
-        <x:v>ピュアニーモ2フィール S／女の子 PFL103-WHT</x:v>
+        <x:v>PLAMATEA Muse Body: Ichika - Silver Bikini Ver.</x:v>
       </x:c>
       <x:c r="E258" s="11" t="str">
-        <x:v>本款独立素体、型号、尺寸口径、材料及配件范围；未披露项保留。</x:v>
+        <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F258" s="11" t="str">
-        <x:v>https://www.azone-int.co.jp/azonet/item/4573199849805</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1141879</x:v>
       </x:c>
       <x:c r="G258" s="11" t="str">
-        <x:v>2026-10-06</x:v>
+        <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H258" s="11" t="str">
-        <x:v>azone-body-pfl103-wht</x:v>
+        <x:v>gsc-plamatea-1141879</x:v>
       </x:c>
     </x:row>
     <x:row r="259" ht="72" customHeight="1">
       <x:c r="A259" s="11" t="str">
-        <x:v>Pure Neemo 2 Feel · S · 白肌</x:v>
+        <x:v>PLAMATEA Cutie Honey</x:v>
       </x:c>
       <x:c r="B259" s="11" t="str">
-        <x:v>补充来源</x:v>
+        <x:v>主来源</x:v>
       </x:c>
       <x:c r="C259" s="11" t="str">
-        <x:v>官方系列说明</x:v>
+        <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D259" s="11" t="str">
-        <x:v>1/6 AZONE 原创素体介绍</x:v>
+        <x:v>PLAMATEA Cutie Honey</x:v>
       </x:c>
       <x:c r="E259" s="11" t="str">
-        <x:v>对应系列的可动结构；不借用旧批次配件、其他型号高度或库存。</x:v>
+        <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F259" s="11" t="str">
-        <x:v>https://news.azone-int.co.jp/archives/43318</x:v>
+        <x:v>https://www.goodsmile.com/en/product/36286</x:v>
       </x:c>
       <x:c r="G259" s="11" t="str">
-        <x:v>2026-10-06</x:v>
+        <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H259" s="11" t="str">
-        <x:v>azone-body-pfl103-wht</x:v>
+        <x:v>gsc-plamatea-36286</x:v>
       </x:c>
     </x:row>
     <x:row r="260" ht="72" customHeight="1">
       <x:c r="A260" s="11" t="str">
-        <x:v>Pure Neemo 2 Feel · M · 白肌</x:v>
+        <x:v>PLAMATEA Guts: Berserker Armor Ver.</x:v>
       </x:c>
       <x:c r="B260" s="11" t="str">
         <x:v>主来源</x:v>
@@ -24327,50 +24472,50 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D260" s="11" t="str">
-        <x:v>ピュアニーモ2フィール M／女の子 PFL104-WHT</x:v>
+        <x:v>PLAMATEA Guts: Berserker Armor Ver.</x:v>
       </x:c>
       <x:c r="E260" s="11" t="str">
-        <x:v>本款独立素体、型号、尺寸口径、材料及配件范围；未披露项保留。</x:v>
+        <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F260" s="11" t="str">
-        <x:v>https://www.azone-int.co.jp/azonet/item/4573199849812</x:v>
+        <x:v>https://www.goodsmile.com/en/product/60249</x:v>
       </x:c>
       <x:c r="G260" s="11" t="str">
-        <x:v>2026-10-06</x:v>
+        <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H260" s="11" t="str">
-        <x:v>azone-body-pfl104-wht</x:v>
+        <x:v>gsc-plamatea-60249</x:v>
       </x:c>
     </x:row>
     <x:row r="261" ht="72" customHeight="1">
       <x:c r="A261" s="11" t="str">
-        <x:v>Pure Neemo 2 Feel · M · 白肌</x:v>
+        <x:v>PLAMATEA Yuki Yuna</x:v>
       </x:c>
       <x:c r="B261" s="11" t="str">
-        <x:v>补充来源</x:v>
+        <x:v>主来源</x:v>
       </x:c>
       <x:c r="C261" s="11" t="str">
-        <x:v>官方系列说明</x:v>
+        <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D261" s="11" t="str">
-        <x:v>1/6 AZONE 原创素体介绍</x:v>
+        <x:v>PLAMATEA Yuki Yuna</x:v>
       </x:c>
       <x:c r="E261" s="11" t="str">
-        <x:v>对应系列的可动结构；不借用旧批次配件、其他型号高度或库存。</x:v>
+        <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F261" s="11" t="str">
-        <x:v>https://news.azone-int.co.jp/archives/43318</x:v>
+        <x:v>https://www.goodsmile.com/en/product/1137794</x:v>
       </x:c>
       <x:c r="G261" s="11" t="str">
-        <x:v>2026-10-06</x:v>
+        <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H261" s="11" t="str">
-        <x:v>azone-body-pfl104-wht</x:v>
+        <x:v>gsc-plamatea-1137794</x:v>
       </x:c>
     </x:row>
     <x:row r="262" ht="72" customHeight="1">
       <x:c r="A262" s="11" t="str">
-        <x:v>Pure Neemo 2 Emotion · S · 白肌</x:v>
+        <x:v>PLAMATEA Shigure Kai San</x:v>
       </x:c>
       <x:c r="B262" s="11" t="str">
         <x:v>主来源</x:v>
@@ -24379,50 +24524,50 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D262" s="11" t="str">
-        <x:v>ピュアニーモ2エモーション S／女の子 PFL099-WHT</x:v>
+        <x:v>PLAMATEA Shigure Kai San</x:v>
       </x:c>
       <x:c r="E262" s="11" t="str">
-        <x:v>本款独立素体、型号、尺寸口径、材料及配件范围；未披露项保留。</x:v>
+        <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F262" s="11" t="str">
-        <x:v>https://www.azone-int.co.jp/azonet/item/4573199846163</x:v>
+        <x:v>https://www.goodsmile.com/en/product/34684</x:v>
       </x:c>
       <x:c r="G262" s="11" t="str">
-        <x:v>2026-10-06</x:v>
+        <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H262" s="11" t="str">
-        <x:v>azone-body-pfl099-wht</x:v>
+        <x:v>gsc-plamatea-34684</x:v>
       </x:c>
     </x:row>
     <x:row r="263" ht="72" customHeight="1">
       <x:c r="A263" s="11" t="str">
-        <x:v>Pure Neemo 2 Emotion · S · 白肌</x:v>
+        <x:v>PLAMATEA 初音未来: Happy 16th Birthday Ver.</x:v>
       </x:c>
       <x:c r="B263" s="11" t="str">
-        <x:v>补充来源</x:v>
+        <x:v>主来源</x:v>
       </x:c>
       <x:c r="C263" s="11" t="str">
-        <x:v>官方系列说明</x:v>
+        <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D263" s="11" t="str">
-        <x:v>1/6 AZONE 原创素体介绍</x:v>
+        <x:v>PLAMATEA Hatsune Miku: Happy 16th Birthday Ver.</x:v>
       </x:c>
       <x:c r="E263" s="11" t="str">
-        <x:v>对应系列的可动结构；不借用旧批次配件、其他型号高度或库存。</x:v>
+        <x:v>具体型号、制造主体、交付规格、材料与尺寸；未知字段保留。</x:v>
       </x:c>
       <x:c r="F263" s="11" t="str">
-        <x:v>https://news.azone-int.co.jp/archives/43318</x:v>
+        <x:v>https://www.goodsmile.com/en/product/57238</x:v>
       </x:c>
       <x:c r="G263" s="11" t="str">
-        <x:v>2026-10-06</x:v>
+        <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="H263" s="11" t="str">
-        <x:v>azone-body-pfl099-wht</x:v>
+        <x:v>gsc-plamatea-57238</x:v>
       </x:c>
     </x:row>
     <x:row r="264" ht="72" customHeight="1">
       <x:c r="A264" s="11" t="str">
-        <x:v>Pure Neemo 2 Emotion · M · 白肌</x:v>
+        <x:v>Pure Neemo 2 Feel · S · 白肌</x:v>
       </x:c>
       <x:c r="B264" s="11" t="str">
         <x:v>主来源</x:v>
@@ -24431,24 +24576,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D264" s="11" t="str">
-        <x:v>ピュアニーモ2エモーション M／女の子 PFL100-WHT</x:v>
+        <x:v>ピュアニーモ2フィール S／女の子 PFL103-WHT</x:v>
       </x:c>
       <x:c r="E264" s="11" t="str">
         <x:v>本款独立素体、型号、尺寸口径、材料及配件范围；未披露项保留。</x:v>
       </x:c>
       <x:c r="F264" s="11" t="str">
-        <x:v>https://www.azone-int.co.jp/azonet/item/4573199846187</x:v>
+        <x:v>https://www.azone-int.co.jp/azonet/item/4573199849805</x:v>
       </x:c>
       <x:c r="G264" s="11" t="str">
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="H264" s="11" t="str">
-        <x:v>azone-body-pfl100-wht</x:v>
+        <x:v>azone-body-pfl103-wht</x:v>
       </x:c>
     </x:row>
     <x:row r="265" ht="72" customHeight="1">
       <x:c r="A265" s="11" t="str">
-        <x:v>Pure Neemo 2 Emotion · M · 白肌</x:v>
+        <x:v>Pure Neemo 2 Feel · S · 白肌</x:v>
       </x:c>
       <x:c r="B265" s="11" t="str">
         <x:v>补充来源</x:v>
@@ -24469,220 +24614,220 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="H265" s="11" t="str">
-        <x:v>azone-body-pfl100-wht</x:v>
+        <x:v>azone-body-pfl103-wht</x:v>
       </x:c>
     </x:row>
     <x:row r="266" ht="72" customHeight="1">
       <x:c r="A266" s="11" t="str">
-        <x:v>Pure Neemo Flection · M · 白肌</x:v>
+        <x:v>Pure Neemo 2 Feel · S · 白肌</x:v>
       </x:c>
       <x:c r="B266" s="11" t="str">
-        <x:v>主来源</x:v>
+        <x:v>补充来源</x:v>
       </x:c>
       <x:c r="C266" s="11" t="str">
-        <x:v>官方产品页</x:v>
+        <x:v>官方配件改版通知</x:v>
       </x:c>
       <x:c r="D266" s="11" t="str">
-        <x:v>ピュアニーモフレクション M／女の子 PFL088-WHT</x:v>
+        <x:v>AZONE：2026 年 8 月起换手配件改版</x:v>
       </x:c>
       <x:c r="E266" s="11" t="str">
-        <x:v>本款独立素体、型号、尺寸口径、材料及配件范围；未披露项保留。</x:v>
+        <x:v>换手配件的新旧品番及内容变化；配件另售，不代表素体附送。</x:v>
       </x:c>
       <x:c r="F266" s="11" t="str">
-        <x:v>https://www.azone-int.co.jp/azonet/item/4573199841397</x:v>
+        <x:v>https://news.azone-int.co.jp/archives/70590</x:v>
       </x:c>
       <x:c r="G266" s="11" t="str">
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="H266" s="11" t="str">
-        <x:v>azone-body-pfl088-wht</x:v>
+        <x:v>azone-body-pfl103-wht</x:v>
       </x:c>
     </x:row>
     <x:row r="267" ht="72" customHeight="1">
       <x:c r="A267" s="11" t="str">
-        <x:v>Pure Neemo Flection · M · 白肌</x:v>
+        <x:v>Pure Neemo 2 Feel · S · 白肌</x:v>
       </x:c>
       <x:c r="B267" s="11" t="str">
         <x:v>补充来源</x:v>
       </x:c>
       <x:c r="C267" s="11" t="str">
-        <x:v>官方系列说明</x:v>
+        <x:v>官方配件适配说明</x:v>
       </x:c>
       <x:c r="D267" s="11" t="str">
-        <x:v>1/6 AZONE 原创素体介绍</x:v>
+        <x:v>Pure Neemo 2 换手：适用 Emotion／Feel 女孩 S、M</x:v>
       </x:c>
       <x:c r="E267" s="11" t="str">
-        <x:v>对应系列的可动结构；不借用旧批次配件、其他型号高度或库存。</x:v>
+        <x:v>PFL065 白肌换手的指定适用身体；不代表其他接口或全身配件通用。</x:v>
       </x:c>
       <x:c r="F267" s="11" t="str">
-        <x:v>https://news.azone-int.co.jp/archives/43318</x:v>
+        <x:v>https://www.azone-int.co.jp/?cid=126&amp;jancd=4573199928364&amp;sid=cdm502</x:v>
       </x:c>
       <x:c r="G267" s="11" t="str">
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="H267" s="11" t="str">
-        <x:v>azone-body-pfl088-wht</x:v>
+        <x:v>azone-body-pfl103-wht</x:v>
       </x:c>
     </x:row>
     <x:row r="268" ht="72" customHeight="1">
       <x:c r="A268" s="11" t="str">
-        <x:v>Picco Neemo · S 女孩 · 白肌</x:v>
+        <x:v>Pure Neemo 2 Feel · S · 白肌</x:v>
       </x:c>
       <x:c r="B268" s="11" t="str">
-        <x:v>主来源</x:v>
+        <x:v>补充来源</x:v>
       </x:c>
       <x:c r="C268" s="11" t="str">
-        <x:v>官方产品页</x:v>
+        <x:v>官方销售方式公告</x:v>
       </x:c>
       <x:c r="D268" s="11" t="str">
-        <x:v>1／12 ピコニーモS 女の子 PCN038-WHT</x:v>
+        <x:v>Pure Neemo 销售调整（8/27、9/1 更新）</x:v>
       </x:c>
       <x:c r="E268" s="11" t="str">
-        <x:v>本款独立素体、型号、尺寸口径、材料及配件范围；未披露项保留。</x:v>
+        <x:v>销售方式变化与适用系列；不作为本款库存或热度排名证据。</x:v>
       </x:c>
       <x:c r="F268" s="11" t="str">
-        <x:v>https://www.azone-int.co.jp/azonet/item/4573199841533</x:v>
+        <x:v>https://news.azone-int.co.jp/archives/70323</x:v>
       </x:c>
       <x:c r="G268" s="11" t="str">
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="H268" s="11" t="str">
-        <x:v>azone-body-pcn038-wht</x:v>
+        <x:v>azone-body-pfl103-wht</x:v>
       </x:c>
     </x:row>
     <x:row r="269" ht="72" customHeight="1">
       <x:c r="A269" s="11" t="str">
-        <x:v>Picco Neemo · S 女孩 · 白肌</x:v>
+        <x:v>Pure Neemo 2 Feel · M · 白肌</x:v>
       </x:c>
       <x:c r="B269" s="11" t="str">
-        <x:v>补充来源</x:v>
+        <x:v>主来源</x:v>
       </x:c>
       <x:c r="C269" s="11" t="str">
-        <x:v>官方系列说明</x:v>
+        <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D269" s="11" t="str">
-        <x:v>Picco Neemo / Flection 系列结构介绍</x:v>
+        <x:v>ピュアニーモ2フィール M／女の子 PFL104-WHT</x:v>
       </x:c>
       <x:c r="E269" s="11" t="str">
-        <x:v>对应系列的可动结构；不借用旧批次配件、其他型号高度或库存。</x:v>
+        <x:v>本款独立素体、型号、尺寸口径、材料及配件范围；未披露项保留。</x:v>
       </x:c>
       <x:c r="F269" s="11" t="str">
-        <x:v>https://www.azone-int.co.jp/?sid=pnm000</x:v>
+        <x:v>https://www.azone-int.co.jp/azonet/item/4573199849812</x:v>
       </x:c>
       <x:c r="G269" s="11" t="str">
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="H269" s="11" t="str">
-        <x:v>azone-body-pcn038-wht</x:v>
+        <x:v>azone-body-pfl104-wht</x:v>
       </x:c>
     </x:row>
     <x:row r="270" ht="72" customHeight="1">
       <x:c r="A270" s="11" t="str">
-        <x:v>Picco Neemo · M 女孩 · 白肌</x:v>
+        <x:v>Pure Neemo 2 Feel · M · 白肌</x:v>
       </x:c>
       <x:c r="B270" s="11" t="str">
-        <x:v>主来源</x:v>
+        <x:v>补充来源</x:v>
       </x:c>
       <x:c r="C270" s="11" t="str">
-        <x:v>官方产品页</x:v>
+        <x:v>官方系列说明</x:v>
       </x:c>
       <x:c r="D270" s="11" t="str">
-        <x:v>1／12 ピコニーモM 女の子 PCN043-WHT</x:v>
+        <x:v>1/6 AZONE 原创素体介绍</x:v>
       </x:c>
       <x:c r="E270" s="11" t="str">
-        <x:v>本款独立素体、型号、尺寸口径、材料及配件范围；未披露项保留。</x:v>
+        <x:v>对应系列的可动结构；不借用旧批次配件、其他型号高度或库存。</x:v>
       </x:c>
       <x:c r="F270" s="11" t="str">
-        <x:v>https://www.azone-int.co.jp/azonet/item/4573199841564</x:v>
+        <x:v>https://news.azone-int.co.jp/archives/43318</x:v>
       </x:c>
       <x:c r="G270" s="11" t="str">
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="H270" s="11" t="str">
-        <x:v>azone-body-pcn043-wht</x:v>
+        <x:v>azone-body-pfl104-wht</x:v>
       </x:c>
     </x:row>
     <x:row r="271" ht="72" customHeight="1">
       <x:c r="A271" s="11" t="str">
-        <x:v>Picco Neemo · M 女孩 · 白肌</x:v>
+        <x:v>Pure Neemo 2 Feel · M · 白肌</x:v>
       </x:c>
       <x:c r="B271" s="11" t="str">
         <x:v>补充来源</x:v>
       </x:c>
       <x:c r="C271" s="11" t="str">
-        <x:v>官方系列说明</x:v>
+        <x:v>官方配件改版通知</x:v>
       </x:c>
       <x:c r="D271" s="11" t="str">
-        <x:v>Picco Neemo / Flection 系列结构介绍</x:v>
+        <x:v>AZONE：2026 年 8 月起换手配件改版</x:v>
       </x:c>
       <x:c r="E271" s="11" t="str">
-        <x:v>对应系列的可动结构；不借用旧批次配件、其他型号高度或库存。</x:v>
+        <x:v>换手配件的新旧品番及内容变化；配件另售，不代表素体附送。</x:v>
       </x:c>
       <x:c r="F271" s="11" t="str">
-        <x:v>https://www.azone-int.co.jp/?sid=pnm000</x:v>
+        <x:v>https://news.azone-int.co.jp/archives/70590</x:v>
       </x:c>
       <x:c r="G271" s="11" t="str">
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="H271" s="11" t="str">
-        <x:v>azone-body-pcn043-wht</x:v>
+        <x:v>azone-body-pfl104-wht</x:v>
       </x:c>
     </x:row>
     <x:row r="272" ht="72" customHeight="1">
       <x:c r="A272" s="11" t="str">
-        <x:v>Picco Neemo · S 女孩 LL 胸 · 白肌</x:v>
+        <x:v>Pure Neemo 2 Feel · M · 白肌</x:v>
       </x:c>
       <x:c r="B272" s="11" t="str">
-        <x:v>主来源</x:v>
+        <x:v>补充来源</x:v>
       </x:c>
       <x:c r="C272" s="11" t="str">
-        <x:v>官方产品页</x:v>
+        <x:v>官方配件适配说明</x:v>
       </x:c>
       <x:c r="D272" s="11" t="str">
-        <x:v>1／12 ピコニーモS 女の子 LLバスト PCN041-WHT</x:v>
+        <x:v>Pure Neemo 2 换手：适用 Emotion／Feel 女孩 S、M</x:v>
       </x:c>
       <x:c r="E272" s="11" t="str">
-        <x:v>本款独立素体、型号、尺寸口径、材料及配件范围；未披露项保留。</x:v>
+        <x:v>PFL065 白肌换手的指定适用身体；不代表其他接口或全身配件通用。</x:v>
       </x:c>
       <x:c r="F272" s="11" t="str">
-        <x:v>https://www.azone-int.co.jp/azonet/item/4573199841540</x:v>
+        <x:v>https://www.azone-int.co.jp/?cid=126&amp;jancd=4573199928364&amp;sid=cdm502</x:v>
       </x:c>
       <x:c r="G272" s="11" t="str">
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="H272" s="11" t="str">
-        <x:v>azone-body-pcn041-wht</x:v>
+        <x:v>azone-body-pfl104-wht</x:v>
       </x:c>
     </x:row>
     <x:row r="273" ht="72" customHeight="1">
       <x:c r="A273" s="11" t="str">
-        <x:v>Picco Neemo · S 女孩 LL 胸 · 白肌</x:v>
+        <x:v>Pure Neemo 2 Feel · M · 白肌</x:v>
       </x:c>
       <x:c r="B273" s="11" t="str">
         <x:v>补充来源</x:v>
       </x:c>
       <x:c r="C273" s="11" t="str">
-        <x:v>官方系列说明</x:v>
+        <x:v>官方销售方式公告</x:v>
       </x:c>
       <x:c r="D273" s="11" t="str">
-        <x:v>Picco Neemo / Flection 系列结构介绍</x:v>
+        <x:v>Pure Neemo 销售调整（8/27、9/1 更新）</x:v>
       </x:c>
       <x:c r="E273" s="11" t="str">
-        <x:v>对应系列的可动结构；不借用旧批次配件、其他型号高度或库存。</x:v>
+        <x:v>销售方式变化与适用系列；不作为本款库存或热度排名证据。</x:v>
       </x:c>
       <x:c r="F273" s="11" t="str">
-        <x:v>https://www.azone-int.co.jp/?sid=pnm000</x:v>
+        <x:v>https://news.azone-int.co.jp/archives/70323</x:v>
       </x:c>
       <x:c r="G273" s="11" t="str">
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="H273" s="11" t="str">
-        <x:v>azone-body-pcn041-wht</x:v>
+        <x:v>azone-body-pfl104-wht</x:v>
       </x:c>
     </x:row>
     <x:row r="274" ht="72" customHeight="1">
       <x:c r="A274" s="11" t="str">
-        <x:v>Picco Neemo · S 女孩 3L 胸 · 白肌</x:v>
+        <x:v>Pure Neemo 2 Emotion · S · 白肌</x:v>
       </x:c>
       <x:c r="B274" s="11" t="str">
         <x:v>主来源</x:v>
@@ -24691,24 +24836,24 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D274" s="11" t="str">
-        <x:v>1／12 ピコニーモS 女の子 3Lバスト PCN042-WHT</x:v>
+        <x:v>ピュアニーモ2エモーション S／女の子 PFL099-WHT</x:v>
       </x:c>
       <x:c r="E274" s="11" t="str">
         <x:v>本款独立素体、型号、尺寸口径、材料及配件范围；未披露项保留。</x:v>
       </x:c>
       <x:c r="F274" s="11" t="str">
-        <x:v>https://www.azone-int.co.jp/azonet/item/4573199841557</x:v>
+        <x:v>https://www.azone-int.co.jp/azonet/item/4573199846163</x:v>
       </x:c>
       <x:c r="G274" s="11" t="str">
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="H274" s="11" t="str">
-        <x:v>azone-body-pcn042-wht</x:v>
+        <x:v>azone-body-pfl099-wht</x:v>
       </x:c>
     </x:row>
     <x:row r="275" ht="72" customHeight="1">
       <x:c r="A275" s="11" t="str">
-        <x:v>Picco Neemo · S 女孩 3L 胸 · 白肌</x:v>
+        <x:v>Pure Neemo 2 Emotion · S · 白肌</x:v>
       </x:c>
       <x:c r="B275" s="11" t="str">
         <x:v>补充来源</x:v>
@@ -24717,232 +24862,232 @@
         <x:v>官方系列说明</x:v>
       </x:c>
       <x:c r="D275" s="11" t="str">
-        <x:v>Picco Neemo / Flection 系列结构介绍</x:v>
+        <x:v>1/6 AZONE 原创素体介绍</x:v>
       </x:c>
       <x:c r="E275" s="11" t="str">
         <x:v>对应系列的可动结构；不借用旧批次配件、其他型号高度或库存。</x:v>
       </x:c>
       <x:c r="F275" s="11" t="str">
-        <x:v>https://www.azone-int.co.jp/?sid=pnm000</x:v>
+        <x:v>https://news.azone-int.co.jp/archives/43318</x:v>
       </x:c>
       <x:c r="G275" s="11" t="str">
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="H275" s="11" t="str">
-        <x:v>azone-body-pcn042-wht</x:v>
+        <x:v>azone-body-pfl099-wht</x:v>
       </x:c>
     </x:row>
     <x:row r="276" ht="72" customHeight="1">
       <x:c r="A276" s="11" t="str">
-        <x:v>Picco Neemo D · 弟弟 · 白肌</x:v>
+        <x:v>Pure Neemo 2 Emotion · S · 白肌</x:v>
       </x:c>
       <x:c r="B276" s="11" t="str">
-        <x:v>主来源</x:v>
+        <x:v>补充来源</x:v>
       </x:c>
       <x:c r="C276" s="11" t="str">
-        <x:v>官方产品页</x:v>
+        <x:v>官方配件改版通知</x:v>
       </x:c>
       <x:c r="D276" s="11" t="str">
-        <x:v>1／12 ピコニーモD 弟 PCN048-WHT</x:v>
+        <x:v>AZONE：2026 年 8 月起换手配件改版</x:v>
       </x:c>
       <x:c r="E276" s="11" t="str">
-        <x:v>本款独立素体、型号、尺寸口径、材料及配件范围；未披露项保留。</x:v>
+        <x:v>换手配件的新旧品番及内容变化；配件另售，不代表素体附送。</x:v>
       </x:c>
       <x:c r="F276" s="11" t="str">
-        <x:v>https://www.azone-int.co.jp/azonet/item/4573199848051</x:v>
+        <x:v>https://news.azone-int.co.jp/archives/70590</x:v>
       </x:c>
       <x:c r="G276" s="11" t="str">
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="H276" s="11" t="str">
-        <x:v>azone-body-pcn048-wht</x:v>
+        <x:v>azone-body-pfl099-wht</x:v>
       </x:c>
     </x:row>
     <x:row r="277" ht="72" customHeight="1">
       <x:c r="A277" s="11" t="str">
-        <x:v>Picco Neemo D · 弟弟 · 白肌</x:v>
+        <x:v>Pure Neemo 2 Emotion · S · 白肌</x:v>
       </x:c>
       <x:c r="B277" s="11" t="str">
         <x:v>补充来源</x:v>
       </x:c>
       <x:c r="C277" s="11" t="str">
-        <x:v>官方系列说明</x:v>
+        <x:v>官方配件适配说明</x:v>
       </x:c>
       <x:c r="D277" s="11" t="str">
-        <x:v>Picco Neemo / Flection 系列结构介绍</x:v>
+        <x:v>Pure Neemo 2 换手：适用 Emotion／Feel 女孩 S、M</x:v>
       </x:c>
       <x:c r="E277" s="11" t="str">
-        <x:v>对应系列的可动结构；不借用旧批次配件、其他型号高度或库存。</x:v>
+        <x:v>PFL065 白肌换手的指定适用身体；不代表其他接口或全身配件通用。</x:v>
       </x:c>
       <x:c r="F277" s="11" t="str">
-        <x:v>https://www.azone-int.co.jp/?sid=pnm000</x:v>
+        <x:v>https://www.azone-int.co.jp/?cid=126&amp;jancd=4573199928364&amp;sid=cdm502</x:v>
       </x:c>
       <x:c r="G277" s="11" t="str">
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="H277" s="11" t="str">
-        <x:v>azone-body-pcn048-wht</x:v>
+        <x:v>azone-body-pfl099-wht</x:v>
       </x:c>
     </x:row>
     <x:row r="278" ht="72" customHeight="1">
       <x:c r="A278" s="11" t="str">
-        <x:v>OBITSU 26 cm · S 胸</x:v>
+        <x:v>Pure Neemo 2 Emotion · S · 白肌</x:v>
       </x:c>
       <x:c r="B278" s="11" t="str">
-        <x:v>主来源</x:v>
+        <x:v>补充来源</x:v>
       </x:c>
       <x:c r="C278" s="11" t="str">
-        <x:v>官方产品页</x:v>
+        <x:v>官方销售方式公告</x:v>
       </x:c>
       <x:c r="D278" s="11" t="str">
-        <x:v>26BD-F01N-S / OBITSU BODY 26</x:v>
+        <x:v>Pure Neemo 销售调整（8/27、9/1 更新）</x:v>
       </x:c>
       <x:c r="E278" s="11" t="str">
-        <x:v>本款独立素体、型号、尺寸口径、材料及配件范围；未披露项保留。</x:v>
+        <x:v>销售方式变化与适用系列；不作为本款库存或热度排名证据。</x:v>
       </x:c>
       <x:c r="F278" s="11" t="str">
-        <x:v>https://obitsu.co.jp/doll-division/obitsu-body-and-parts/obitsu-body/obitsu-body-26/</x:v>
+        <x:v>https://news.azone-int.co.jp/archives/70323</x:v>
       </x:c>
       <x:c r="G278" s="11" t="str">
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="H278" s="11" t="str">
-        <x:v>bare-26bd-f01n-s</x:v>
+        <x:v>azone-body-pfl099-wht</x:v>
       </x:c>
     </x:row>
     <x:row r="279" ht="72" customHeight="1">
       <x:c r="A279" s="11" t="str">
-        <x:v>OBITSU 26 cm · S 胸</x:v>
+        <x:v>Pure Neemo 2 Emotion · M · 白肌</x:v>
       </x:c>
       <x:c r="B279" s="11" t="str">
-        <x:v>补充来源</x:v>
+        <x:v>主来源</x:v>
       </x:c>
       <x:c r="C279" s="11" t="str">
-        <x:v>官方商店型号链接</x:v>
+        <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D279" s="11" t="str">
-        <x:v>【26BD-F01N-S】26cmオビツボディ バストサイズS ナチュラル</x:v>
+        <x:v>ピュアニーモ2エモーション M／女の子 PFL100-WHT</x:v>
       </x:c>
       <x:c r="E279" s="11" t="str">
-        <x:v>厂家型号说明页直接列出的对应 SKU；库存未单独核对。</x:v>
+        <x:v>本款独立素体、型号、尺寸口径、材料及配件范围；未披露项保留。</x:v>
       </x:c>
       <x:c r="F279" s="11" t="str">
-        <x:v>https://www.obitsushop.com/SHOP/26BD-F01N-S.html</x:v>
+        <x:v>https://www.azone-int.co.jp/azonet/item/4573199846187</x:v>
       </x:c>
       <x:c r="G279" s="11" t="str">
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="H279" s="11" t="str">
-        <x:v>bare-26bd-f01n-s</x:v>
+        <x:v>azone-body-pfl100-wht</x:v>
       </x:c>
     </x:row>
     <x:row r="280" ht="72" customHeight="1">
       <x:c r="A280" s="11" t="str">
-        <x:v>OBITSU 27 cm · 男性 Slim</x:v>
+        <x:v>Pure Neemo 2 Emotion · M · 白肌</x:v>
       </x:c>
       <x:c r="B280" s="11" t="str">
-        <x:v>主来源</x:v>
+        <x:v>补充来源</x:v>
       </x:c>
       <x:c r="C280" s="11" t="str">
-        <x:v>官方产品页</x:v>
+        <x:v>官方系列说明</x:v>
       </x:c>
       <x:c r="D280" s="11" t="str">
-        <x:v>27BD-M03N / OBITSU BODY 27 MEN Slim</x:v>
+        <x:v>1/6 AZONE 原创素体介绍</x:v>
       </x:c>
       <x:c r="E280" s="11" t="str">
-        <x:v>本款独立素体、型号、尺寸口径、材料及配件范围；未披露项保留。</x:v>
+        <x:v>对应系列的可动结构；不借用旧批次配件、其他型号高度或库存。</x:v>
       </x:c>
       <x:c r="F280" s="11" t="str">
-        <x:v>https://obitsu.co.jp/doll-division/obitsu-body-and-parts/obitsu-body/obitsu-body-27-m/</x:v>
+        <x:v>https://news.azone-int.co.jp/archives/43318</x:v>
       </x:c>
       <x:c r="G280" s="11" t="str">
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="H280" s="11" t="str">
-        <x:v>bare-27bd-m03n</x:v>
+        <x:v>azone-body-pfl100-wht</x:v>
       </x:c>
     </x:row>
     <x:row r="281" ht="72" customHeight="1">
       <x:c r="A281" s="11" t="str">
-        <x:v>OBITSU 27 cm · 男性 Slim</x:v>
+        <x:v>Pure Neemo 2 Emotion · M · 白肌</x:v>
       </x:c>
       <x:c r="B281" s="11" t="str">
         <x:v>补充来源</x:v>
       </x:c>
       <x:c r="C281" s="11" t="str">
-        <x:v>官方商店型号链接</x:v>
+        <x:v>官方配件改版通知</x:v>
       </x:c>
       <x:c r="D281" s="11" t="str">
-        <x:v>【27BD-M03N】男性ボディ　スリム(新型)　ナチュラル</x:v>
+        <x:v>AZONE：2026 年 8 月起换手配件改版</x:v>
       </x:c>
       <x:c r="E281" s="11" t="str">
-        <x:v>厂家型号说明页直接列出的对应 SKU；库存未单独核对。</x:v>
+        <x:v>换手配件的新旧品番及内容变化；配件另售，不代表素体附送。</x:v>
       </x:c>
       <x:c r="F281" s="11" t="str">
-        <x:v>https://www.obitsushop.com/SHOP/27BD-M03N.html</x:v>
+        <x:v>https://news.azone-int.co.jp/archives/70590</x:v>
       </x:c>
       <x:c r="G281" s="11" t="str">
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="H281" s="11" t="str">
-        <x:v>bare-27bd-m03n</x:v>
+        <x:v>azone-body-pfl100-wht</x:v>
       </x:c>
     </x:row>
     <x:row r="282" ht="72" customHeight="1">
       <x:c r="A282" s="11" t="str">
-        <x:v>OBITSU 27 cm · 女性 SBH M 胸</x:v>
+        <x:v>Pure Neemo 2 Emotion · M · 白肌</x:v>
       </x:c>
       <x:c r="B282" s="11" t="str">
-        <x:v>主来源</x:v>
+        <x:v>补充来源</x:v>
       </x:c>
       <x:c r="C282" s="11" t="str">
-        <x:v>官方产品页</x:v>
+        <x:v>官方配件适配说明</x:v>
       </x:c>
       <x:c r="D282" s="11" t="str">
-        <x:v>27BD-F06N / OBITSU BODY 27 WOMAN – SBH</x:v>
+        <x:v>Pure Neemo 2 换手：适用 Emotion／Feel 女孩 S、M</x:v>
       </x:c>
       <x:c r="E282" s="11" t="str">
-        <x:v>本款独立素体、型号、尺寸口径、材料及配件范围；未披露项保留。</x:v>
+        <x:v>PFL065 白肌换手的指定适用身体；不代表其他接口或全身配件通用。</x:v>
       </x:c>
       <x:c r="F282" s="11" t="str">
-        <x:v>https://obitsu.co.jp/doll-division/obitsu-body-and-parts/obitsu-body/obitsu-body-27woman-sbh/</x:v>
+        <x:v>https://www.azone-int.co.jp/?cid=126&amp;jancd=4573199928364&amp;sid=cdm502</x:v>
       </x:c>
       <x:c r="G282" s="11" t="str">
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="H282" s="11" t="str">
-        <x:v>bare-27bd-f06n</x:v>
+        <x:v>azone-body-pfl100-wht</x:v>
       </x:c>
     </x:row>
     <x:row r="283" ht="72" customHeight="1">
       <x:c r="A283" s="11" t="str">
-        <x:v>OBITSU 27 cm · 女性 SBH M 胸</x:v>
+        <x:v>Pure Neemo 2 Emotion · M · 白肌</x:v>
       </x:c>
       <x:c r="B283" s="11" t="str">
         <x:v>补充来源</x:v>
       </x:c>
       <x:c r="C283" s="11" t="str">
-        <x:v>官方商店型号链接</x:v>
+        <x:v>官方销售方式公告</x:v>
       </x:c>
       <x:c r="D283" s="11" t="str">
-        <x:v>【27BD-F06N】女性バージョン　SBH-M胸　ナチュラル</x:v>
+        <x:v>Pure Neemo 销售调整（8/27、9/1 更新）</x:v>
       </x:c>
       <x:c r="E283" s="11" t="str">
-        <x:v>厂家型号说明页直接列出的对应 SKU；库存未单独核对。</x:v>
+        <x:v>销售方式变化与适用系列；不作为本款库存或热度排名证据。</x:v>
       </x:c>
       <x:c r="F283" s="11" t="str">
-        <x:v>https://www.obitsushop.com/SHOP/27BD-F06N.html</x:v>
+        <x:v>https://news.azone-int.co.jp/archives/70323</x:v>
       </x:c>
       <x:c r="G283" s="11" t="str">
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="H283" s="11" t="str">
-        <x:v>bare-27bd-f06n</x:v>
+        <x:v>azone-body-pfl100-wht</x:v>
       </x:c>
     </x:row>
     <x:row r="284" ht="72" customHeight="1">
       <x:c r="A284" s="11" t="str">
-        <x:v>OBITSU 30 cm · 男性素体</x:v>
+        <x:v>Pure Neemo Flection · M · 白肌</x:v>
       </x:c>
       <x:c r="B284" s="11" t="str">
         <x:v>主来源</x:v>
@@ -24951,128 +25096,128 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D284" s="11" t="str">
-        <x:v>30BD-M01N / OBITSU BODY30</x:v>
+        <x:v>ピュアニーモフレクション M／女の子 PFL088-WHT</x:v>
       </x:c>
       <x:c r="E284" s="11" t="str">
         <x:v>本款独立素体、型号、尺寸口径、材料及配件范围；未披露项保留。</x:v>
       </x:c>
       <x:c r="F284" s="11" t="str">
-        <x:v>https://obitsu.co.jp/doll-division/obitsu-body-and-parts/obitsu-body/obitsu-body30/</x:v>
+        <x:v>https://www.azone-int.co.jp/azonet/item/4573199841397</x:v>
       </x:c>
       <x:c r="G284" s="11" t="str">
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="H284" s="11" t="str">
-        <x:v>bare-30bd-m01n</x:v>
+        <x:v>azone-body-pfl088-wht</x:v>
       </x:c>
     </x:row>
     <x:row r="285" ht="72" customHeight="1">
       <x:c r="A285" s="11" t="str">
-        <x:v>OBITSU 30 cm · 男性素体</x:v>
+        <x:v>Pure Neemo Flection · M · 白肌</x:v>
       </x:c>
       <x:c r="B285" s="11" t="str">
         <x:v>补充来源</x:v>
       </x:c>
       <x:c r="C285" s="11" t="str">
-        <x:v>官方商店型号链接</x:v>
+        <x:v>官方系列说明</x:v>
       </x:c>
       <x:c r="D285" s="11" t="str">
-        <x:v>【30BD-M01N】30cmオビツボディ ナチュラル</x:v>
+        <x:v>1/6 AZONE 原创素体介绍</x:v>
       </x:c>
       <x:c r="E285" s="11" t="str">
-        <x:v>厂家型号说明页直接列出的对应 SKU；库存未单独核对。</x:v>
+        <x:v>对应系列的可动结构；不借用旧批次配件、其他型号高度或库存。</x:v>
       </x:c>
       <x:c r="F285" s="11" t="str">
-        <x:v>https://www.obitsushop.com/SHOP/30BD-M01N.html</x:v>
+        <x:v>https://news.azone-int.co.jp/archives/43318</x:v>
       </x:c>
       <x:c r="G285" s="11" t="str">
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="H285" s="11" t="str">
-        <x:v>bare-30bd-m01n</x:v>
+        <x:v>azone-body-pfl088-wht</x:v>
       </x:c>
     </x:row>
     <x:row r="286" ht="72" customHeight="1">
       <x:c r="A286" s="11" t="str">
-        <x:v>OBITSU Ver.1.5 · GGR50 M 胸</x:v>
+        <x:v>Pure Neemo Flection · M · 白肌</x:v>
       </x:c>
       <x:c r="B286" s="11" t="str">
-        <x:v>主来源</x:v>
+        <x:v>补充来源</x:v>
       </x:c>
       <x:c r="C286" s="11" t="str">
-        <x:v>官方产品页</x:v>
+        <x:v>官方配件改版通知</x:v>
       </x:c>
       <x:c r="D286" s="11" t="str">
-        <x:v>50BD-GGRW-G / OBITSU BODY Ver1.5 GGR50</x:v>
+        <x:v>AZONE：2026 年 8 月起换手配件改版</x:v>
       </x:c>
       <x:c r="E286" s="11" t="str">
-        <x:v>本款独立素体、型号、尺寸口径、材料及配件范围；未披露项保留。</x:v>
+        <x:v>换手配件的新旧品番及内容变化；配件另售，不代表素体附送。</x:v>
       </x:c>
       <x:c r="F286" s="11" t="str">
-        <x:v>https://obitsu.co.jp/doll-division/obitsu-body-and-parts/obitsu-body/obitsu-body-ver1-5-ggr50/</x:v>
+        <x:v>https://news.azone-int.co.jp/archives/70590</x:v>
       </x:c>
       <x:c r="G286" s="11" t="str">
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="H286" s="11" t="str">
-        <x:v>bare-50bd-ggrw-g</x:v>
+        <x:v>azone-body-pfl088-wht</x:v>
       </x:c>
     </x:row>
     <x:row r="287" ht="72" customHeight="1">
       <x:c r="A287" s="11" t="str">
-        <x:v>OBITSU Ver.1.5 · GGR50 M 胸</x:v>
+        <x:v>Pure Neemo Flection · M · 白肌</x:v>
       </x:c>
       <x:c r="B287" s="11" t="str">
         <x:v>补充来源</x:v>
       </x:c>
       <x:c r="C287" s="11" t="str">
-        <x:v>官方商店型号链接</x:v>
+        <x:v>官方身体改版说明</x:v>
       </x:c>
       <x:c r="D287" s="11" t="str">
-        <x:v>【50BD-GGRW-G】50cmオビツボディ Ver1.5 GGR50　ホワイティ</x:v>
+        <x:v>Flection S／M：新模具与默认手型变化</x:v>
       </x:c>
       <x:c r="E287" s="11" t="str">
-        <x:v>厂家型号说明页直接列出的对应 SKU；库存未单独核对。</x:v>
+        <x:v>默认手型、新旧模具的换手与松紧／色差限制。</x:v>
       </x:c>
       <x:c r="F287" s="11" t="str">
-        <x:v>https://www.obitsushop.com/SHOP/50BD-GGRW-G.html</x:v>
+        <x:v>https://news.azone-int.co.jp/archives/48837</x:v>
       </x:c>
       <x:c r="G287" s="11" t="str">
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="H287" s="11" t="str">
-        <x:v>bare-50bd-ggrw-g</x:v>
+        <x:v>azone-body-pfl088-wht</x:v>
       </x:c>
     </x:row>
     <x:row r="288" ht="72" customHeight="1">
       <x:c r="A288" s="11" t="str">
-        <x:v>PICCODO · CHUBBY BODY</x:v>
+        <x:v>Pure Neemo Flection · M · 白肌</x:v>
       </x:c>
       <x:c r="B288" s="11" t="str">
-        <x:v>主来源</x:v>
+        <x:v>补充来源</x:v>
       </x:c>
       <x:c r="C288" s="11" t="str">
-        <x:v>官方产品页</x:v>
+        <x:v>官方销售方式公告</x:v>
       </x:c>
       <x:c r="D288" s="11" t="str">
-        <x:v>PICCODO CHUBBY BODY</x:v>
+        <x:v>Pure Neemo 销售调整（8/27、9/1 更新）</x:v>
       </x:c>
       <x:c r="E288" s="11" t="str">
-        <x:v>本款独立素体、型号、尺寸口径、材料及配件范围；未披露项保留。</x:v>
+        <x:v>销售方式变化与适用系列；不作为本款库存或热度排名证据。</x:v>
       </x:c>
       <x:c r="F288" s="11" t="str">
-        <x:v>https://piccodo.official.ec/items/118319611</x:v>
+        <x:v>https://news.azone-int.co.jp/archives/70323</x:v>
       </x:c>
       <x:c r="G288" s="11" t="str">
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="H288" s="11" t="str">
-        <x:v>piccodo-118319611</x:v>
+        <x:v>azone-body-pfl088-wht</x:v>
       </x:c>
     </x:row>
     <x:row r="289" ht="72" customHeight="1">
       <x:c r="A289" s="11" t="str">
-        <x:v>PICCODO · BODY11</x:v>
+        <x:v>Picco Neemo · S 女孩 · 白肌</x:v>
       </x:c>
       <x:c r="B289" s="11" t="str">
         <x:v>主来源</x:v>
@@ -25081,50 +25226,50 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D289" s="11" t="str">
-        <x:v>PICCODO BODY11</x:v>
+        <x:v>1／12 ピコニーモS 女の子 PCN038-WHT</x:v>
       </x:c>
       <x:c r="E289" s="11" t="str">
         <x:v>本款独立素体、型号、尺寸口径、材料及配件范围；未披露项保留。</x:v>
       </x:c>
       <x:c r="F289" s="11" t="str">
-        <x:v>https://piccodo.official.ec/items/115850461</x:v>
+        <x:v>https://www.azone-int.co.jp/azonet/item/4573199841533</x:v>
       </x:c>
       <x:c r="G289" s="11" t="str">
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="H289" s="11" t="str">
-        <x:v>piccodo-115850461</x:v>
+        <x:v>azone-body-pcn038-wht</x:v>
       </x:c>
     </x:row>
     <x:row r="290" ht="72" customHeight="1">
       <x:c r="A290" s="11" t="str">
-        <x:v>PICCODO · BODY10 Ver.2.0</x:v>
+        <x:v>Picco Neemo · S 女孩 · 白肌</x:v>
       </x:c>
       <x:c r="B290" s="11" t="str">
-        <x:v>主来源</x:v>
+        <x:v>补充来源</x:v>
       </x:c>
       <x:c r="C290" s="11" t="str">
-        <x:v>官方产品页</x:v>
+        <x:v>官方型号与配件目录</x:v>
       </x:c>
       <x:c r="D290" s="11" t="str">
-        <x:v>PICCODO BODY10 Ver.2.0</x:v>
+        <x:v>AZONE：1/12 Picco Neemo 素体与配件</x:v>
       </x:c>
       <x:c r="E290" s="11" t="str">
-        <x:v>本款独立素体、型号、尺寸口径、材料及配件范围；未披露项保留。</x:v>
+        <x:v>核对当前 PCN 型号及 S／M、D、P 各自的换手和关节配件。</x:v>
       </x:c>
       <x:c r="F290" s="11" t="str">
-        <x:v>https://piccodo.official.ec/items/76733551</x:v>
+        <x:v>https://news.azone-int.co.jp/archives/43183</x:v>
       </x:c>
       <x:c r="G290" s="11" t="str">
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="H290" s="11" t="str">
-        <x:v>piccodo-76733551</x:v>
+        <x:v>azone-body-pcn038-wht</x:v>
       </x:c>
     </x:row>
     <x:row r="291" ht="72" customHeight="1">
       <x:c r="A291" s="11" t="str">
-        <x:v>PICCODO · BODY9 Ver.2.0</x:v>
+        <x:v>Picco Neemo · M 女孩 · 白肌</x:v>
       </x:c>
       <x:c r="B291" s="11" t="str">
         <x:v>主来源</x:v>
@@ -25133,50 +25278,50 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D291" s="11" t="str">
-        <x:v>PICCODO BODY9 Ver.2.0</x:v>
+        <x:v>1／12 ピコニーモM 女の子 PCN043-WHT</x:v>
       </x:c>
       <x:c r="E291" s="11" t="str">
         <x:v>本款独立素体、型号、尺寸口径、材料及配件范围；未披露项保留。</x:v>
       </x:c>
       <x:c r="F291" s="11" t="str">
-        <x:v>https://piccodo.official.ec/items/76732953</x:v>
+        <x:v>https://www.azone-int.co.jp/azonet/item/4573199841564</x:v>
       </x:c>
       <x:c r="G291" s="11" t="str">
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="H291" s="11" t="str">
-        <x:v>piccodo-76732953</x:v>
+        <x:v>azone-body-pcn043-wht</x:v>
       </x:c>
     </x:row>
     <x:row r="292" ht="72" customHeight="1">
       <x:c r="A292" s="11" t="str">
-        <x:v>PICCODO · CUTE BODY10</x:v>
+        <x:v>Picco Neemo · M 女孩 · 白肌</x:v>
       </x:c>
       <x:c r="B292" s="11" t="str">
-        <x:v>主来源</x:v>
+        <x:v>补充来源</x:v>
       </x:c>
       <x:c r="C292" s="11" t="str">
-        <x:v>官方产品页</x:v>
+        <x:v>官方型号与配件目录</x:v>
       </x:c>
       <x:c r="D292" s="11" t="str">
-        <x:v>PICCODO CUTE BODY10</x:v>
+        <x:v>AZONE：1/12 Picco Neemo 素体与配件</x:v>
       </x:c>
       <x:c r="E292" s="11" t="str">
-        <x:v>本款独立素体、型号、尺寸口径、材料及配件范围；未披露项保留。</x:v>
+        <x:v>核对当前 PCN 型号及 S／M、D、P 各自的换手和关节配件。</x:v>
       </x:c>
       <x:c r="F292" s="11" t="str">
-        <x:v>https://piccodo.official.ec/items/72696060</x:v>
+        <x:v>https://news.azone-int.co.jp/archives/43183</x:v>
       </x:c>
       <x:c r="G292" s="11" t="str">
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="H292" s="11" t="str">
-        <x:v>piccodo-72696060</x:v>
+        <x:v>azone-body-pcn043-wht</x:v>
       </x:c>
     </x:row>
     <x:row r="293" ht="72" customHeight="1">
       <x:c r="A293" s="11" t="str">
-        <x:v>PICCODO · BODY20</x:v>
+        <x:v>Picco Neemo · S 女孩 LL 胸 · 白肌</x:v>
       </x:c>
       <x:c r="B293" s="11" t="str">
         <x:v>主来源</x:v>
@@ -25185,45 +25330,799 @@
         <x:v>官方产品页</x:v>
       </x:c>
       <x:c r="D293" s="11" t="str">
-        <x:v>PICCODO BODY20</x:v>
+        <x:v>1／12 ピコニーモS 女の子 LLバスト PCN041-WHT</x:v>
       </x:c>
       <x:c r="E293" s="11" t="str">
         <x:v>本款独立素体、型号、尺寸口径、材料及配件范围；未披露项保留。</x:v>
       </x:c>
       <x:c r="F293" s="11" t="str">
-        <x:v>https://piccodo.official.ec/items/72695579</x:v>
+        <x:v>https://www.azone-int.co.jp/azonet/item/4573199841540</x:v>
       </x:c>
       <x:c r="G293" s="11" t="str">
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="H293" s="11" t="str">
-        <x:v>piccodo-72695579</x:v>
+        <x:v>azone-body-pcn041-wht</x:v>
       </x:c>
     </x:row>
     <x:row r="294" ht="72" customHeight="1">
       <x:c r="A294" s="11" t="str">
-        <x:v>PICCODO · BODY8 PLUS</x:v>
+        <x:v>Picco Neemo · S 女孩 LL 胸 · 白肌</x:v>
       </x:c>
       <x:c r="B294" s="11" t="str">
-        <x:v>主来源</x:v>
+        <x:v>补充来源</x:v>
       </x:c>
       <x:c r="C294" s="11" t="str">
-        <x:v>官方产品页</x:v>
+        <x:v>官方型号与配件目录</x:v>
       </x:c>
       <x:c r="D294" s="11" t="str">
-        <x:v>PICCODO BODY8 PLUS</x:v>
+        <x:v>AZONE：1/12 Picco Neemo 素体与配件</x:v>
       </x:c>
       <x:c r="E294" s="11" t="str">
-        <x:v>本款独立素体、型号、尺寸口径、材料及配件范围；未披露项保留。</x:v>
+        <x:v>核对当前 PCN 型号及 S／M、D、P 各自的换手和关节配件。</x:v>
       </x:c>
       <x:c r="F294" s="11" t="str">
-        <x:v>https://piccodo.official.ec/items/72138227</x:v>
+        <x:v>https://news.azone-int.co.jp/archives/43183</x:v>
       </x:c>
       <x:c r="G294" s="11" t="str">
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="H294" s="11" t="str">
+        <x:v>azone-body-pcn041-wht</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="295" ht="72" customHeight="1">
+      <x:c r="A295" s="11" t="str">
+        <x:v>Picco Neemo · S 女孩 3L 胸 · 白肌</x:v>
+      </x:c>
+      <x:c r="B295" s="11" t="str">
+        <x:v>主来源</x:v>
+      </x:c>
+      <x:c r="C295" s="11" t="str">
+        <x:v>官方产品页</x:v>
+      </x:c>
+      <x:c r="D295" s="11" t="str">
+        <x:v>1／12 ピコニーモS 女の子 3Lバスト PCN042-WHT</x:v>
+      </x:c>
+      <x:c r="E295" s="11" t="str">
+        <x:v>本款独立素体、型号、尺寸口径、材料及配件范围；未披露项保留。</x:v>
+      </x:c>
+      <x:c r="F295" s="11" t="str">
+        <x:v>https://www.azone-int.co.jp/azonet/item/4573199841557</x:v>
+      </x:c>
+      <x:c r="G295" s="11" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="H295" s="11" t="str">
+        <x:v>azone-body-pcn042-wht</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="296" ht="72" customHeight="1">
+      <x:c r="A296" s="11" t="str">
+        <x:v>Picco Neemo · S 女孩 3L 胸 · 白肌</x:v>
+      </x:c>
+      <x:c r="B296" s="11" t="str">
+        <x:v>补充来源</x:v>
+      </x:c>
+      <x:c r="C296" s="11" t="str">
+        <x:v>官方型号与配件目录</x:v>
+      </x:c>
+      <x:c r="D296" s="11" t="str">
+        <x:v>AZONE：1/12 Picco Neemo 素体与配件</x:v>
+      </x:c>
+      <x:c r="E296" s="11" t="str">
+        <x:v>核对当前 PCN 型号及 S／M、D、P 各自的换手和关节配件。</x:v>
+      </x:c>
+      <x:c r="F296" s="11" t="str">
+        <x:v>https://news.azone-int.co.jp/archives/43183</x:v>
+      </x:c>
+      <x:c r="G296" s="11" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="H296" s="11" t="str">
+        <x:v>azone-body-pcn042-wht</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="297" ht="72" customHeight="1">
+      <x:c r="A297" s="11" t="str">
+        <x:v>Picco Neemo D · 弟弟 · 白肌</x:v>
+      </x:c>
+      <x:c r="B297" s="11" t="str">
+        <x:v>主来源</x:v>
+      </x:c>
+      <x:c r="C297" s="11" t="str">
+        <x:v>官方产品页</x:v>
+      </x:c>
+      <x:c r="D297" s="11" t="str">
+        <x:v>1／12 ピコニーモD 弟 PCN048-WHT</x:v>
+      </x:c>
+      <x:c r="E297" s="11" t="str">
+        <x:v>本款独立素体、型号、尺寸口径、材料及配件范围；未披露项保留。</x:v>
+      </x:c>
+      <x:c r="F297" s="11" t="str">
+        <x:v>https://www.azone-int.co.jp/azonet/item/4573199848051</x:v>
+      </x:c>
+      <x:c r="G297" s="11" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="H297" s="11" t="str">
+        <x:v>azone-body-pcn048-wht</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="298" ht="72" customHeight="1">
+      <x:c r="A298" s="11" t="str">
+        <x:v>Picco Neemo D · 弟弟 · 白肌</x:v>
+      </x:c>
+      <x:c r="B298" s="11" t="str">
+        <x:v>补充来源</x:v>
+      </x:c>
+      <x:c r="C298" s="11" t="str">
+        <x:v>官方型号与配件目录</x:v>
+      </x:c>
+      <x:c r="D298" s="11" t="str">
+        <x:v>AZONE：1/12 Picco Neemo 素体与配件</x:v>
+      </x:c>
+      <x:c r="E298" s="11" t="str">
+        <x:v>核对当前 PCN 型号及 S／M、D、P 各自的换手和关节配件。</x:v>
+      </x:c>
+      <x:c r="F298" s="11" t="str">
+        <x:v>https://news.azone-int.co.jp/archives/43183</x:v>
+      </x:c>
+      <x:c r="G298" s="11" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="H298" s="11" t="str">
+        <x:v>azone-body-pcn048-wht</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="299" ht="72" customHeight="1">
+      <x:c r="A299" s="11" t="str">
+        <x:v>Picco Neemo D · 弟弟 · 白肌</x:v>
+      </x:c>
+      <x:c r="B299" s="11" t="str">
+        <x:v>补充来源</x:v>
+      </x:c>
+      <x:c r="C299" s="11" t="str">
+        <x:v>官方配件改版通知</x:v>
+      </x:c>
+      <x:c r="D299" s="11" t="str">
+        <x:v>AZONE：2026 年 8 月起换手配件改版</x:v>
+      </x:c>
+      <x:c r="E299" s="11" t="str">
+        <x:v>换手配件的新旧品番及内容变化；配件另售，不代表素体附送。</x:v>
+      </x:c>
+      <x:c r="F299" s="11" t="str">
+        <x:v>https://news.azone-int.co.jp/archives/70590</x:v>
+      </x:c>
+      <x:c r="G299" s="11" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="H299" s="11" t="str">
+        <x:v>azone-body-pcn048-wht</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="300" ht="72" customHeight="1">
+      <x:c r="A300" s="11" t="str">
+        <x:v>Picco Neemo D · 弟弟 · 白肌</x:v>
+      </x:c>
+      <x:c r="B300" s="11" t="str">
+        <x:v>补充来源</x:v>
+      </x:c>
+      <x:c r="C300" s="11" t="str">
+        <x:v>官方本款发布说明</x:v>
+      </x:c>
+      <x:c r="D300" s="11" t="str">
+        <x:v>Picco Neemo D 弟：交付内容与发售</x:v>
+      </x:c>
+      <x:c r="E300" s="11" t="str">
+        <x:v>PCN048 的身体与首关节、D 系列手脚造型及相对大小。</x:v>
+      </x:c>
+      <x:c r="F300" s="11" t="str">
+        <x:v>https://news.azone-int.co.jp/archives/65442</x:v>
+      </x:c>
+      <x:c r="G300" s="11" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="H300" s="11" t="str">
+        <x:v>azone-body-pcn048-wht</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="301" ht="72" customHeight="1">
+      <x:c r="A301" s="11" t="str">
+        <x:v>OBITSU 26 cm · S 胸</x:v>
+      </x:c>
+      <x:c r="B301" s="11" t="str">
+        <x:v>主来源</x:v>
+      </x:c>
+      <x:c r="C301" s="11" t="str">
+        <x:v>官方产品页</x:v>
+      </x:c>
+      <x:c r="D301" s="11" t="str">
+        <x:v>26BD-F01N-S / OBITSU BODY 26</x:v>
+      </x:c>
+      <x:c r="E301" s="11" t="str">
+        <x:v>本款独立素体、型号、尺寸口径、材料及配件范围；未披露项保留。</x:v>
+      </x:c>
+      <x:c r="F301" s="11" t="str">
+        <x:v>https://obitsu.co.jp/doll-division/obitsu-body-and-parts/obitsu-body/obitsu-body-26/</x:v>
+      </x:c>
+      <x:c r="G301" s="11" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="H301" s="11" t="str">
+        <x:v>bare-26bd-f01n-s</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="302" ht="72" customHeight="1">
+      <x:c r="A302" s="11" t="str">
+        <x:v>OBITSU 26 cm · S 胸</x:v>
+      </x:c>
+      <x:c r="B302" s="11" t="str">
+        <x:v>补充来源</x:v>
+      </x:c>
+      <x:c r="C302" s="11" t="str">
+        <x:v>官方商店型号链接</x:v>
+      </x:c>
+      <x:c r="D302" s="11" t="str">
+        <x:v>【26BD-F01N-S】26cmオビツボディ バストサイズS ナチュラル</x:v>
+      </x:c>
+      <x:c r="E302" s="11" t="str">
+        <x:v>厂家型号说明页直接列出的对应 SKU；库存未单独核对。</x:v>
+      </x:c>
+      <x:c r="F302" s="11" t="str">
+        <x:v>https://www.obitsushop.com/SHOP/26BD-F01N-S.html</x:v>
+      </x:c>
+      <x:c r="G302" s="11" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="H302" s="11" t="str">
+        <x:v>bare-26bd-f01n-s</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="303" ht="72" customHeight="1">
+      <x:c r="A303" s="11" t="str">
+        <x:v>OBITSU 27 cm · 男性 Slim</x:v>
+      </x:c>
+      <x:c r="B303" s="11" t="str">
+        <x:v>主来源</x:v>
+      </x:c>
+      <x:c r="C303" s="11" t="str">
+        <x:v>官方产品页</x:v>
+      </x:c>
+      <x:c r="D303" s="11" t="str">
+        <x:v>27BD-M03N / OBITSU BODY 27 MEN Slim</x:v>
+      </x:c>
+      <x:c r="E303" s="11" t="str">
+        <x:v>本款独立素体、型号、尺寸口径、材料及配件范围；未披露项保留。</x:v>
+      </x:c>
+      <x:c r="F303" s="11" t="str">
+        <x:v>https://obitsu.co.jp/doll-division/obitsu-body-and-parts/obitsu-body/obitsu-body-27-m/</x:v>
+      </x:c>
+      <x:c r="G303" s="11" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="H303" s="11" t="str">
+        <x:v>bare-27bd-m03n</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="304" ht="72" customHeight="1">
+      <x:c r="A304" s="11" t="str">
+        <x:v>OBITSU 27 cm · 男性 Slim</x:v>
+      </x:c>
+      <x:c r="B304" s="11" t="str">
+        <x:v>补充来源</x:v>
+      </x:c>
+      <x:c r="C304" s="11" t="str">
+        <x:v>官方商店型号链接</x:v>
+      </x:c>
+      <x:c r="D304" s="11" t="str">
+        <x:v>【27BD-M03N】男性ボディ　スリム(新型)　ナチュラル</x:v>
+      </x:c>
+      <x:c r="E304" s="11" t="str">
+        <x:v>厂家型号说明页直接列出的对应 SKU；库存未单独核对。</x:v>
+      </x:c>
+      <x:c r="F304" s="11" t="str">
+        <x:v>https://www.obitsushop.com/SHOP/27BD-M03N.html</x:v>
+      </x:c>
+      <x:c r="G304" s="11" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="H304" s="11" t="str">
+        <x:v>bare-27bd-m03n</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="305" ht="72" customHeight="1">
+      <x:c r="A305" s="11" t="str">
+        <x:v>OBITSU 27 cm · 女性 SBH M 胸</x:v>
+      </x:c>
+      <x:c r="B305" s="11" t="str">
+        <x:v>主来源</x:v>
+      </x:c>
+      <x:c r="C305" s="11" t="str">
+        <x:v>官方产品页</x:v>
+      </x:c>
+      <x:c r="D305" s="11" t="str">
+        <x:v>27BD-F06N / OBITSU BODY 27 WOMAN – SBH</x:v>
+      </x:c>
+      <x:c r="E305" s="11" t="str">
+        <x:v>本款独立素体、型号、尺寸口径、材料及配件范围；未披露项保留。</x:v>
+      </x:c>
+      <x:c r="F305" s="11" t="str">
+        <x:v>https://obitsu.co.jp/doll-division/obitsu-body-and-parts/obitsu-body/obitsu-body-27woman-sbh/</x:v>
+      </x:c>
+      <x:c r="G305" s="11" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="H305" s="11" t="str">
+        <x:v>bare-27bd-f06n</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="306" ht="72" customHeight="1">
+      <x:c r="A306" s="11" t="str">
+        <x:v>OBITSU 27 cm · 女性 SBH M 胸</x:v>
+      </x:c>
+      <x:c r="B306" s="11" t="str">
+        <x:v>补充来源</x:v>
+      </x:c>
+      <x:c r="C306" s="11" t="str">
+        <x:v>官方商店型号链接</x:v>
+      </x:c>
+      <x:c r="D306" s="11" t="str">
+        <x:v>【27BD-F06N】女性バージョン　SBH-M胸　ナチュラル</x:v>
+      </x:c>
+      <x:c r="E306" s="11" t="str">
+        <x:v>厂家型号说明页直接列出的对应 SKU；库存未单独核对。</x:v>
+      </x:c>
+      <x:c r="F306" s="11" t="str">
+        <x:v>https://www.obitsushop.com/SHOP/27BD-F06N.html</x:v>
+      </x:c>
+      <x:c r="G306" s="11" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="H306" s="11" t="str">
+        <x:v>bare-27bd-f06n</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="307" ht="72" customHeight="1">
+      <x:c r="A307" s="11" t="str">
+        <x:v>OBITSU 30 cm · 男性素体</x:v>
+      </x:c>
+      <x:c r="B307" s="11" t="str">
+        <x:v>主来源</x:v>
+      </x:c>
+      <x:c r="C307" s="11" t="str">
+        <x:v>官方产品页</x:v>
+      </x:c>
+      <x:c r="D307" s="11" t="str">
+        <x:v>30BD-M01N / OBITSU BODY30</x:v>
+      </x:c>
+      <x:c r="E307" s="11" t="str">
+        <x:v>本款独立素体、型号、尺寸口径、材料及配件范围；未披露项保留。</x:v>
+      </x:c>
+      <x:c r="F307" s="11" t="str">
+        <x:v>https://obitsu.co.jp/doll-division/obitsu-body-and-parts/obitsu-body/obitsu-body30/</x:v>
+      </x:c>
+      <x:c r="G307" s="11" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="H307" s="11" t="str">
+        <x:v>bare-30bd-m01n</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="308" ht="72" customHeight="1">
+      <x:c r="A308" s="11" t="str">
+        <x:v>OBITSU 30 cm · 男性素体</x:v>
+      </x:c>
+      <x:c r="B308" s="11" t="str">
+        <x:v>补充来源</x:v>
+      </x:c>
+      <x:c r="C308" s="11" t="str">
+        <x:v>官方商店型号链接</x:v>
+      </x:c>
+      <x:c r="D308" s="11" t="str">
+        <x:v>【30BD-M01N】30cmオビツボディ ナチュラル</x:v>
+      </x:c>
+      <x:c r="E308" s="11" t="str">
+        <x:v>厂家型号说明页直接列出的对应 SKU；库存未单独核对。</x:v>
+      </x:c>
+      <x:c r="F308" s="11" t="str">
+        <x:v>https://www.obitsushop.com/SHOP/30BD-M01N.html</x:v>
+      </x:c>
+      <x:c r="G308" s="11" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="H308" s="11" t="str">
+        <x:v>bare-30bd-m01n</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="309" ht="72" customHeight="1">
+      <x:c r="A309" s="11" t="str">
+        <x:v>OBITSU Ver.1.5 · GGR50 M 胸</x:v>
+      </x:c>
+      <x:c r="B309" s="11" t="str">
+        <x:v>主来源</x:v>
+      </x:c>
+      <x:c r="C309" s="11" t="str">
+        <x:v>官方产品页</x:v>
+      </x:c>
+      <x:c r="D309" s="11" t="str">
+        <x:v>50BD-GGRW-G / OBITSU BODY Ver1.5 GGR50</x:v>
+      </x:c>
+      <x:c r="E309" s="11" t="str">
+        <x:v>本款独立素体、型号、尺寸口径、材料及配件范围；未披露项保留。</x:v>
+      </x:c>
+      <x:c r="F309" s="11" t="str">
+        <x:v>https://obitsu.co.jp/doll-division/obitsu-body-and-parts/obitsu-body/obitsu-body-ver1-5-ggr50/</x:v>
+      </x:c>
+      <x:c r="G309" s="11" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="H309" s="11" t="str">
+        <x:v>bare-50bd-ggrw-g</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="310" ht="72" customHeight="1">
+      <x:c r="A310" s="11" t="str">
+        <x:v>OBITSU Ver.1.5 · GGR50 M 胸</x:v>
+      </x:c>
+      <x:c r="B310" s="11" t="str">
+        <x:v>补充来源</x:v>
+      </x:c>
+      <x:c r="C310" s="11" t="str">
+        <x:v>官方商店型号链接</x:v>
+      </x:c>
+      <x:c r="D310" s="11" t="str">
+        <x:v>【50BD-GGRW-G】50cmオビツボディ Ver1.5 GGR50　ホワイティ</x:v>
+      </x:c>
+      <x:c r="E310" s="11" t="str">
+        <x:v>厂家型号说明页直接列出的对应 SKU；库存未单独核对。</x:v>
+      </x:c>
+      <x:c r="F310" s="11" t="str">
+        <x:v>https://www.obitsushop.com/SHOP/50BD-GGRW-G.html</x:v>
+      </x:c>
+      <x:c r="G310" s="11" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="H310" s="11" t="str">
+        <x:v>bare-50bd-ggrw-g</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="311" ht="72" customHeight="1">
+      <x:c r="A311" s="11" t="str">
+        <x:v>PICCODO · CHUBBY BODY</x:v>
+      </x:c>
+      <x:c r="B311" s="11" t="str">
+        <x:v>主来源</x:v>
+      </x:c>
+      <x:c r="C311" s="11" t="str">
+        <x:v>官方产品页</x:v>
+      </x:c>
+      <x:c r="D311" s="11" t="str">
+        <x:v>PICCODO CHUBBY BODY</x:v>
+      </x:c>
+      <x:c r="E311" s="11" t="str">
+        <x:v>本款独立素体、型号、尺寸口径、材料及配件范围；未披露项保留。</x:v>
+      </x:c>
+      <x:c r="F311" s="11" t="str">
+        <x:v>https://piccodo.official.ec/items/118319611</x:v>
+      </x:c>
+      <x:c r="G311" s="11" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="H311" s="11" t="str">
+        <x:v>piccodo-118319611</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="312" ht="72" customHeight="1">
+      <x:c r="A312" s="11" t="str">
+        <x:v>PICCODO · BODY11</x:v>
+      </x:c>
+      <x:c r="B312" s="11" t="str">
+        <x:v>主来源</x:v>
+      </x:c>
+      <x:c r="C312" s="11" t="str">
+        <x:v>官方产品页</x:v>
+      </x:c>
+      <x:c r="D312" s="11" t="str">
+        <x:v>PICCODO BODY11</x:v>
+      </x:c>
+      <x:c r="E312" s="11" t="str">
+        <x:v>本款独立素体、型号、尺寸口径、材料及配件范围；未披露项保留。</x:v>
+      </x:c>
+      <x:c r="F312" s="11" t="str">
+        <x:v>https://piccodo.official.ec/items/115850461</x:v>
+      </x:c>
+      <x:c r="G312" s="11" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="H312" s="11" t="str">
+        <x:v>piccodo-115850461</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="313" ht="72" customHeight="1">
+      <x:c r="A313" s="11" t="str">
+        <x:v>PICCODO · BODY10 Ver.2.0</x:v>
+      </x:c>
+      <x:c r="B313" s="11" t="str">
+        <x:v>主来源</x:v>
+      </x:c>
+      <x:c r="C313" s="11" t="str">
+        <x:v>官方产品页</x:v>
+      </x:c>
+      <x:c r="D313" s="11" t="str">
+        <x:v>PICCODO BODY10 Ver.2.0</x:v>
+      </x:c>
+      <x:c r="E313" s="11" t="str">
+        <x:v>本款独立素体、型号、尺寸口径、材料及配件范围；未披露项保留。</x:v>
+      </x:c>
+      <x:c r="F313" s="11" t="str">
+        <x:v>https://piccodo.official.ec/items/76733551</x:v>
+      </x:c>
+      <x:c r="G313" s="11" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="H313" s="11" t="str">
+        <x:v>piccodo-76733551</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="314" ht="72" customHeight="1">
+      <x:c r="A314" s="11" t="str">
+        <x:v>PICCODO · BODY9 Ver.2.0</x:v>
+      </x:c>
+      <x:c r="B314" s="11" t="str">
+        <x:v>主来源</x:v>
+      </x:c>
+      <x:c r="C314" s="11" t="str">
+        <x:v>官方产品页</x:v>
+      </x:c>
+      <x:c r="D314" s="11" t="str">
+        <x:v>PICCODO BODY9 Ver.2.0</x:v>
+      </x:c>
+      <x:c r="E314" s="11" t="str">
+        <x:v>本款独立素体、型号、尺寸口径、材料及配件范围；未披露项保留。</x:v>
+      </x:c>
+      <x:c r="F314" s="11" t="str">
+        <x:v>https://piccodo.official.ec/items/76732953</x:v>
+      </x:c>
+      <x:c r="G314" s="11" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="H314" s="11" t="str">
+        <x:v>piccodo-76732953</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="315" ht="72" customHeight="1">
+      <x:c r="A315" s="11" t="str">
+        <x:v>PICCODO · CUTE BODY10</x:v>
+      </x:c>
+      <x:c r="B315" s="11" t="str">
+        <x:v>主来源</x:v>
+      </x:c>
+      <x:c r="C315" s="11" t="str">
+        <x:v>官方产品页</x:v>
+      </x:c>
+      <x:c r="D315" s="11" t="str">
+        <x:v>PICCODO CUTE BODY10</x:v>
+      </x:c>
+      <x:c r="E315" s="11" t="str">
+        <x:v>本款独立素体、型号、尺寸口径、材料及配件范围；未披露项保留。</x:v>
+      </x:c>
+      <x:c r="F315" s="11" t="str">
+        <x:v>https://piccodo.official.ec/items/72696060</x:v>
+      </x:c>
+      <x:c r="G315" s="11" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="H315" s="11" t="str">
+        <x:v>piccodo-72696060</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="316" ht="72" customHeight="1">
+      <x:c r="A316" s="11" t="str">
+        <x:v>PICCODO · BODY20</x:v>
+      </x:c>
+      <x:c r="B316" s="11" t="str">
+        <x:v>主来源</x:v>
+      </x:c>
+      <x:c r="C316" s="11" t="str">
+        <x:v>官方产品页</x:v>
+      </x:c>
+      <x:c r="D316" s="11" t="str">
+        <x:v>PICCODO BODY20</x:v>
+      </x:c>
+      <x:c r="E316" s="11" t="str">
+        <x:v>本款独立素体、型号、尺寸口径、材料及配件范围；未披露项保留。</x:v>
+      </x:c>
+      <x:c r="F316" s="11" t="str">
+        <x:v>https://piccodo.official.ec/items/72695579</x:v>
+      </x:c>
+      <x:c r="G316" s="11" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="H316" s="11" t="str">
+        <x:v>piccodo-72695579</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="317" ht="72" customHeight="1">
+      <x:c r="A317" s="11" t="str">
+        <x:v>PICCODO · BODY8 PLUS</x:v>
+      </x:c>
+      <x:c r="B317" s="11" t="str">
+        <x:v>主来源</x:v>
+      </x:c>
+      <x:c r="C317" s="11" t="str">
+        <x:v>官方产品页</x:v>
+      </x:c>
+      <x:c r="D317" s="11" t="str">
+        <x:v>PICCODO BODY8 PLUS</x:v>
+      </x:c>
+      <x:c r="E317" s="11" t="str">
+        <x:v>本款独立素体、型号、尺寸口径、材料及配件范围；未披露项保留。</x:v>
+      </x:c>
+      <x:c r="F317" s="11" t="str">
+        <x:v>https://piccodo.official.ec/items/72138227</x:v>
+      </x:c>
+      <x:c r="G317" s="11" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="H317" s="11" t="str">
         <x:v>piccodo-72138227</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="318" ht="72" customHeight="1">
+      <x:c r="A318" s="11" t="str">
+        <x:v>Picco Neemo P · 白肌</x:v>
+      </x:c>
+      <x:c r="B318" s="11" t="str">
+        <x:v>主来源</x:v>
+      </x:c>
+      <x:c r="C318" s="11" t="str">
+        <x:v>官方产品页</x:v>
+      </x:c>
+      <x:c r="D318" s="11" t="str">
+        <x:v>ピコニーモP PCN036-WHT</x:v>
+      </x:c>
+      <x:c r="E318" s="11" t="str">
+        <x:v>本款独立素体、白肌型号、标称比例及头部不附属。</x:v>
+      </x:c>
+      <x:c r="F318" s="11" t="str">
+        <x:v>https://www.azone-int.co.jp/azonet/item/4573199840475</x:v>
+      </x:c>
+      <x:c r="G318" s="11" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="H318" s="11" t="str">
+        <x:v>azone-body-pcn036-wht</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="319" ht="72" customHeight="1">
+      <x:c r="A319" s="11" t="str">
+        <x:v>Picco Neemo P · 白肌</x:v>
+      </x:c>
+      <x:c r="B319" s="11" t="str">
+        <x:v>补充来源</x:v>
+      </x:c>
+      <x:c r="C319" s="11" t="str">
+        <x:v>官方型号与配件目录</x:v>
+      </x:c>
+      <x:c r="D319" s="11" t="str">
+        <x:v>AZONE：1/12 Picco Neemo 素体与配件</x:v>
+      </x:c>
+      <x:c r="E319" s="11" t="str">
+        <x:v>核对当前 PCN 型号及 S／M、D、P 各自的换手和关节配件。</x:v>
+      </x:c>
+      <x:c r="F319" s="11" t="str">
+        <x:v>https://news.azone-int.co.jp/archives/43183</x:v>
+      </x:c>
+      <x:c r="G319" s="11" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="H319" s="11" t="str">
+        <x:v>azone-body-pcn036-wht</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="320" ht="72" customHeight="1">
+      <x:c r="A320" s="11" t="str">
+        <x:v>Picco Neemo P · 白肌</x:v>
+      </x:c>
+      <x:c r="B320" s="11" t="str">
+        <x:v>补充来源</x:v>
+      </x:c>
+      <x:c r="C320" s="11" t="str">
+        <x:v>官方配件改版通知</x:v>
+      </x:c>
+      <x:c r="D320" s="11" t="str">
+        <x:v>AZONE：2026 年 8 月起换手配件改版</x:v>
+      </x:c>
+      <x:c r="E320" s="11" t="str">
+        <x:v>换手配件的新旧品番及内容变化；配件另售，不代表素体附送。</x:v>
+      </x:c>
+      <x:c r="F320" s="11" t="str">
+        <x:v>https://news.azone-int.co.jp/archives/70590</x:v>
+      </x:c>
+      <x:c r="G320" s="11" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="H320" s="11" t="str">
+        <x:v>azone-body-pcn036-wht</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="321" ht="72" customHeight="1">
+      <x:c r="A321" s="11" t="str">
+        <x:v>Q’z BODY · M · C 胸 · 白肌</x:v>
+      </x:c>
+      <x:c r="B321" s="11" t="str">
+        <x:v>主来源</x:v>
+      </x:c>
+      <x:c r="C321" s="11" t="str">
+        <x:v>官方产品页</x:v>
+      </x:c>
+      <x:c r="D321" s="11" t="str">
+        <x:v>AZONE Q’z BODY M/Cバスト AOB016-WHT</x:v>
+      </x:c>
+      <x:c r="E321" s="11" t="str">
+        <x:v>本款独立素体、白肌型号、标称比例及头部不附属。</x:v>
+      </x:c>
+      <x:c r="F321" s="11" t="str">
+        <x:v>https://www.azone-int.co.jp/azonet/item/4573199842639</x:v>
+      </x:c>
+      <x:c r="G321" s="11" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="H321" s="11" t="str">
+        <x:v>azone-body-aob016-wht</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="322" ht="72" customHeight="1">
+      <x:c r="A322" s="11" t="str">
+        <x:v>Q’z BODY · M · C 胸 · 白肌</x:v>
+      </x:c>
+      <x:c r="B322" s="11" t="str">
+        <x:v>补充来源</x:v>
+      </x:c>
+      <x:c r="C322" s="11" t="str">
+        <x:v>官方使用说明</x:v>
+      </x:c>
+      <x:c r="D322" s="11" t="str">
+        <x:v>Q’z BODY：关节方向与活动范围</x:v>
+      </x:c>
+      <x:c r="E322" s="11" t="str">
+        <x:v>Q’z 系列的手腕、髋、膝和脚踝使用限制。</x:v>
+      </x:c>
+      <x:c r="F322" s="11" t="str">
+        <x:v>https://news.azone-int.co.jp/archives/58516</x:v>
+      </x:c>
+      <x:c r="G322" s="11" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="H322" s="11" t="str">
+        <x:v>azone-body-aob016-wht</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="323" ht="72" customHeight="1">
+      <x:c r="A323" s="11" t="str">
+        <x:v>Q’z BODY · M · C 胸 · 白肌</x:v>
+      </x:c>
+      <x:c r="B323" s="11" t="str">
+        <x:v>补充来源</x:v>
+      </x:c>
+      <x:c r="C323" s="11" t="str">
+        <x:v>官方配件改版通知</x:v>
+      </x:c>
+      <x:c r="D323" s="11" t="str">
+        <x:v>AZONE：2026 年 8 月起换手配件改版</x:v>
+      </x:c>
+      <x:c r="E323" s="11" t="str">
+        <x:v>换手配件的新旧品番及内容变化；配件另售，不代表素体附送。</x:v>
+      </x:c>
+      <x:c r="F323" s="11" t="str">
+        <x:v>https://news.azone-int.co.jp/archives/70590</x:v>
+      </x:c>
+      <x:c r="G323" s="11" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="H323" s="11" t="str">
+        <x:v>azone-body-aob016-wht</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -25233,7 +26132,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ed4caca90184e1f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8409bd1aac640c3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25309,7 +26208,7 @@
         <x:v>深红表示厂商标称比例，浅红表示厂商公布的高度等实际尺寸规格，并非自行实测。1:1、2:1 也可能以作品设定中的小型人偶为基准，不能直接换算成人体身高。含头、含底座等测量口径单独保留。</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>比例未披露、高度 54 cm、比例 1:6、高度 27.5 cm、素体 22.5 cm、高度 11 cm、无固定比例、高度 13 cm、比例 1:10、素体 14.2 cm、含头约 16 cm、高度 22 cm、约 1:6、高度 24 cm、约 1:3、高度 50 cm、高度 14 cm、高度 10 cm、高度 23 cm、比例 1:12、高度 17 cm、素体 12.1 cm、含头约 14 cm、比例 1:1、比例 2:1、高度 28 cm、高度 15 cm、比例 1:3、标称 75 cm、标称 73 cm、标称 70 cm、比例 1:4、标称 45 cm、标称 77 cm、标称 71 cm、标称 24 cm、标称 43 cm、高度 16 cm、高度 15.5 cm、高度 13.5 cm、高度 12 cm、高度 14.5 cm、高度 18 cm、高度 15.6 cm、头顶高度 14.8 cm、高度 16.5 cm、高度 15.4 cm、高度 20 cm、高度 8 cm、高度 25 cm、高度 22.5 cm、高度 27 cm、高度 33 cm、高度 21 cm、Polyester · 高度 14 cm、Polyurethane · 高度 14 cm、头顶高度 17 cm、人形高度 17 cm、人形高度 15.5 cm、人形高度 12 cm、含笼架高度 22.5 cm、高度 17.5 cm、Hurricane Honey · 高度 17 cm、Mash · 高度 16.5 cm、高度 18.5 cm、素体 26 cm、素体 27 cm、素体 30 cm、50 cm 级别、素体 9.1 cm、素体 11.3 cm、素体 10.5 cm、素体 9.5 cm、素体 10.9 cm、素体 21.2 cm</x:v>
+        <x:v>比例未披露、高度 54 cm、比例 1:6、高度 27.5 cm、素体 22.5 cm、高度 11 cm、无固定比例、高度 13 cm、比例 1:10、素体 14.2 cm、含头约 16 cm、高度 22 cm、素体全长约 22 cm、约 1:6、标称约 24 cm、规格表全长约 21.8 cm、约 1:3、高度 50 cm、高度 14 cm、高度 10 cm、高度 23 cm、比例 1:12、高度 17 cm、素体 12.1 cm、含头约 14 cm、比例 1:1、比例 2:1、高度 28 cm、高度 15 cm、高度 24 cm、比例 1:3、标称 75 cm、标称 73 cm、标称 70 cm、比例 1:4、标称 45 cm、标称 77 cm、标称 71 cm、标称 24 cm、标称 43 cm、高度 16 cm、高度 15.5 cm、高度 13.5 cm、高度 12 cm、高度 14.5 cm、高度 18 cm、高度 15.6 cm、头顶高度 14.8 cm、高度 16.5 cm、高度 15.4 cm、高度 20 cm、高度 8 cm、高度 25 cm、高度 22.5 cm、高度 27 cm、高度 33 cm、高度 21 cm、Polyester · 高度 14 cm、Polyurethane · 高度 14 cm、头顶高度 17 cm、人形高度 17 cm、人形高度 15.5 cm、人形高度 12 cm、含笼架高度 22.5 cm、高度 17.5 cm、Hurricane Honey · 高度 17 cm、Mash · 高度 16.5 cm、高度 18.5 cm、素体 26 cm、素体 27 cm、素体 30 cm、50 cm 级别、素体 9.1 cm、素体 11.3 cm、素体 10.5 cm、素体 9.5 cm、素体 10.9 cm、素体 21.2 cm</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="160" customHeight="1">
@@ -25323,7 +26222,7 @@
         <x:v>区别成品含服、素体成品、待拼装与服装成品。成品含服仍可能需要自己穿衣；展示照片中的道具不一定属于交付内容。</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
-        <x:v>成品含服、素体成品、待拼装、涂装成品、计划商品、服装成品、裸娃成品、头部另配</x:v>
+        <x:v>成品含服、素体成品、待拼装、头部另配、涂装成品、计划商品、服装成品、裸娃成品</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="160" customHeight="1">
@@ -25375,7 +26274,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf54b3ad234144e91"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R979fda3b47f942c9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25644,7 +26543,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb79d42c7a98a4c77"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5aad55696cfc4152"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25703,8 +26602,8 @@
         <x:v>商品记录</x:v>
       </x:c>
       <x:c r="C5" s="22" t="n">
-        <x:f>COUNTA('产品资料'!A5:A271)</x:f>
-        <x:v>267</x:v>
+        <x:f>COUNTA('产品资料'!A5:A273)</x:f>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
         <x:v>按具体商品／配套条目计数</x:v>
@@ -25746,7 +26645,7 @@
         <x:v>有单一主要高度</x:v>
       </x:c>
       <x:c r="C8" s="22" t="n">
-        <x:f>COUNT('产品资料'!F5:F271)</x:f>
+        <x:f>COUNT('产品资料'!F5:F273)</x:f>
         <x:v>203</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
@@ -25762,7 +26661,7 @@
       </x:c>
       <x:c r="C9" s="22" t="n">
         <x:f>C5-C8</x:f>
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
         <x:v>包括未披露、不适用及多件套</x:v>
@@ -25776,7 +26675,7 @@
         <x:v>来源条数</x:v>
       </x:c>
       <x:c r="C10" s="22" t="n">
-        <x:v>290</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
         <x:v>包含主来源与补充来源</x:v>
@@ -25790,8 +26689,8 @@
         <x:v>AZONE</x:v>
       </x:c>
       <x:c r="C11" s="22" t="n">
-        <x:f>COUNTIFS('产品资料'!$B$5:$B$271,B11)</x:f>
-        <x:v>11</x:v>
+        <x:f>COUNTIFS('产品资料'!$B$5:$B$273,B11)</x:f>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D11" s="11" t="str">
         <x:v>具体型号数量</x:v>
@@ -25805,7 +26704,7 @@
         <x:v>BANDAI SPIRITS</x:v>
       </x:c>
       <x:c r="C12" s="22" t="n">
-        <x:f>COUNTIFS('产品资料'!$B$5:$B$271,B12)</x:f>
+        <x:f>COUNTIFS('产品资料'!$B$5:$B$273,B12)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="D12" s="11" t="str">
@@ -25820,7 +26719,7 @@
         <x:v>DollZone</x:v>
       </x:c>
       <x:c r="C13" s="22" t="n">
-        <x:f>COUNTIFS('产品资料'!$B$5:$B$271,B13)</x:f>
+        <x:f>COUNTIFS('产品资料'!$B$5:$B$273,B13)</x:f>
         <x:v>21</x:v>
       </x:c>
       <x:c r="D13" s="11" t="str">
@@ -25835,7 +26734,7 @@
         <x:v>FREEing</x:v>
       </x:c>
       <x:c r="C14" s="22" t="n">
-        <x:f>COUNTIFS('产品资料'!$B$5:$B$271,B14)</x:f>
+        <x:f>COUNTIFS('产品资料'!$B$5:$B$273,B14)</x:f>
         <x:v>4</x:v>
       </x:c>
       <x:c r="D14" s="11" t="str">
@@ -25850,7 +26749,7 @@
         <x:v>GOODSMILE RACING</x:v>
       </x:c>
       <x:c r="C15" s="22" t="n">
-        <x:f>COUNTIFS('产品资料'!$B$5:$B$271,B15)</x:f>
+        <x:f>COUNTIFS('产品资料'!$B$5:$B$273,B15)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="D15" s="11" t="str">
@@ -25865,7 +26764,7 @@
         <x:v>Good Smile Company</x:v>
       </x:c>
       <x:c r="C16" s="22" t="n">
-        <x:f>COUNTIFS('产品资料'!$B$5:$B$271,B16)</x:f>
+        <x:f>COUNTIFS('产品资料'!$B$5:$B$273,B16)</x:f>
         <x:v>138</x:v>
       </x:c>
       <x:c r="D16" s="11" t="str">
@@ -25880,7 +26779,7 @@
         <x:v>KOTOBUKIYA</x:v>
       </x:c>
       <x:c r="C17" s="22" t="n">
-        <x:f>COUNTIFS('产品资料'!$B$5:$B$271,B17)</x:f>
+        <x:f>COUNTIFS('产品资料'!$B$5:$B$273,B17)</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="D17" s="11" t="str">
@@ -25895,7 +26794,7 @@
         <x:v>Mattel</x:v>
       </x:c>
       <x:c r="C18" s="22" t="n">
-        <x:f>COUNTIFS('产品资料'!$B$5:$B$271,B18)</x:f>
+        <x:f>COUNTIFS('产品资料'!$B$5:$B$273,B18)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="D18" s="11" t="str">
@@ -25910,7 +26809,7 @@
         <x:v>Max Factory</x:v>
       </x:c>
       <x:c r="C19" s="22" t="n">
-        <x:f>COUNTIFS('产品资料'!$B$5:$B$271,B19)</x:f>
+        <x:f>COUNTIFS('产品资料'!$B$5:$B$273,B19)</x:f>
         <x:v>27</x:v>
       </x:c>
       <x:c r="D19" s="11" t="str">
@@ -25925,7 +26824,7 @@
         <x:v>Mezco Toyz</x:v>
       </x:c>
       <x:c r="C20" s="22" t="n">
-        <x:f>COUNTIFS('产品资料'!$B$5:$B$271,B20)</x:f>
+        <x:f>COUNTIFS('产品资料'!$B$5:$B$273,B20)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="D20" s="11" t="str">
@@ -25940,7 +26839,7 @@
         <x:v>OBITSU</x:v>
       </x:c>
       <x:c r="C21" s="22" t="n">
-        <x:f>COUNTIFS('产品资料'!$B$5:$B$271,B21)</x:f>
+        <x:f>COUNTIFS('产品资料'!$B$5:$B$273,B21)</x:f>
         <x:v>9</x:v>
       </x:c>
       <x:c r="D21" s="11" t="str">
@@ -25955,7 +26854,7 @@
         <x:v>ORANGE ROUGE</x:v>
       </x:c>
       <x:c r="C22" s="22" t="n">
-        <x:f>COUNTIFS('产品资料'!$B$5:$B$271,B22)</x:f>
+        <x:f>COUNTIFS('产品资料'!$B$5:$B$273,B22)</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="D22" s="11" t="str">
@@ -25970,7 +26869,7 @@
         <x:v>PICCODO</x:v>
       </x:c>
       <x:c r="C23" s="22" t="n">
-        <x:f>COUNTIFS('产品资料'!$B$5:$B$271,B23)</x:f>
+        <x:f>COUNTIFS('产品资料'!$B$5:$B$273,B23)</x:f>
         <x:v>7</x:v>
       </x:c>
       <x:c r="D23" s="11" t="str">
@@ -25985,7 +26884,7 @@
         <x:v>PetWORKs</x:v>
       </x:c>
       <x:c r="C24" s="22" t="n">
-        <x:f>COUNTIFS('产品资料'!$B$5:$B$271,B24)</x:f>
+        <x:f>COUNTIFS('产品资料'!$B$5:$B$273,B24)</x:f>
         <x:v>26</x:v>
       </x:c>
       <x:c r="D24" s="11" t="str">
@@ -26000,7 +26899,7 @@
         <x:v>Smart Doll</x:v>
       </x:c>
       <x:c r="C25" s="22" t="n">
-        <x:f>COUNTIFS('产品资料'!$B$5:$B$271,B25)</x:f>
+        <x:f>COUNTIFS('产品资料'!$B$5:$B$273,B25)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="D25" s="11" t="str">
@@ -26015,7 +26914,7 @@
         <x:v>TOMYTEC</x:v>
       </x:c>
       <x:c r="C26" s="22" t="n">
-        <x:f>COUNTIFS('产品资料'!$B$5:$B$271,B26)</x:f>
+        <x:f>COUNTIFS('产品资料'!$B$5:$B$273,B26)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="D26" s="11" t="str">
@@ -26030,7 +26929,7 @@
         <x:v>TinyFox</x:v>
       </x:c>
       <x:c r="C27" s="22" t="n">
-        <x:f>COUNTIFS('产品资料'!$B$5:$B$271,B27)</x:f>
+        <x:f>COUNTIFS('产品资料'!$B$5:$B$273,B27)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="D27" s="11" t="str">
@@ -26045,7 +26944,7 @@
         <x:v>VOLKS</x:v>
       </x:c>
       <x:c r="C28" s="22" t="n">
-        <x:f>COUNTIFS('产品资料'!$B$5:$B$271,B28)</x:f>
+        <x:f>COUNTIFS('产品资料'!$B$5:$B$273,B28)</x:f>
         <x:v>4</x:v>
       </x:c>
       <x:c r="D28" s="11" t="str">
@@ -26060,7 +26959,7 @@
         <x:v>可动人形</x:v>
       </x:c>
       <x:c r="C29" s="22" t="n">
-        <x:v>193</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="D29" s="11" t="str">
         <x:v>入口可重叠，不把各类相加当总数</x:v>
@@ -26088,7 +26987,7 @@
         <x:v>素体</x:v>
       </x:c>
       <x:c r="C31" s="22" t="n">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D31" s="11" t="str">
         <x:v>入口可重叠，不把各类相加当总数</x:v>
@@ -26129,7 +27028,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R16f7e4d53ca74733"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1ed21ab66b94451"/>
   </x:tableParts>
 </x:worksheet>
 </file>